--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1348,13 +1348,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.66552056713</v>
+        <v>46079.8321872338</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54914192129</v>
+        <v>46092.715808587964</v>
       </c>
       <c r="D4" s="5">
-        <v>46158.83449060185</v>
+        <v>46159.00115726852</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1397,13 +1397,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66552091435</v>
+        <v>46079.83218758102</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54910645833</v>
+        <v>46092.715773125004</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.54914292824</v>
+        <v>46092.71580959491</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1462,13 +1462,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66552115741</v>
+        <v>46079.832187824075</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54910701389</v>
+        <v>46092.71577368055</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.5491424537</v>
+        <v>46092.715809120375</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1527,13 +1527,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66552142361</v>
+        <v>46079.83218809028</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54910741898</v>
+        <v>46092.71577408565</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54914295139</v>
+        <v>46092.71580961805</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1592,13 +1592,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66552167824</v>
+        <v>46079.83218834491</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.54910778935</v>
+        <v>46092.71577445602</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.61045414352</v>
+        <v>46100.777120810184</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1657,13 +1657,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54910842593</v>
+        <v>46092.71577509259</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.549143275464</v>
+        <v>46092.71580994213</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1722,11 +1722,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.66552293982</v>
+        <v>46079.83218960648</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46100.61045412037</v>
+        <v>46100.77712078704</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1769,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66552079861</v>
+        <v>46079.832187465276</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.377863726855</v>
+        <v>46097.54453039352</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.37788289352</v>
+        <v>46097.54454956019</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1834,11 +1834,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66552108796</v>
+        <v>46079.832187754626</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46114.34928703704</v>
+        <v>46114.5159537037</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1897,11 +1897,11 @@
         <v>54</v>
       </c>
       <c r="B13" s="8">
-        <v>46114.348928506945</v>
+        <v>46114.51559517361</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46139.628807685185</v>
+        <v>46139.79547435185</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>55</v>
@@ -1950,11 +1950,11 @@
         <v>56</v>
       </c>
       <c r="B14" s="5">
-        <v>46114.349081990746</v>
+        <v>46114.5157486574</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46129.54631466435</v>
+        <v>46129.71298133102</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>57</v>
@@ -2003,13 +2003,13 @@
         <v>58</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.665521435185</v>
+        <v>46079.83218810185</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.37807184028</v>
+        <v>46097.54473850694</v>
       </c>
       <c r="D15" s="8">
-        <v>46097.37808972222</v>
+        <v>46097.54475638889</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>59</v>
@@ -2068,11 +2068,11 @@
         <v>61</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.66552181713</v>
+        <v>46079.83218848379</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46100.61045414352</v>
+        <v>46100.777120810184</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>62</v>
@@ -2131,11 +2131,11 @@
         <v>65</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.665522152776</v>
+        <v>46079.83218881945</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46097.37814590278</v>
+        <v>46097.544812569446</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>66</v>
@@ -2178,13 +2178,13 @@
         <v>68</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.37811188657</v>
+        <v>46097.544778553245</v>
       </c>
       <c r="D18" s="5">
-        <v>46097.37877938658</v>
+        <v>46097.54544605324</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>69</v>
@@ -2243,11 +2243,11 @@
         <v>71</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.66552304398</v>
+        <v>46079.83218971065</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46100.610454131944</v>
+        <v>46100.77712079861</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>72</v>
@@ -2306,11 +2306,11 @@
         <v>74</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46114.349770092595</v>
+        <v>46114.51643675926</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>75</v>
@@ -2369,13 +2369,13 @@
         <v>78</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66552032407</v>
+        <v>46079.83218699074</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.3781387037</v>
+        <v>46097.54480537037</v>
       </c>
       <c r="D21" s="8">
-        <v>46100.61084952546</v>
+        <v>46100.77751619213</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>79</v>
@@ -2434,11 +2434,11 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.66552068287</v>
+        <v>46079.83218734954</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46112.33928854167</v>
+        <v>46112.50595520833</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -2481,11 +2481,11 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46169.68261282408</v>
+        <v>46169.849279490736</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -2544,11 +2544,11 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.66552123842</v>
+        <v>46079.83218790509</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.682661875</v>
+        <v>46169.84932854166</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -2603,11 +2603,11 @@
         <v>95</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.665521504634</v>
+        <v>46079.83218817129</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46169.68267998843</v>
+        <v>46169.84934665509</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>96</v>
@@ -2660,11 +2660,11 @@
         <v>98</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.66552247685</v>
+        <v>46079.83218914352</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46121.5665640625</v>
+        <v>46121.733230729165</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>99</v>
@@ -2723,11 +2723,11 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.66552270833</v>
+        <v>46079.832189374996</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46169.68271395833</v>
+        <v>46169.849380625004</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -2782,11 +2782,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.66552043981</v>
+        <v>46079.83218710648</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.682739421296</v>
+        <v>46169.84940608796</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -2841,13 +2841,13 @@
         <v>107</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.665520787035</v>
+        <v>46079.83218745371</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37891262732</v>
+        <v>46097.54557929398</v>
       </c>
       <c r="D29" s="8">
-        <v>46127.011858784725</v>
+        <v>46127.17852545139</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>108</v>
@@ -2906,13 +2906,13 @@
         <v>110</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.66552111111</v>
+        <v>46079.83218777778</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.37881908564</v>
+        <v>46097.545485752315</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.378820983795</v>
+        <v>46097.54548765047</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>111</v>
@@ -2967,13 +2967,13 @@
         <v>113</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.665521365736</v>
+        <v>46079.83218803241</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.378872685185</v>
+        <v>46097.54553935185</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.378873946756</v>
+        <v>46097.54554061343</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>114</v>
@@ -3028,13 +3028,13 @@
         <v>116</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.66552164352</v>
+        <v>46079.83218831019</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.37889787037</v>
+        <v>46097.54556453704</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.37889954861</v>
+        <v>46097.54556621528</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>117</v>
@@ -3089,13 +3089,13 @@
         <v>119</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66552193287</v>
+        <v>46079.83218859954</v>
       </c>
       <c r="C33" s="8">
-        <v>46112.33927761574</v>
+        <v>46112.505944282406</v>
       </c>
       <c r="D33" s="8">
-        <v>46120.0064228588</v>
+        <v>46120.17308952546</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>120</v>
@@ -3154,13 +3154,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66552219907</v>
+        <v>46079.83218886574</v>
       </c>
       <c r="C34" s="5">
-        <v>46097.379011296296</v>
+        <v>46097.54567796296</v>
       </c>
       <c r="D34" s="5">
-        <v>46097.379012881946</v>
+        <v>46097.54567954861</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3215,13 +3215,13 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C35" s="8">
-        <v>46112.34110125</v>
+        <v>46112.50776791667</v>
       </c>
       <c r="D35" s="8">
-        <v>46112.34110265046</v>
+        <v>46112.50776931713</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3276,11 +3276,11 @@
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46127.52321417824</v>
+        <v>46127.689880844904</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3323,13 +3323,13 @@
         <v>133</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.66552299769</v>
+        <v>46079.83218966435</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.350045196756</v>
+        <v>46114.51671186343</v>
       </c>
       <c r="D37" s="8">
-        <v>46127.522372928244</v>
+        <v>46127.68903959491</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>134</v>
@@ -3388,13 +3388,13 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.52245238426</v>
+        <v>46127.68911905093</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.52246925926</v>
+        <v>46127.689135925924</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -3453,13 +3453,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.607717962965</v>
+        <v>46087.77438462963</v>
       </c>
       <c r="C39" s="8">
-        <v>46127.523203958335</v>
+        <v>46127.689870625</v>
       </c>
       <c r="D39" s="8">
-        <v>46127.52323594908</v>
+        <v>46127.68990261574</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3518,11 +3518,11 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46087.60831841435</v>
+        <v>46087.77498508102</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46150.002481076386</v>
+        <v>46150.16914774306</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -3579,11 +3579,11 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.66552171296</v>
+        <v>46079.83218837963</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46080.47855263889</v>
+        <v>46080.64521930556</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3626,11 +3626,11 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.66552199074</v>
+        <v>46079.83218865741</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46122.017928194444</v>
+        <v>46122.184594861115</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3689,11 +3689,11 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.665522256946</v>
+        <v>46079.83218892361</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46126.03956027778</v>
+        <v>46126.20622694444</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3752,11 +3752,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.6655225463</v>
+        <v>46079.83218921296</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46080.479148495375</v>
+        <v>46080.64581516203</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3799,11 +3799,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.66552283565</v>
+        <v>46079.83218950231</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46128.01660333334</v>
+        <v>46128.18327</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>168</v>
@@ -3862,11 +3862,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.66552310185</v>
+        <v>46079.832189768524</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46135.0202475</v>
+        <v>46135.18691416667</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -3925,11 +3925,11 @@
         <v>176</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.66552203704</v>
+        <v>46079.8321887037</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46136.02202104167</v>
+        <v>46136.18868770833</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>177</v>
@@ -3986,11 +3986,11 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.66552230324</v>
+        <v>46079.83218896991</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46087.61757743056</v>
+        <v>46087.78424409722</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>152</v>
@@ -4033,11 +4033,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.66552256944</v>
+        <v>46079.83218923611</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46097.98025273148</v>
+        <v>46098.14691939815</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4096,11 +4096,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.66552284722</v>
+        <v>46079.832189513894</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46113.95844315972</v>
+        <v>46114.12510982639</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4159,11 +4159,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.66552311342</v>
+        <v>46079.83218978009</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46129.006316875</v>
+        <v>46129.17298354166</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4222,11 +4222,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46080.482004537036</v>
+        <v>46080.6486712037</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4269,11 +4269,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.66552392361</v>
+        <v>46079.83219059028</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46142.002359618054</v>
+        <v>46142.169026284726</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4332,11 +4332,11 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46146.001842893515</v>
+        <v>46146.168509560186</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4395,11 +4395,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46147.00122291667</v>
+        <v>46147.16788958333</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4458,11 +4458,11 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.66552163195</v>
+        <v>46079.83218829861</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46148.00131451389</v>
+        <v>46148.16798118055</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4521,11 +4521,11 @@
         <v>208</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46149.00130991898</v>
+        <v>46149.16797658565</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>149</v>
@@ -4584,11 +4584,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.6655221875</v>
+        <v>46079.83218885417</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46153.00153898148</v>
+        <v>46153.16820564815</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4645,11 +4645,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46087.61454869213</v>
+        <v>46087.781215358795</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>214</v>
@@ -4692,11 +4692,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46154.00127270834</v>
+        <v>46154.167939374995</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>212</v>
@@ -4753,11 +4753,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.665522986106</v>
+        <v>46079.83218965278</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46155.08375481481</v>
+        <v>46155.25042148148</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>219</v>
@@ -4816,11 +4816,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.665523275464</v>
+        <v>46079.83218994213</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.08377037037</v>
+        <v>46156.25043703704</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>222</v>
@@ -4877,11 +4877,11 @@
         <v>224</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66552355324</v>
+        <v>46079.83219021991</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46157.0839104051</v>
+        <v>46157.250577071754</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>225</v>
@@ -4940,11 +4940,11 @@
         <v>227</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66552094907</v>
+        <v>46079.83218761574</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46087.61454819444</v>
+        <v>46087.78121486111</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>228</v>
@@ -4987,11 +4987,11 @@
         <v>230</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.66552170139</v>
+        <v>46079.832188368055</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.022141249996</v>
+        <v>46169.18880791667</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>231</v>
@@ -5050,11 +5050,11 @@
         <v>235</v>
       </c>
       <c r="B66" s="5">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46169.02214035879</v>
+        <v>46169.188807025464</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>236</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="237">
   <si>
     <t>50001520 -  XEMORTIZ DDG</t>
   </si>
@@ -172,130 +172,130 @@
     <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
   </si>
   <si>
+    <t>1213899724258045</t>
+  </si>
+  <si>
+    <t>ot 4268 ZVN 1-6-25/2</t>
+  </si>
+  <si>
+    <t>1213899724258046</t>
+  </si>
+  <si>
+    <t>ot 4269 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1213396196529411</t>
+  </si>
+  <si>
+    <t>Ingenieria  Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1213396196529412</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1213899724258045</t>
-  </si>
-  <si>
-    <t>ot 4268 ZVN 1-6-25/2</t>
-  </si>
-  <si>
-    <t>1213899724258046</t>
-  </si>
-  <si>
-    <t>ot 4269 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1213396196529411</t>
-  </si>
-  <si>
-    <t>Ingenieria  Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213396196529412</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
+    <t>1213396196529413</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete,propuesta motor,propuesta alabes,propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213396196529414</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación oc Motor</t>
+  </si>
+  <si>
+    <t>1213396196529415</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe  ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>1213396196529417</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>1213396196529418</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales</t>
+  </si>
+  <si>
+    <t>1213396196529419</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe ot 4268 // ot 4269,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento</t>
+  </si>
+  <si>
+    <t>1213396196529420</t>
+  </si>
+  <si>
+    <t>Alabe ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4268 // ot 4269,Fabricación Alabe  ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>1213396196529421</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe  ot 4268 // ot 4269,Alabe ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>Baja</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213396196529413</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete,propuesta motor,propuesta alabes,propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213396196529414</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación oc Motor</t>
-  </si>
-  <si>
-    <t>1213396196529415</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe  ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>1213396196529417</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>1213396196529418</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales</t>
-  </si>
-  <si>
-    <t>1213396196529419</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe ot 4268 // ot 4269,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento</t>
-  </si>
-  <si>
-    <t>1213396196529420</t>
-  </si>
-  <si>
-    <t>Alabe ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4268 // ot 4269,Fabricación Alabe  ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>1213396196529421</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe  ot 4268 // ot 4269,Alabe ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>Baja</t>
   </si>
   <si>
     <t>1213396196529422</t>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46100.77712078704</v>
+        <v>46191.78179945602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1836,9 +1836,11 @@
       <c r="B12" s="5">
         <v>46079.832187754626</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46191.781787141204</v>
+      </c>
       <c r="D12" s="5">
-        <v>46114.5159537037</v>
+        <v>46191.781807465275</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1883,28 +1885,30 @@
         <v>46085</v>
       </c>
       <c r="S12" s="6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U12" s="12" t="s">
-        <v>53</v>
+      <c r="U12" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="8">
         <v>46114.51559517361</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="8">
+        <v>46191.78184763889</v>
+      </c>
       <c r="D13" s="8">
-        <v>46139.79547435185</v>
+        <v>46191.781849074076</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -1947,17 +1951,19 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="5">
         <v>46114.5157486574</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46191.78186625</v>
+      </c>
       <c r="D14" s="5">
-        <v>46129.71298133102</v>
+        <v>46191.781867453705</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2000,7 +2006,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="8">
         <v>46079.83218810185</v>
@@ -2012,7 +2018,7 @@
         <v>46097.54475638889</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2045,7 +2051,7 @@
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q15" s="8">
         <v>46084</v>
@@ -2065,17 +2071,17 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" s="5">
         <v>46079.83218848379</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46100.777120810184</v>
+        <v>46191.78181219907</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2108,7 +2114,7 @@
         <v>41</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q16" s="5">
         <v>46084</v>
@@ -2122,23 +2128,25 @@
       <c r="T16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U16" s="10" t="s">
-        <v>64</v>
+      <c r="U16" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="8">
         <v>46079.83218881945</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="C17" s="8">
+        <v>46191.78195586806</v>
+      </c>
       <c r="D17" s="8">
-        <v>46097.544812569446</v>
+        <v>46191.781968599535</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>25</v>
@@ -2162,20 +2170,24 @@
         <v>26</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
+      <c r="S17" s="9">
+        <v>1</v>
+      </c>
       <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
+      <c r="U17" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="5">
         <v>46079.83218939815</v>
@@ -2187,7 +2199,7 @@
         <v>46097.54544605324</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2214,13 +2226,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q18" s="5">
         <v>46086</v>
@@ -2240,17 +2252,19 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B19" s="8">
         <v>46079.83218971065</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="8">
+        <v>46191.781938229164</v>
+      </c>
       <c r="D19" s="8">
-        <v>46100.77712079861</v>
+        <v>46191.78195724537</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2277,13 +2291,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>51</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q19" s="8">
         <v>46086</v>
@@ -2292,37 +2306,39 @@
         <v>46087</v>
       </c>
       <c r="S19" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U19" s="10" t="s">
-        <v>64</v>
+      <c r="U19" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="5">
         <v>46079.8321903125</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46191.78194402778</v>
+      </c>
       <c r="D20" s="5">
-        <v>46114.51643675926</v>
+        <v>46191.781959687505</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="H20" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I20" s="5">
         <v>46086</v>
@@ -2340,13 +2356,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>51</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q20" s="5">
         <v>46086</v>
@@ -2355,18 +2371,18 @@
         <v>46087</v>
       </c>
       <c r="S20" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U20" s="10" t="s">
-        <v>64</v>
+      <c r="U20" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" s="8">
         <v>46079.83218699074</v>
@@ -2378,16 +2394,16 @@
         <v>46100.77751619213</v>
       </c>
       <c r="E21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="9" t="s">
+      <c r="H21" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="I21" s="8">
         <v>46087</v>
@@ -2405,13 +2421,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q21" s="8">
         <v>46087</v>
@@ -2431,17 +2447,17 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="5">
         <v>46079.83218734954</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46112.50595520833</v>
+        <v>46191.782222615744</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2465,7 +2481,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2474,30 +2490,34 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
+      <c r="U22" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="8">
         <v>46079.832187673615</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="8">
+        <v>46191.782201967595</v>
+      </c>
       <c r="D23" s="8">
-        <v>46169.849279490736</v>
+        <v>46191.78221601852</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="I23" s="8">
         <v>46090</v>
@@ -2515,13 +2535,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q23" s="8">
         <v>46090</v>
@@ -2530,37 +2550,39 @@
         <v>46093</v>
       </c>
       <c r="S23" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U23" s="10" t="s">
-        <v>64</v>
+      <c r="U23" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83218790509</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46191.78214869213</v>
+      </c>
       <c r="D24" s="5">
-        <v>46169.84932854166</v>
+        <v>46191.78215086806</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="I24" s="5">
         <v>46090</v>
@@ -2578,13 +2600,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2592,10 +2614,10 @@
         <v>0</v>
       </c>
       <c r="T24" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U24" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U24" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2605,9 +2627,11 @@
       <c r="B25" s="8">
         <v>46079.83218817129</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="8">
+        <v>46191.78218685185</v>
+      </c>
       <c r="D25" s="8">
-        <v>46169.84934665509</v>
+        <v>46191.78218898148</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>96</v>
@@ -2616,10 +2640,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="I25" s="8">
         <v>46092</v>
@@ -2637,10 +2661,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>97</v>
@@ -2649,7 +2673,7 @@
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U25" s="11" t="s">
         <v>32</v>
@@ -2662,9 +2686,11 @@
       <c r="B26" s="5">
         <v>46079.83218914352</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46191.78212915509</v>
+      </c>
       <c r="D26" s="5">
-        <v>46121.733230729165</v>
+        <v>46191.78214355324</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>99</v>
@@ -2673,10 +2699,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="I26" s="5">
         <v>46090</v>
@@ -2694,13 +2720,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>100</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q26" s="5">
         <v>46090</v>
@@ -2709,13 +2735,13 @@
         <v>46111</v>
       </c>
       <c r="S26" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U26" s="10" t="s">
-        <v>64</v>
+      <c r="U26" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -2725,9 +2751,11 @@
       <c r="B27" s="8">
         <v>46079.832189374996</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="8">
+        <v>46191.782070057874</v>
+      </c>
       <c r="D27" s="8">
-        <v>46169.849380625004</v>
+        <v>46191.78207137731</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -2736,10 +2764,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="I27" s="8">
         <v>46090</v>
@@ -2760,7 +2788,7 @@
         <v>99</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>103</v>
@@ -2771,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U27" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U27" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -2784,9 +2812,11 @@
       <c r="B28" s="5">
         <v>46079.83218710648</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46191.78211299768</v>
+      </c>
       <c r="D28" s="5">
-        <v>46169.84940608796</v>
+        <v>46191.7821143287</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -2795,10 +2825,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="I28" s="5">
         <v>46092</v>
@@ -2830,10 +2860,10 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U28" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U28" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -2856,10 +2886,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="I29" s="8">
         <v>46090</v>
@@ -2877,13 +2907,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>109</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q29" s="8">
         <v>46090</v>
@@ -2921,10 +2951,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="I30" s="5">
         <v>46090</v>
@@ -2945,7 +2975,7 @@
         <v>108</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>112</v>
@@ -2956,10 +2986,10 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U30" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U30" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -2982,10 +3012,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="I31" s="8">
         <v>46099</v>
@@ -3017,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U31" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U31" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3043,10 +3073,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="I32" s="5">
         <v>46099</v>
@@ -3078,10 +3108,10 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U32" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U32" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3125,13 +3155,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q33" s="8">
         <v>46091</v>
@@ -3146,7 +3176,7 @@
         <v>31</v>
       </c>
       <c r="U33" s="12" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3193,7 +3223,7 @@
         <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>126</v>
@@ -3204,10 +3234,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U34" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U34" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3265,10 +3295,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U35" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U35" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3362,7 +3392,7 @@
         <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>137</v>
@@ -3568,10 +3598,10 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U40" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U40" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3581,9 +3611,11 @@
       <c r="B41" s="8">
         <v>46079.83218837963</v>
       </c>
-      <c r="C41" s="9"/>
+      <c r="C41" s="8">
+        <v>46191.78224238426</v>
+      </c>
       <c r="D41" s="8">
-        <v>46080.64521930556</v>
+        <v>46191.78225478009</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3617,9 +3649,13 @@
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
+      <c r="S41" s="9">
+        <v>1</v>
+      </c>
       <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
+      <c r="U41" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
@@ -3628,9 +3664,11 @@
       <c r="B42" s="5">
         <v>46079.83218865741</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46191.78222800926</v>
+      </c>
       <c r="D42" s="5">
-        <v>46122.184594861115</v>
+        <v>46191.78224288195</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3675,13 +3713,13 @@
         <v>46121</v>
       </c>
       <c r="S42" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U42" s="12" t="s">
-        <v>53</v>
+      <c r="U42" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -3691,9 +3729,11 @@
       <c r="B43" s="8">
         <v>46079.83218892361</v>
       </c>
-      <c r="C43" s="9"/>
+      <c r="C43" s="8">
+        <v>46191.781853368055</v>
+      </c>
       <c r="D43" s="8">
-        <v>46126.20622694444</v>
+        <v>46191.78224165509</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3738,13 +3778,13 @@
         <v>46125</v>
       </c>
       <c r="S43" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U43" s="10" t="s">
-        <v>64</v>
+      <c r="U43" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -3754,9 +3794,11 @@
       <c r="B44" s="5">
         <v>46079.83218921296</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46191.78230420139</v>
+      </c>
       <c r="D44" s="5">
-        <v>46080.64581516203</v>
+        <v>46191.782318287034</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3790,9 +3832,13 @@
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
+      <c r="S44" s="6">
+        <v>1</v>
+      </c>
       <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
+      <c r="U44" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
@@ -3801,9 +3847,11 @@
       <c r="B45" s="8">
         <v>46079.83218950231</v>
       </c>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8">
+        <v>46191.782240671295</v>
+      </c>
       <c r="D45" s="8">
-        <v>46128.18327</v>
+        <v>46191.78225513889</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>168</v>
@@ -3848,13 +3896,13 @@
         <v>46127</v>
       </c>
       <c r="S45" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U45" s="10" t="s">
-        <v>64</v>
+      <c r="U45" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -3864,9 +3912,11 @@
       <c r="B46" s="5">
         <v>46079.832189768524</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46191.78228831018</v>
+      </c>
       <c r="D46" s="5">
-        <v>46135.18691416667</v>
+        <v>46191.78230329861</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -3911,13 +3961,13 @@
         <v>46134</v>
       </c>
       <c r="S46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U46" s="10" t="s">
-        <v>64</v>
+      <c r="U46" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -3927,9 +3977,11 @@
       <c r="B47" s="8">
         <v>46079.8321887037</v>
       </c>
-      <c r="C47" s="9"/>
+      <c r="C47" s="8">
+        <v>46191.78193627315</v>
+      </c>
       <c r="D47" s="8">
-        <v>46136.18868770833</v>
+        <v>46191.7823071875</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>177</v>
@@ -3972,13 +4024,13 @@
         <v>46135</v>
       </c>
       <c r="S47" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U47" s="10" t="s">
-        <v>64</v>
+      <c r="U47" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -3988,9 +4040,11 @@
       <c r="B48" s="5">
         <v>46079.83218896991</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46191.78245119213</v>
+      </c>
       <c r="D48" s="5">
-        <v>46087.78424409722</v>
+        <v>46191.782462372685</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>152</v>
@@ -4024,9 +4078,13 @@
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
-      <c r="S48" s="6"/>
+      <c r="S48" s="6">
+        <v>1</v>
+      </c>
       <c r="T48" s="6"/>
-      <c r="U48" s="6"/>
+      <c r="U48" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
@@ -4035,9 +4093,11 @@
       <c r="B49" s="8">
         <v>46079.83218923611</v>
       </c>
-      <c r="C49" s="9"/>
+      <c r="C49" s="8">
+        <v>46191.78241675926</v>
+      </c>
       <c r="D49" s="8">
-        <v>46098.14691939815</v>
+        <v>46191.78243247685</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4082,13 +4142,13 @@
         <v>46097</v>
       </c>
       <c r="S49" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U49" s="10" t="s">
-        <v>64</v>
+      <c r="U49" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4098,9 +4158,11 @@
       <c r="B50" s="5">
         <v>46079.832189513894</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46191.78242726852</v>
+      </c>
       <c r="D50" s="5">
-        <v>46114.12510982639</v>
+        <v>46191.78244430556</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4145,13 +4207,13 @@
         <v>46113</v>
       </c>
       <c r="S50" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U50" s="10" t="s">
-        <v>64</v>
+      <c r="U50" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4161,9 +4223,11 @@
       <c r="B51" s="8">
         <v>46079.83218978009</v>
       </c>
-      <c r="C51" s="9"/>
+      <c r="C51" s="8">
+        <v>46191.782435497684</v>
+      </c>
       <c r="D51" s="8">
-        <v>46129.17298354166</v>
+        <v>46191.78245195602</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4208,13 +4272,13 @@
         <v>46128</v>
       </c>
       <c r="S51" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>53</v>
+      <c r="U51" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4226,7 +4290,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46080.6486712037</v>
+        <v>46191.78261115741</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4262,7 +4326,9 @@
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
       <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
+      <c r="U52" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
@@ -4271,9 +4337,11 @@
       <c r="B53" s="8">
         <v>46079.83219059028</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46191.78238421296</v>
+      </c>
       <c r="D53" s="8">
-        <v>46142.169026284726</v>
+        <v>46191.7824008912</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>195</v>
@@ -4282,10 +4350,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I53" s="8">
         <v>46136</v>
@@ -4318,13 +4386,13 @@
         <v>46142</v>
       </c>
       <c r="S53" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="U53" s="10" t="s">
-        <v>64</v>
+      <c r="U53" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4334,9 +4402,11 @@
       <c r="B54" s="5">
         <v>46079.832187673615</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46191.7824912037</v>
+      </c>
       <c r="D54" s="5">
-        <v>46146.168509560186</v>
+        <v>46191.78250809028</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4345,10 +4415,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I54" s="5">
         <v>46146</v>
@@ -4381,13 +4451,13 @@
         <v>46146</v>
       </c>
       <c r="S54" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="U54" s="10" t="s">
-        <v>64</v>
+      <c r="U54" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4397,9 +4467,11 @@
       <c r="B55" s="8">
         <v>46079.832188009255</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="8">
+        <v>46191.78258708333</v>
+      </c>
       <c r="D55" s="8">
-        <v>46147.16788958333</v>
+        <v>46191.78260511574</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4408,10 +4480,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I55" s="8">
         <v>46147</v>
@@ -4444,13 +4516,13 @@
         <v>46147</v>
       </c>
       <c r="S55" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="U55" s="10" t="s">
-        <v>64</v>
+        <v>93</v>
+      </c>
+      <c r="U55" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4460,9 +4532,11 @@
       <c r="B56" s="5">
         <v>46079.83218829861</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46191.7825933912</v>
+      </c>
       <c r="D56" s="5">
-        <v>46148.16798118055</v>
+        <v>46191.782608622685</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4471,10 +4545,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I56" s="5">
         <v>46148</v>
@@ -4507,13 +4581,13 @@
         <v>46148</v>
       </c>
       <c r="S56" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="U56" s="10" t="s">
-        <v>64</v>
+        <v>93</v>
+      </c>
+      <c r="U56" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4525,7 +4599,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46149.16797658565</v>
+        <v>46191.78261061343</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>149</v>
@@ -4534,10 +4608,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I57" s="8">
         <v>46149</v>
@@ -4573,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="T57" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="U57" s="10" t="s">
-        <v>64</v>
+        <v>93</v>
+      </c>
+      <c r="U57" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4597,10 +4671,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -4634,10 +4708,10 @@
         <v>0</v>
       </c>
       <c r="T58" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U58" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U58" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4742,10 +4816,10 @@
         <v>0</v>
       </c>
       <c r="T60" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U60" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U60" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4766,10 +4840,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I61" s="8">
         <v>46155</v>
@@ -4805,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="T61" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U61" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U61" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -4866,10 +4940,10 @@
         <v>0</v>
       </c>
       <c r="T62" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U62" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U62" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -4929,10 +5003,10 @@
         <v>0</v>
       </c>
       <c r="T63" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U63" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="U63" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5042,7 +5116,7 @@
         <v>31</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5105,7 +5179,7 @@
         <v>31</v>
       </c>
       <c r="U66" s="10" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="233">
   <si>
     <t>50001520 -  XEMORTIZ DDG</t>
   </si>
@@ -151,7 +151,10 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Ingenieria  Detalle,Ingenieria  Basica Motor,Ingenieria  basica Rodete,Analisis de costeo</t>
+    <t>Ingenieria  Detalle,Ingenieria  Basica Motor,Ingenieria  basica Rodete</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213396196529409</t>
@@ -160,7 +163,7 @@
     <t>Ingenieria  Basica Motor</t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta motor</t>
   </si>
   <si>
     <t>1213396196529410</t>
@@ -169,7 +172,7 @@
     <t>Ingenieria  basica Rodete</t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
   </si>
   <si>
     <t>1213899724258045</t>
@@ -190,19 +193,7 @@
     <t>Ingenieria  Detalle</t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213396196529412</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
   </si>
   <si>
     <t>1213396196529413</t>
@@ -713,9 +704,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Despacho,Analisis de costeo</t>
   </si>
   <si>
     <t>1213458939855371</t>
@@ -1245,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U66"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -1726,7 +1714,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46191.78179945602</v>
+        <v>46192.680794733795</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1762,11 +1750,13 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="U10" s="12" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="8">
         <v>46079.832187465276</v>
@@ -1775,10 +1765,10 @@
         <v>46097.54453039352</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.54454956019</v>
+        <v>46192.680783703705</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
@@ -1811,7 +1801,7 @@
         <v>40</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="8">
         <v>46084</v>
@@ -1831,7 +1821,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="5">
         <v>46079.832187754626</v>
@@ -1840,10 +1830,10 @@
         <v>46191.781787141204</v>
       </c>
       <c r="D12" s="5">
-        <v>46191.781807465275</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -1876,7 +1866,7 @@
         <v>40</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q12" s="5">
         <v>46084</v>
@@ -1896,7 +1886,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8">
         <v>46114.51559517361</v>
@@ -1908,7 +1898,7 @@
         <v>46191.781849074076</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -1935,7 +1925,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>26</v>
@@ -1951,7 +1941,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="5">
         <v>46114.5157486574</v>
@@ -1963,7 +1953,7 @@
         <v>46191.781867453705</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -1990,7 +1980,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>26</v>
@@ -2006,7 +1996,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="8">
         <v>46079.83218810185</v>
@@ -2015,10 +2005,10 @@
         <v>46097.54473850694</v>
       </c>
       <c r="D15" s="8">
-        <v>46097.54475638889</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2051,7 +2041,7 @@
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q15" s="8">
         <v>46084</v>
@@ -2071,33 +2061,29 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.83218848379</v>
-      </c>
-      <c r="C16" s="6"/>
+        <v>46079.83218881945</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46191.78195586806</v>
+      </c>
       <c r="D16" s="5">
-        <v>46191.78181219907</v>
+        <v>46191.781968599535</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="5">
-        <v>46084</v>
-      </c>
-      <c r="J16" s="5">
-        <v>46087</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
       <c r="K16" s="6" t="s">
         <v>26</v>
       </c>
@@ -2105,31 +2091,25 @@
         <v>26</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q16" s="5">
-        <v>46084</v>
-      </c>
-      <c r="R16" s="5">
-        <v>46087</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
       <c r="S16" s="6">
-        <v>0</v>
-      </c>
-      <c r="T16" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>63</v>
+        <v>1</v>
+      </c>
+      <c r="T16" s="6"/>
+      <c r="U16" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -2137,26 +2117,32 @@
         <v>64</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.83218881945</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C17" s="8">
-        <v>46191.78195586806</v>
+        <v>46097.544778553245</v>
       </c>
       <c r="D17" s="8">
-        <v>46191.781968599535</v>
+        <v>46097.54544605324</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>65</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="8">
+        <v>46086</v>
+      </c>
+      <c r="J17" s="8">
+        <v>46087</v>
+      </c>
       <c r="K17" s="9" t="s">
         <v>26</v>
       </c>
@@ -2164,23 +2150,29 @@
         <v>26</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="O17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="P17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
+      <c r="Q17" s="8">
+        <v>46086</v>
+      </c>
+      <c r="R17" s="8">
+        <v>46087</v>
+      </c>
       <c r="S17" s="9">
         <v>1</v>
       </c>
-      <c r="T17" s="9"/>
+      <c r="T17" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="U17" s="11" t="s">
         <v>32</v>
       </c>
@@ -2190,13 +2182,13 @@
         <v>67</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.83218939815</v>
+        <v>46079.83218971065</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.544778553245</v>
+        <v>46191.781938229164</v>
       </c>
       <c r="D18" s="5">
-        <v>46097.54544605324</v>
+        <v>46191.78195724537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>68</v>
@@ -2226,10 +2218,10 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>69</v>
@@ -2255,13 +2247,13 @@
         <v>70</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.83218971065</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C19" s="8">
-        <v>46191.781938229164</v>
+        <v>46191.78194402778</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.78195724537</v>
+        <v>46191.781959687505</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>71</v>
@@ -2270,10 +2262,10 @@
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="I19" s="8">
         <v>46086</v>
@@ -2291,13 +2283,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q19" s="8">
         <v>46086</v>
@@ -2317,58 +2309,58 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.8321903125</v>
+        <v>46079.83218699074</v>
       </c>
       <c r="C20" s="5">
-        <v>46191.78194402778</v>
+        <v>46097.54480537037</v>
       </c>
       <c r="D20" s="5">
-        <v>46191.781959687505</v>
+        <v>46100.77751619213</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I20" s="5">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="J20" s="5">
+        <v>46090</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q20" s="5">
         <v>46087</v>
       </c>
-      <c r="K20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q20" s="5">
-        <v>46086</v>
-      </c>
       <c r="R20" s="5">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="S20" s="6">
         <v>1</v>
@@ -2382,35 +2374,29 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.83218699074</v>
+        <v>46079.83218734954</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.54480537037</v>
+        <v>46192.68083542824</v>
       </c>
       <c r="D21" s="8">
-        <v>46100.77751619213</v>
+        <v>46192.680850335644</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I21" s="8">
-        <v>46087</v>
-      </c>
-      <c r="J21" s="8">
-        <v>46090</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
       <c r="K21" s="9" t="s">
         <v>26</v>
       </c>
@@ -2418,29 +2404,23 @@
         <v>26</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>46087</v>
-      </c>
-      <c r="R21" s="8">
-        <v>46090</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
       <c r="S21" s="9">
         <v>1</v>
       </c>
-      <c r="T21" s="10" t="s">
-        <v>31</v>
-      </c>
+      <c r="T21" s="9"/>
       <c r="U21" s="11" t="s">
         <v>32</v>
       </c>
@@ -2450,24 +2430,32 @@
         <v>82</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.83218734954</v>
-      </c>
-      <c r="C22" s="6"/>
+        <v>46079.832187673615</v>
+      </c>
+      <c r="C22" s="5">
+        <v>46191.782201967595</v>
+      </c>
       <c r="D22" s="5">
-        <v>46191.782222615744</v>
+        <v>46191.78221601852</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>83</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="5">
+        <v>46090</v>
+      </c>
+      <c r="J22" s="5">
+        <v>46093</v>
+      </c>
       <c r="K22" s="6" t="s">
         <v>26</v>
       </c>
@@ -2475,55 +2463,63 @@
         <v>26</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="12" t="s">
-        <v>63</v>
+        <v>80</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>46090</v>
+      </c>
+      <c r="R22" s="5">
+        <v>46093</v>
+      </c>
+      <c r="S22" s="6">
+        <v>1</v>
+      </c>
+      <c r="T22" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="8">
+        <v>46079.83218790509</v>
+      </c>
+      <c r="C23" s="8">
+        <v>46191.78214869213</v>
+      </c>
+      <c r="D23" s="8">
+        <v>46191.78215086806</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="B23" s="8">
-        <v>46079.832187673615</v>
-      </c>
-      <c r="C23" s="8">
-        <v>46191.782201967595</v>
-      </c>
-      <c r="D23" s="8">
-        <v>46191.78221601852</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="I23" s="8">
         <v>46090</v>
       </c>
       <c r="J23" s="8">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>26</v>
@@ -2538,86 +2534,80 @@
         <v>83</v>
       </c>
       <c r="O23" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="P23" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="P23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>46090</v>
-      </c>
-      <c r="R23" s="8">
-        <v>46093</v>
-      </c>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
       <c r="S23" s="9">
-        <v>1</v>
-      </c>
-      <c r="T23" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U23" s="11" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="U23" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.83218790509</v>
+        <v>46079.83218817129</v>
       </c>
       <c r="C24" s="5">
-        <v>46191.78214869213</v>
+        <v>46191.78218685185</v>
       </c>
       <c r="D24" s="5">
-        <v>46191.78215086806</v>
+        <v>46191.78218898148</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H24" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" s="5">
+        <v>46092</v>
+      </c>
+      <c r="J24" s="5">
+        <v>46093</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="O24" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I24" s="5">
-        <v>46090</v>
-      </c>
-      <c r="J24" s="5">
-        <v>46091</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="P24" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="6">
-        <v>0</v>
-      </c>
+      <c r="S24" s="6"/>
       <c r="T24" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="U24" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2625,13 +2615,13 @@
         <v>95</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.83218817129</v>
+        <v>46079.83218914352</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.78218685185</v>
+        <v>46191.78212915509</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.78218898148</v>
+        <v>46191.78214355324</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>96</v>
@@ -2640,16 +2630,16 @@
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I25" s="8">
-        <v>46092</v>
+        <v>46090</v>
       </c>
       <c r="J25" s="8">
-        <v>46093</v>
+        <v>46111</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>26</v>
@@ -2661,19 +2651,25 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="11" t="s">
-        <v>93</v>
+        <v>80</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>46090</v>
+      </c>
+      <c r="R25" s="8">
+        <v>46111</v>
+      </c>
+      <c r="S25" s="9">
+        <v>1</v>
+      </c>
+      <c r="T25" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U25" s="11" t="s">
         <v>32</v>
@@ -2684,13 +2680,13 @@
         <v>98</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.83218914352</v>
+        <v>46079.832189374996</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.78212915509</v>
+        <v>46191.782070057874</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.78214355324</v>
+        <v>46191.78207137731</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>99</v>
@@ -2699,16 +2695,16 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I26" s="5">
         <v>46090</v>
       </c>
       <c r="J26" s="5">
-        <v>46111</v>
+        <v>46091</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>26</v>
@@ -2720,28 +2716,24 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="P26" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="P26" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>46090</v>
-      </c>
-      <c r="R26" s="5">
-        <v>46111</v>
-      </c>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
       <c r="S26" s="6">
-        <v>1</v>
-      </c>
-      <c r="T26" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U26" s="11" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="U26" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -2749,13 +2741,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.832189374996</v>
+        <v>46079.83218710648</v>
       </c>
       <c r="C27" s="8">
-        <v>46191.782070057874</v>
+        <v>46191.78211299768</v>
       </c>
       <c r="D27" s="8">
-        <v>46191.78207137731</v>
+        <v>46191.7821143287</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -2764,16 +2756,16 @@
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I27" s="8">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="J27" s="8">
-        <v>46091</v>
+        <v>46111</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>26</v>
@@ -2785,10 +2777,10 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="O27" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>103</v>
@@ -2799,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -2810,13 +2802,13 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.83218710648</v>
+        <v>46079.83218745371</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.78211299768</v>
+        <v>46097.54557929398</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.7821143287</v>
+        <v>46127.17852545139</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -2825,16 +2817,16 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I28" s="5">
-        <v>46092</v>
+        <v>46090</v>
       </c>
       <c r="J28" s="5">
-        <v>46111</v>
+        <v>46126</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
@@ -2846,24 +2838,28 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>46090</v>
+      </c>
+      <c r="R28" s="5">
+        <v>46126</v>
+      </c>
       <c r="S28" s="6">
-        <v>0</v>
-      </c>
-      <c r="T28" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="U28" s="10" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="T28" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -2871,13 +2867,13 @@
         <v>107</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.83218745371</v>
+        <v>46079.83218777778</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.54557929398</v>
+        <v>46097.545485752315</v>
       </c>
       <c r="D29" s="8">
-        <v>46127.17852545139</v>
+        <v>46097.54548765047</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>108</v>
@@ -2886,16 +2882,16 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I29" s="8">
         <v>46090</v>
       </c>
       <c r="J29" s="8">
-        <v>46126</v>
+        <v>46098</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>26</v>
@@ -2907,28 +2903,24 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="O29" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P29" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="P29" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q29" s="8">
-        <v>46090</v>
-      </c>
-      <c r="R29" s="8">
-        <v>46126</v>
-      </c>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
       <c r="S29" s="9">
-        <v>1</v>
-      </c>
-      <c r="T29" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T29" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="U29" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -2936,13 +2928,13 @@
         <v>110</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.83218777778</v>
+        <v>46079.83218803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.545485752315</v>
+        <v>46097.54553935185</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.54548765047</v>
+        <v>46097.54554061343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>111</v>
@@ -2951,16 +2943,16 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I30" s="5">
-        <v>46090</v>
+        <v>46099</v>
       </c>
       <c r="J30" s="5">
-        <v>46098</v>
+        <v>46126</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -2972,10 +2964,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>112</v>
@@ -2986,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -2997,13 +2989,13 @@
         <v>113</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.83218803241</v>
+        <v>46079.83218831019</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.54553935185</v>
+        <v>46097.54556453704</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.54554061343</v>
+        <v>46097.54556621528</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>114</v>
@@ -3012,16 +3004,16 @@
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I31" s="8">
         <v>46099</v>
       </c>
       <c r="J31" s="8">
-        <v>46126</v>
+        <v>46107</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>26</v>
@@ -3033,10 +3025,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>111</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>115</v>
@@ -3047,10 +3039,10 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3058,13 +3050,13 @@
         <v>116</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.83218831019</v>
+        <v>46079.83218859954</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.54556453704</v>
+        <v>46112.505944282406</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.54556621528</v>
+        <v>46120.17308952546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>117</v>
@@ -3073,16 +3065,16 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="I32" s="5">
-        <v>46099</v>
+        <v>46091</v>
       </c>
       <c r="J32" s="5">
-        <v>46107</v>
+        <v>46119</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3094,56 +3086,60 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>46091</v>
+      </c>
+      <c r="R32" s="5">
+        <v>46119</v>
+      </c>
       <c r="S32" s="6">
-        <v>0</v>
-      </c>
-      <c r="T32" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="U32" s="10" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="T32" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U32" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46079.83218886574</v>
+      </c>
+      <c r="C33" s="8">
+        <v>46097.54567796296</v>
+      </c>
+      <c r="D33" s="8">
+        <v>46097.54567954861</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="B33" s="8">
-        <v>46079.83218859954</v>
-      </c>
-      <c r="C33" s="8">
-        <v>46112.505944282406</v>
-      </c>
-      <c r="D33" s="8">
-        <v>46120.17308952546</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>122</v>
       </c>
       <c r="I33" s="8">
         <v>46091</v>
       </c>
       <c r="J33" s="8">
-        <v>46119</v>
+        <v>46099</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>26</v>
@@ -3155,28 +3151,24 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="O33" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="P33" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="P33" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q33" s="8">
-        <v>46091</v>
-      </c>
-      <c r="R33" s="8">
-        <v>46119</v>
-      </c>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
       <c r="S33" s="9">
-        <v>1</v>
-      </c>
-      <c r="T33" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U33" s="12" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="U33" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3184,13 +3176,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.83218886574</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C34" s="5">
-        <v>46097.54567796296</v>
+        <v>46112.50776791667</v>
       </c>
       <c r="D34" s="5">
-        <v>46097.54567954861</v>
+        <v>46112.50776931713</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3199,31 +3191,31 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H34" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I34" s="5">
+        <v>46100</v>
+      </c>
+      <c r="J34" s="5">
+        <v>46119</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="O34" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="I34" s="5">
-        <v>46091</v>
-      </c>
-      <c r="J34" s="5">
-        <v>46099</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>126</v>
@@ -3234,10 +3226,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3245,32 +3237,24 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.83218913194</v>
-      </c>
-      <c r="C35" s="8">
-        <v>46112.50776791667</v>
-      </c>
+        <v>46079.83218939815</v>
+      </c>
+      <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46112.50776931713</v>
+        <v>46127.689880844904</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I35" s="8">
-        <v>46100</v>
-      </c>
-      <c r="J35" s="8">
-        <v>46119</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
       <c r="K35" s="9" t="s">
         <v>26</v>
       </c>
@@ -3278,52 +3262,54 @@
         <v>26</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
-      <c r="S35" s="9">
-        <v>0</v>
-      </c>
-      <c r="T35" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="U35" s="10" t="s">
-        <v>94</v>
-      </c>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.83218939815</v>
-      </c>
-      <c r="C36" s="6"/>
+        <v>46079.83218966435</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46114.51671186343</v>
+      </c>
       <c r="D36" s="5">
-        <v>46127.689880844904</v>
+        <v>46127.68903959491</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
+        <v>132</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="5">
+        <v>46087</v>
+      </c>
+      <c r="J36" s="5">
+        <v>46093</v>
+      </c>
       <c r="K36" s="6" t="s">
         <v>26</v>
       </c>
@@ -3331,53 +3317,63 @@
         <v>26</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
+        <v>134</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>46087</v>
+      </c>
+      <c r="R36" s="5">
+        <v>46093</v>
+      </c>
+      <c r="S36" s="6">
+        <v>1</v>
+      </c>
+      <c r="T36" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U36" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46079.832188009255</v>
+      </c>
+      <c r="C37" s="8">
+        <v>46127.68911905093</v>
+      </c>
+      <c r="D37" s="8">
+        <v>46127.689135925924</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="8">
-        <v>46079.83218966435</v>
-      </c>
-      <c r="C37" s="8">
-        <v>46114.51671186343</v>
-      </c>
-      <c r="D37" s="8">
-        <v>46127.68903959491</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>136</v>
-      </c>
       <c r="I37" s="8">
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="J37" s="8">
-        <v>46093</v>
+        <v>46114</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>26</v>
@@ -3389,19 +3385,19 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="8">
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="R37" s="8">
-        <v>46093</v>
+        <v>46114</v>
       </c>
       <c r="S37" s="9">
         <v>1</v>
@@ -3415,58 +3411,58 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46079.832188009255</v>
+        <v>46087.77438462963</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.68911905093</v>
+        <v>46127.689870625</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.689135925924</v>
+        <v>46127.68990261574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H38" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="5">
+        <v>46115</v>
+      </c>
+      <c r="J38" s="5">
+        <v>46115</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="O38" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="I38" s="5">
-        <v>46108</v>
-      </c>
-      <c r="J38" s="5">
-        <v>46114</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>141</v>
       </c>
       <c r="Q38" s="5">
-        <v>46108</v>
+        <v>46115</v>
       </c>
       <c r="R38" s="5">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="S38" s="6">
         <v>1</v>
@@ -3483,13 +3479,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.77438462963</v>
-      </c>
-      <c r="C39" s="8">
-        <v>46127.689870625</v>
-      </c>
+        <v>46087.77498508102</v>
+      </c>
+      <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46127.68990261574</v>
+        <v>46150.16914774306</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3498,16 +3492,14 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="I39" s="8">
-        <v>46115</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="I39" s="9"/>
       <c r="J39" s="8">
-        <v>46115</v>
+        <v>46150</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>26</v>
@@ -3519,57 +3511,55 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="8">
-        <v>46115</v>
+        <v>46150</v>
       </c>
       <c r="R39" s="8">
-        <v>46115</v>
+        <v>46150</v>
       </c>
       <c r="S39" s="9">
-        <v>1</v>
-      </c>
-      <c r="T39" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T39" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="U39" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46087.77498508102</v>
-      </c>
-      <c r="C40" s="6"/>
+        <v>46079.83218837963</v>
+      </c>
+      <c r="C40" s="5">
+        <v>46191.78224238426</v>
+      </c>
       <c r="D40" s="5">
-        <v>46150.16914774306</v>
+        <v>46191.78225478009</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>148</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H40" s="6"/>
       <c r="I40" s="6"/>
-      <c r="J40" s="5">
-        <v>46150</v>
-      </c>
+      <c r="J40" s="6"/>
       <c r="K40" s="6" t="s">
         <v>26</v>
       </c>
@@ -3577,31 +3567,25 @@
         <v>26</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>131</v>
+        <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>46150</v>
-      </c>
-      <c r="R40" s="5">
-        <v>46150</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
       <c r="S40" s="6">
-        <v>0</v>
-      </c>
-      <c r="T40" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="U40" s="10" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="T40" s="6"/>
+      <c r="U40" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3609,26 +3593,32 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.83218837963</v>
+        <v>46079.83218865741</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.78224238426</v>
+        <v>46191.78222800926</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.78225478009</v>
+        <v>46191.78224288195</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
+        <v>153</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="I41" s="8">
+        <v>46120</v>
+      </c>
+      <c r="J41" s="8">
+        <v>46121</v>
+      </c>
       <c r="K41" s="9" t="s">
         <v>26</v>
       </c>
@@ -3636,57 +3626,63 @@
         <v>26</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
+        <v>155</v>
+      </c>
+      <c r="Q41" s="8">
+        <v>46120</v>
+      </c>
+      <c r="R41" s="8">
+        <v>46121</v>
+      </c>
       <c r="S41" s="9">
         <v>1</v>
       </c>
-      <c r="T41" s="9"/>
+      <c r="T41" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="U41" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.83218865741</v>
+        <v>46079.83218892361</v>
       </c>
       <c r="C42" s="5">
-        <v>46191.78222800926</v>
+        <v>46191.781853368055</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.78224288195</v>
+        <v>46191.78224165509</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="J42" s="5">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>26</v>
@@ -3698,19 +3694,19 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="O42" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="O42" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q42" s="5">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="R42" s="5">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="S42" s="6">
         <v>1</v>
@@ -3718,41 +3714,35 @@
       <c r="T42" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U42" s="11" t="s">
-        <v>32</v>
+      <c r="U42" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.83218892361</v>
+        <v>46079.83218921296</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.781853368055</v>
+        <v>46191.78230420139</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.78224165509</v>
+        <v>46191.782318287034</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="I43" s="8">
-        <v>46122</v>
-      </c>
-      <c r="J43" s="8">
-        <v>46125</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
       <c r="K43" s="9" t="s">
         <v>26</v>
       </c>
@@ -3760,31 +3750,25 @@
         <v>26</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q43" s="8">
-        <v>46122</v>
-      </c>
-      <c r="R43" s="8">
-        <v>46125</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
       <c r="S43" s="9">
         <v>1</v>
       </c>
-      <c r="T43" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U43" s="12" t="s">
-        <v>63</v>
+      <c r="T43" s="9"/>
+      <c r="U43" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -3792,26 +3776,32 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.83218921296</v>
+        <v>46079.83218950231</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.78230420139</v>
+        <v>46191.782240671295</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.782318287034</v>
+        <v>46191.78225513889</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
+        <v>166</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I44" s="5">
+        <v>46126</v>
+      </c>
+      <c r="J44" s="5">
+        <v>46127</v>
+      </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
       </c>
@@ -3819,57 +3809,63 @@
         <v>26</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
+        <v>168</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>46126</v>
+      </c>
+      <c r="R44" s="5">
+        <v>46127</v>
+      </c>
       <c r="S44" s="6">
         <v>1</v>
       </c>
-      <c r="T44" s="6"/>
+      <c r="T44" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="U44" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46079.832189768524</v>
+      </c>
+      <c r="C45" s="8">
+        <v>46191.78228831018</v>
+      </c>
+      <c r="D45" s="8">
+        <v>46191.78230329861</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B45" s="8">
-        <v>46079.83218950231</v>
-      </c>
-      <c r="C45" s="8">
-        <v>46191.782240671295</v>
-      </c>
-      <c r="D45" s="8">
-        <v>46191.78225513889</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="I45" s="8">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="J45" s="8">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>26</v>
@@ -3881,19 +3877,19 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="8">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="R45" s="8">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="S45" s="9">
         <v>1</v>
@@ -3907,34 +3903,32 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.832189768524</v>
+        <v>46079.8321887037</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.78228831018</v>
+        <v>46191.78193627315</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.78230329861</v>
+        <v>46191.7823071875</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="I46" s="5">
-        <v>46128</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="I46" s="6"/>
       <c r="J46" s="5">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>26</v>
@@ -3946,19 +3940,19 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q46" s="5">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="R46" s="5">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="S46" s="6">
         <v>1</v>
@@ -3966,39 +3960,35 @@
       <c r="T46" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U46" s="11" t="s">
-        <v>32</v>
+      <c r="U46" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.8321887037</v>
+        <v>46079.83218896991</v>
       </c>
       <c r="C47" s="8">
-        <v>46191.78193627315</v>
+        <v>46191.78245119213</v>
       </c>
       <c r="D47" s="8">
-        <v>46191.7823071875</v>
+        <v>46191.782462372685</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>162</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H47" s="9"/>
       <c r="I47" s="9"/>
-      <c r="J47" s="8">
-        <v>46135</v>
-      </c>
+      <c r="J47" s="9"/>
       <c r="K47" s="9" t="s">
         <v>26</v>
       </c>
@@ -4006,58 +3996,58 @@
         <v>26</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>178</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q47" s="8">
-        <v>46135</v>
-      </c>
-      <c r="R47" s="8">
-        <v>46135</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
       <c r="S47" s="9">
         <v>1</v>
       </c>
-      <c r="T47" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U47" s="12" t="s">
-        <v>63</v>
+      <c r="T47" s="9"/>
+      <c r="U47" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B48" s="5">
+        <v>46079.83218923611</v>
+      </c>
+      <c r="C48" s="5">
+        <v>46191.78241675926</v>
+      </c>
+      <c r="D48" s="5">
+        <v>46191.78243247685</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B48" s="5">
-        <v>46079.83218896991</v>
-      </c>
-      <c r="C48" s="5">
-        <v>46191.78245119213</v>
-      </c>
-      <c r="D48" s="5">
-        <v>46191.782462372685</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="F48" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
+        <v>153</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I48" s="5">
+        <v>46094</v>
+      </c>
+      <c r="J48" s="5">
+        <v>46097</v>
+      </c>
       <c r="K48" s="6" t="s">
         <v>26</v>
       </c>
@@ -4065,23 +4055,29 @@
         <v>26</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="P48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
+      <c r="Q48" s="5">
+        <v>46094</v>
+      </c>
+      <c r="R48" s="5">
+        <v>46097</v>
+      </c>
       <c r="S48" s="6">
         <v>1</v>
       </c>
-      <c r="T48" s="6"/>
+      <c r="T48" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="U48" s="11" t="s">
         <v>32</v>
       </c>
@@ -4091,13 +4087,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.83218923611</v>
+        <v>46079.832189513894</v>
       </c>
       <c r="C49" s="8">
-        <v>46191.78241675926</v>
+        <v>46191.78242726852</v>
       </c>
       <c r="D49" s="8">
-        <v>46191.78243247685</v>
+        <v>46191.78244430556</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4106,16 +4102,16 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I49" s="8">
-        <v>46094</v>
+        <v>46112</v>
       </c>
       <c r="J49" s="8">
-        <v>46097</v>
+        <v>46113</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>26</v>
@@ -4127,19 +4123,19 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>184</v>
       </c>
       <c r="Q49" s="8">
-        <v>46094</v>
+        <v>46112</v>
       </c>
       <c r="R49" s="8">
-        <v>46097</v>
+        <v>46113</v>
       </c>
       <c r="S49" s="9">
         <v>1</v>
@@ -4156,13 +4152,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.832189513894</v>
+        <v>46079.83218978009</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.78242726852</v>
+        <v>46191.782435497684</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.78244430556</v>
+        <v>46191.78245195602</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4171,16 +4167,16 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I50" s="5">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="J50" s="5">
-        <v>46113</v>
+        <v>46128</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>26</v>
@@ -4192,19 +4188,19 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>187</v>
       </c>
       <c r="Q50" s="5">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="R50" s="5">
-        <v>46113</v>
+        <v>46128</v>
       </c>
       <c r="S50" s="6">
         <v>1</v>
@@ -4221,32 +4217,24 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.83218978009</v>
-      </c>
-      <c r="C51" s="8">
-        <v>46191.782435497684</v>
-      </c>
+        <v>46079.8321903125</v>
+      </c>
+      <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46191.78245195602</v>
+        <v>46191.78261115741</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="I51" s="8">
-        <v>46127</v>
-      </c>
-      <c r="J51" s="8">
-        <v>46128</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
       <c r="K51" s="9" t="s">
         <v>26</v>
       </c>
@@ -4254,31 +4242,23 @@
         <v>26</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q51" s="8">
-        <v>46127</v>
-      </c>
-      <c r="R51" s="8">
-        <v>46128</v>
-      </c>
-      <c r="S51" s="9">
-        <v>1</v>
-      </c>
-      <c r="T51" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U51" s="11" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4286,24 +4266,32 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.8321903125</v>
-      </c>
-      <c r="C52" s="6"/>
+        <v>46079.83219059028</v>
+      </c>
+      <c r="C52" s="5">
+        <v>46191.78238421296</v>
+      </c>
       <c r="D52" s="5">
-        <v>46191.78261115741</v>
+        <v>46191.7824008912</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I52" s="5">
+        <v>46136</v>
+      </c>
+      <c r="J52" s="5">
+        <v>46142</v>
+      </c>
       <c r="K52" s="6" t="s">
         <v>26</v>
       </c>
@@ -4311,55 +4299,63 @@
         <v>26</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="P52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="12" t="s">
-        <v>63</v>
+      <c r="Q52" s="5">
+        <v>46136</v>
+      </c>
+      <c r="R52" s="5">
+        <v>46142</v>
+      </c>
+      <c r="S52" s="6">
+        <v>1</v>
+      </c>
+      <c r="T52" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="U52" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.83219059028</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.78238421296</v>
+        <v>46191.7824912037</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.7824008912</v>
+        <v>46191.78250809028</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I53" s="8">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="J53" s="8">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>26</v>
@@ -4371,25 +4367,25 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="8">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="R53" s="8">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="S53" s="9">
         <v>1</v>
       </c>
       <c r="T53" s="12" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="U53" s="11" t="s">
         <v>32</v>
@@ -4397,64 +4393,64 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B54" s="5">
+        <v>46079.832188009255</v>
+      </c>
+      <c r="C54" s="5">
+        <v>46191.78258708333</v>
+      </c>
+      <c r="D54" s="5">
+        <v>46191.78260511574</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I54" s="5">
+        <v>46147</v>
+      </c>
+      <c r="J54" s="5">
+        <v>46147</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B54" s="5">
-        <v>46079.832187673615</v>
-      </c>
-      <c r="C54" s="5">
-        <v>46191.7824912037</v>
-      </c>
-      <c r="D54" s="5">
-        <v>46191.78250809028</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="I54" s="5">
-        <v>46146</v>
-      </c>
-      <c r="J54" s="5">
-        <v>46146</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>201</v>
-      </c>
       <c r="Q54" s="5">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="R54" s="5">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="S54" s="6">
         <v>1</v>
       </c>
-      <c r="T54" s="12" t="s">
-        <v>197</v>
+      <c r="T54" s="11" t="s">
+        <v>90</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>32</v>
@@ -4465,13 +4461,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.832188009255</v>
+        <v>46079.83218829861</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.78258708333</v>
+        <v>46191.7825933912</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.78260511574</v>
+        <v>46191.782608622685</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4480,16 +4476,16 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I55" s="8">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="J55" s="8">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="K55" s="9" t="s">
         <v>26</v>
@@ -4501,25 +4497,25 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>204</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="8">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="R55" s="8">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="S55" s="9">
         <v>1</v>
       </c>
       <c r="T55" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U55" s="11" t="s">
         <v>32</v>
@@ -4530,94 +4526,90 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.83218829861</v>
-      </c>
-      <c r="C56" s="5">
-        <v>46191.7825933912</v>
-      </c>
+        <v>46079.83218858796</v>
+      </c>
+      <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.782608622685</v>
+        <v>46191.78261061343</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I56" s="5">
+        <v>46149</v>
+      </c>
+      <c r="J56" s="5">
+        <v>46149</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="O56" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="I56" s="5">
-        <v>46148</v>
-      </c>
-      <c r="J56" s="5">
-        <v>46148</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>207</v>
-      </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="Q56" s="5">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="R56" s="5">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="S56" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="U56" s="11" t="s">
-        <v>32</v>
+        <v>90</v>
+      </c>
+      <c r="U56" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.83218858796</v>
+        <v>46079.83218885417</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.78261061343</v>
+        <v>46153.16820564815</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>149</v>
+        <v>208</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I57" s="8">
-        <v>46149</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I57" s="9"/>
       <c r="J57" s="8">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>26</v>
@@ -4629,28 +4621,28 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O57" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="P57" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="P57" s="9" t="s">
-        <v>146</v>
-      </c>
       <c r="Q57" s="8">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="R57" s="8">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="S57" s="9">
         <v>0</v>
       </c>
       <c r="T57" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="U57" s="12" t="s">
-        <v>63</v>
+        <v>90</v>
+      </c>
+      <c r="U57" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4658,28 +4650,24 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.83218885417</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46153.16820564815</v>
+        <v>46087.781215358795</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H58" s="6"/>
       <c r="I58" s="6"/>
-      <c r="J58" s="5">
-        <v>46153</v>
-      </c>
+      <c r="J58" s="6"/>
       <c r="K58" s="6" t="s">
         <v>26</v>
       </c>
@@ -4687,106 +4675,112 @@
         <v>26</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>146</v>
+        <v>212</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q58" s="5">
-        <v>46153</v>
-      </c>
-      <c r="R58" s="5">
-        <v>46153</v>
-      </c>
-      <c r="S58" s="6">
-        <v>0</v>
-      </c>
-      <c r="T58" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="U58" s="10" t="s">
-        <v>94</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6"/>
+      <c r="U58" s="6"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.83218913194</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46087.781215358795</v>
+        <v>46154.167939374995</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" s="9"/>
+      <c r="J59" s="8">
+        <v>46154</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="O59" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" s="9" t="s">
+      <c r="Q59" s="8">
+        <v>46154</v>
+      </c>
+      <c r="R59" s="8">
+        <v>46154</v>
+      </c>
+      <c r="S59" s="9">
         <v>0</v>
       </c>
-      <c r="N59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O59" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q59" s="9"/>
-      <c r="R59" s="9"/>
-      <c r="S59" s="9"/>
-      <c r="T59" s="9"/>
-      <c r="U59" s="9"/>
+      <c r="T59" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="U59" s="10" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.83218939815</v>
+        <v>46079.83218965278</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46154.167939374995</v>
+        <v>46155.25042148148</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I60" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="I60" s="5">
+        <v>46155</v>
+      </c>
       <c r="J60" s="5">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
@@ -4798,28 +4792,28 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>217</v>
       </c>
       <c r="Q60" s="5">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="R60" s="5">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="S60" s="6">
         <v>0</v>
       </c>
       <c r="T60" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4827,11 +4821,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.83218965278</v>
+        <v>46079.83218994213</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46155.25042148148</v>
+        <v>46156.25043703704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>219</v>
@@ -4840,16 +4834,14 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I61" s="8">
-        <v>46155</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="I61" s="9"/>
       <c r="J61" s="8">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="K61" s="9" t="s">
         <v>26</v>
@@ -4861,10 +4853,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>220</v>
@@ -4879,10 +4871,10 @@
         <v>0</v>
       </c>
       <c r="T61" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U61" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -4890,11 +4882,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.83218994213</v>
+        <v>46079.83219021991</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.25043703704</v>
+        <v>46157.250577071754</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>222</v>
@@ -4903,14 +4895,16 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="I62" s="6"/>
+        <v>167</v>
+      </c>
+      <c r="I62" s="5">
+        <v>46157</v>
+      </c>
       <c r="J62" s="5">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
@@ -4922,7 +4916,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>219</v>
@@ -4931,19 +4925,19 @@
         <v>223</v>
       </c>
       <c r="Q62" s="5">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="R62" s="5">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="S62" s="6">
         <v>0</v>
       </c>
       <c r="T62" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U62" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -4951,30 +4945,24 @@
         <v>224</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.83219021991</v>
+        <v>46079.83218761574</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46157.250577071754</v>
+        <v>46087.78121486111</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>225</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="I63" s="8">
-        <v>46157</v>
-      </c>
-      <c r="J63" s="8">
-        <v>46157</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
       <c r="K63" s="9" t="s">
         <v>26</v>
       </c>
@@ -4982,56 +4970,52 @@
         <v>26</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q63" s="8">
-        <v>46157</v>
-      </c>
-      <c r="R63" s="8">
-        <v>46157</v>
-      </c>
-      <c r="S63" s="9">
-        <v>0</v>
-      </c>
-      <c r="T63" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="U63" s="10" t="s">
-        <v>94</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q63" s="9"/>
+      <c r="R63" s="9"/>
+      <c r="S63" s="9"/>
+      <c r="T63" s="9"/>
+      <c r="U63" s="9"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>227</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.83218761574</v>
+        <v>46079.832188368055</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46087.78121486111</v>
+        <v>46192.680783738426</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>228</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
+        <v>229</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I64" s="5">
+        <v>46160</v>
+      </c>
+      <c r="J64" s="5">
+        <v>46168</v>
+      </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
       </c>
@@ -5039,45 +5023,55 @@
         <v>26</v>
       </c>
       <c r="M64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>46160</v>
+      </c>
+      <c r="R64" s="5">
+        <v>46168</v>
+      </c>
+      <c r="S64" s="6">
         <v>0</v>
       </c>
-      <c r="N64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+      <c r="T64" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U64" s="10" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.832188368055</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.18880791667</v>
+        <v>46169.188807025464</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I65" s="8">
         <v>46160</v>
@@ -5095,13 +5089,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q65" s="8">
         <v>46160</v>
@@ -5116,70 +5110,7 @@
         <v>31</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B66" s="5">
-        <v>46079.832188009255</v>
-      </c>
-      <c r="C66" s="6"/>
-      <c r="D66" s="5">
-        <v>46169.188807025464</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="I66" s="5">
-        <v>46160</v>
-      </c>
-      <c r="J66" s="5">
-        <v>46168</v>
-      </c>
-      <c r="K66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q66" s="5">
-        <v>46160</v>
-      </c>
-      <c r="R66" s="5">
-        <v>46168</v>
-      </c>
-      <c r="S66" s="6">
-        <v>0</v>
-      </c>
-      <c r="T66" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U66" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -154,226 +154,226 @@
     <t>Ingenieria  Detalle,Ingenieria  Basica Motor,Ingenieria  basica Rodete</t>
   </si>
   <si>
+    <t>1213396196529409</t>
+  </si>
+  <si>
+    <t>Ingenieria  Basica Motor</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213396196529410</t>
+  </si>
+  <si>
+    <t>Ingenieria  basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213899724258045</t>
+  </si>
+  <si>
+    <t>ot 4268 ZVN 1-6-25/2</t>
+  </si>
+  <si>
+    <t>1213899724258046</t>
+  </si>
+  <si>
+    <t>ot 4269 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1213396196529411</t>
+  </si>
+  <si>
+    <t>Ingenieria  Detalle</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1213396196529413</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete,propuesta motor,propuesta alabes,propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213396196529414</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación oc Motor</t>
+  </si>
+  <si>
+    <t>1213396196529415</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe  ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>1213396196529417</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>1213396196529418</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales</t>
+  </si>
+  <si>
+    <t>1213396196529419</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe ot 4268 // ot 4269,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento</t>
+  </si>
+  <si>
+    <t>1213396196529420</t>
+  </si>
+  <si>
+    <t>Alabe ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4268 // ot 4269,Fabricación Alabe  ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>1213396196529421</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe  ot 4268 // ot 4269,Alabe ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1213396196529422</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe  ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>Alabe ot 4268 // ot 4269,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1213396196529426</t>
+  </si>
+  <si>
+    <t>rodete</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4268 // ot 4269,Fabricación Rodete  ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>1213396196529427</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete  ot 4268 // ot 4269,rodete</t>
+  </si>
+  <si>
+    <t>1213396196529428</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete  ot 4268 // ot 4269</t>
+  </si>
+  <si>
+    <t>rodete,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1213458940250178</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Generación oc Motor,Fabricación motor,Planos proveedor</t>
+  </si>
+  <si>
+    <t>1213458940250179</t>
+  </si>
+  <si>
+    <t>Generación oc Motor</t>
+  </si>
+  <si>
+    <t>Fabricación motor,Planos proveedor,Motor</t>
+  </si>
+  <si>
+    <t>1213458940250180</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor,Recepcion Motor</t>
+  </si>
+  <si>
+    <t>1213458940250181</t>
+  </si>
+  <si>
+    <t>Planos proveedor</t>
+  </si>
+  <si>
+    <t>Motor,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213458940250182</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213396196529409</t>
-  </si>
-  <si>
-    <t>Ingenieria  Basica Motor</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213396196529410</t>
-  </si>
-  <si>
-    <t>Ingenieria  basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213899724258045</t>
-  </si>
-  <si>
-    <t>ot 4268 ZVN 1-6-25/2</t>
-  </si>
-  <si>
-    <t>1213899724258046</t>
-  </si>
-  <si>
-    <t>ot 4269 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1213396196529411</t>
-  </si>
-  <si>
-    <t>Ingenieria  Detalle</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213396196529413</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete,propuesta motor,propuesta alabes,propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213396196529414</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación oc Motor</t>
-  </si>
-  <si>
-    <t>1213396196529415</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe  ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>1213396196529417</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>1213396196529418</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales</t>
-  </si>
-  <si>
-    <t>1213396196529419</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe ot 4268 // ot 4269,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento</t>
-  </si>
-  <si>
-    <t>1213396196529420</t>
-  </si>
-  <si>
-    <t>Alabe ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4268 // ot 4269,Fabricación Alabe  ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>1213396196529421</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe  ot 4268 // ot 4269,Alabe ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213396196529422</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe  ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>Alabe ot 4268 // ot 4269,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1213396196529426</t>
-  </si>
-  <si>
-    <t>rodete</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4268 // ot 4269,Fabricación Rodete  ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>1213396196529427</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete  ot 4268 // ot 4269,rodete</t>
-  </si>
-  <si>
-    <t>1213396196529428</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete  ot 4268 // ot 4269</t>
-  </si>
-  <si>
-    <t>rodete,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1213458940250178</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>Generación oc Motor,Fabricación motor,Planos proveedor</t>
-  </si>
-  <si>
-    <t>1213458940250179</t>
-  </si>
-  <si>
-    <t>Generación oc Motor</t>
-  </si>
-  <si>
-    <t>Fabricación motor,Planos proveedor,Motor</t>
-  </si>
-  <si>
-    <t>1213458940250180</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor,Recepcion Motor</t>
-  </si>
-  <si>
-    <t>1213458940250181</t>
-  </si>
-  <si>
-    <t>Planos proveedor</t>
-  </si>
-  <si>
-    <t>Motor,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213458940250182</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
   </si>
   <si>
     <t>1213458940250183</t>
@@ -1712,9 +1712,11 @@
       <c r="B10" s="5">
         <v>46079.83218960648</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46193.559375868055</v>
+      </c>
       <c r="D10" s="5">
-        <v>46192.680794733795</v>
+        <v>46193.559412372684</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1748,15 +1750,17 @@
       </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
+      <c r="S10" s="6">
+        <v>1</v>
+      </c>
       <c r="T10" s="6"/>
-      <c r="U10" s="12" t="s">
-        <v>47</v>
+      <c r="U10" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="8">
         <v>46079.832187465276</v>
@@ -1768,7 +1772,7 @@
         <v>46192.680783703705</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
@@ -1801,7 +1805,7 @@
         <v>40</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q11" s="8">
         <v>46084</v>
@@ -1821,7 +1825,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="5">
         <v>46079.832187754626</v>
@@ -1833,7 +1837,7 @@
         <v>46192.680783749995</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -1866,7 +1870,7 @@
         <v>40</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q12" s="5">
         <v>46084</v>
@@ -1886,7 +1890,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="8">
         <v>46114.51559517361</v>
@@ -1898,7 +1902,7 @@
         <v>46191.781849074076</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -1925,7 +1929,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>26</v>
@@ -1941,7 +1945,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="5">
         <v>46114.5157486574</v>
@@ -1953,7 +1957,7 @@
         <v>46191.781867453705</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -1980,7 +1984,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>26</v>
@@ -1996,7 +2000,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="8">
         <v>46079.83218810185</v>
@@ -2008,7 +2012,7 @@
         <v>46192.680783749995</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2041,7 +2045,7 @@
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q15" s="8">
         <v>46084</v>
@@ -2061,7 +2065,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" s="5">
         <v>46079.83218881945</v>
@@ -2073,7 +2077,7 @@
         <v>46191.781968599535</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -2097,7 +2101,7 @@
         <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>26</v>
@@ -2114,7 +2118,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="8">
         <v>46079.83218939815</v>
@@ -2126,7 +2130,7 @@
         <v>46097.54544605324</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2153,13 +2157,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q17" s="8">
         <v>46086</v>
@@ -2179,7 +2183,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18" s="5">
         <v>46079.83218971065</v>
@@ -2191,7 +2195,7 @@
         <v>46191.78195724537</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2218,13 +2222,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q18" s="5">
         <v>46086</v>
@@ -2244,7 +2248,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="8">
         <v>46079.8321903125</v>
@@ -2256,16 +2260,16 @@
         <v>46191.781959687505</v>
       </c>
       <c r="E19" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>72</v>
-      </c>
       <c r="H19" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I19" s="8">
         <v>46086</v>
@@ -2283,13 +2287,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q19" s="8">
         <v>46086</v>
@@ -2309,7 +2313,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="5">
         <v>46079.83218699074</v>
@@ -2321,16 +2325,16 @@
         <v>46100.77751619213</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I20" s="5">
         <v>46087</v>
@@ -2348,13 +2352,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q20" s="5">
         <v>46087</v>
@@ -2374,7 +2378,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B21" s="8">
         <v>46079.83218734954</v>
@@ -2386,7 +2390,7 @@
         <v>46192.680850335644</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2410,7 +2414,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2427,7 +2431,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" s="5">
         <v>46079.832187673615</v>
@@ -2439,16 +2443,16 @@
         <v>46191.78221601852</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46090</v>
@@ -2466,13 +2470,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q22" s="5">
         <v>46090</v>
@@ -2492,7 +2496,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="8">
         <v>46079.83218790509</v>
@@ -2504,16 +2508,16 @@
         <v>46191.78215086806</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="I23" s="8">
         <v>46090</v>
@@ -2531,13 +2535,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
@@ -2545,15 +2549,15 @@
         <v>0</v>
       </c>
       <c r="T23" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U23" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U23" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83218817129</v>
@@ -2565,16 +2569,16 @@
         <v>46191.78218898148</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I24" s="5">
         <v>46092</v>
@@ -2592,19 +2596,19 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U24" s="11" t="s">
         <v>32</v>
@@ -2612,7 +2616,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8">
         <v>46079.83218914352</v>
@@ -2624,16 +2628,16 @@
         <v>46191.78214355324</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="I25" s="8">
         <v>46090</v>
@@ -2651,13 +2655,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q25" s="8">
         <v>46090</v>
@@ -2677,7 +2681,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46079.832189374996</v>
@@ -2689,16 +2693,16 @@
         <v>46191.78207137731</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I26" s="5">
         <v>46090</v>
@@ -2716,13 +2720,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2730,15 +2734,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U26" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U26" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8">
         <v>46079.83218710648</v>
@@ -2750,16 +2754,16 @@
         <v>46191.7821143287</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="I27" s="8">
         <v>46092</v>
@@ -2777,13 +2781,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2791,15 +2795,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U27" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U27" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46079.83218745371</v>
@@ -2811,16 +2815,16 @@
         <v>46127.17852545139</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I28" s="5">
         <v>46090</v>
@@ -2838,13 +2842,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q28" s="5">
         <v>46090</v>
@@ -2864,7 +2868,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83218777778</v>
@@ -2876,16 +2880,16 @@
         <v>46097.54548765047</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="I29" s="8">
         <v>46090</v>
@@ -2903,13 +2907,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -2917,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U29" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U29" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83218803241</v>
@@ -2937,16 +2941,16 @@
         <v>46097.54554061343</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I30" s="5">
         <v>46099</v>
@@ -2964,13 +2968,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -2978,15 +2982,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U30" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U30" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83218831019</v>
@@ -2998,16 +3002,16 @@
         <v>46097.54556621528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="I31" s="8">
         <v>46099</v>
@@ -3025,13 +3029,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3039,15 +3043,15 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U31" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U31" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83218859954</v>
@@ -3059,16 +3063,16 @@
         <v>46120.17308952546</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I32" s="5">
         <v>46091</v>
@@ -3086,13 +3090,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q32" s="5">
         <v>46091</v>
@@ -3107,7 +3111,7 @@
         <v>31</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3130,10 +3134,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>119</v>
       </c>
       <c r="I33" s="8">
         <v>46091</v>
@@ -3151,10 +3155,10 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>123</v>
@@ -3165,10 +3169,10 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U33" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U33" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3191,10 +3195,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I34" s="5">
         <v>46100</v>
@@ -3212,7 +3216,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>122</v>
@@ -3226,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U34" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U34" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3323,7 +3327,7 @@
         <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>134</v>
@@ -3483,7 +3487,7 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46150.16914774306</v>
+        <v>46193.60539675926</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3529,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="U39" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
+      </c>
+      <c r="U39" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3715,7 +3719,7 @@
         <v>31</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -3961,7 +3965,7 @@
         <v>31</v>
       </c>
       <c r="U46" s="12" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4061,7 +4065,7 @@
         <v>149</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>181</v>
@@ -4126,7 +4130,7 @@
         <v>149</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>184</v>
@@ -4191,7 +4195,7 @@
         <v>149</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>187</v>
@@ -4258,7 +4262,7 @@
       <c r="S51" s="9"/>
       <c r="T51" s="9"/>
       <c r="U51" s="12" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4281,10 +4285,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I52" s="5">
         <v>46136</v>
@@ -4346,10 +4350,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I53" s="8">
         <v>46146</v>
@@ -4411,10 +4415,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I54" s="5">
         <v>46147</v>
@@ -4450,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>32</v>
@@ -4476,10 +4480,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I55" s="8">
         <v>46148</v>
@@ -4515,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="T55" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U55" s="11" t="s">
         <v>32</v>
@@ -4528,9 +4532,11 @@
       <c r="B56" s="5">
         <v>46079.83218858796</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46193.605380381945</v>
+      </c>
       <c r="D56" s="5">
-        <v>46191.78261061343</v>
+        <v>46193.60613947916</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>
@@ -4539,10 +4545,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I56" s="5">
         <v>46149</v>
@@ -4575,13 +4581,13 @@
         <v>46149</v>
       </c>
       <c r="S56" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="U56" s="12" t="s">
-        <v>47</v>
+        <v>89</v>
+      </c>
+      <c r="U56" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4602,10 +4608,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4639,10 +4645,10 @@
         <v>0</v>
       </c>
       <c r="T57" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U57" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U57" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4747,10 +4753,10 @@
         <v>0</v>
       </c>
       <c r="T59" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U59" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U59" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4771,10 +4777,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I60" s="5">
         <v>46155</v>
@@ -4810,10 +4816,10 @@
         <v>0</v>
       </c>
       <c r="T60" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U60" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U60" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4825,7 +4831,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46156.25043703704</v>
+        <v>46193.560094953704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>219</v>
@@ -4871,10 +4877,10 @@
         <v>0</v>
       </c>
       <c r="T61" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U61" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U61" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -4934,10 +4940,10 @@
         <v>0</v>
       </c>
       <c r="T62" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U62" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="U62" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5047,7 +5053,7 @@
         <v>31</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5110,7 +5116,7 @@
         <v>31</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46193.60539675926</v>
+        <v>46196.902704189815</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1336,13 +1336,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.8321872338</v>
+        <v>46079.66552056713</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.715808587964</v>
+        <v>46092.54914192129</v>
       </c>
       <c r="D4" s="5">
-        <v>46159.00115726852</v>
+        <v>46158.83449060185</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1385,13 +1385,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.83218758102</v>
+        <v>46079.66552091435</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.715773125004</v>
+        <v>46092.54910645833</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.71580959491</v>
+        <v>46092.54914292824</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1450,13 +1450,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.832187824075</v>
+        <v>46079.66552115741</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.71577368055</v>
+        <v>46092.54910701389</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.715809120375</v>
+        <v>46092.5491424537</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1515,13 +1515,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.83218809028</v>
+        <v>46079.66552142361</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71577408565</v>
+        <v>46092.54910741898</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71580961805</v>
+        <v>46092.54914295139</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1580,13 +1580,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.83218834491</v>
+        <v>46079.66552167824</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71577445602</v>
+        <v>46092.54910778935</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.777120810184</v>
+        <v>46100.61045414352</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1645,13 +1645,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.83218858796</v>
+        <v>46079.6655219213</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71577509259</v>
+        <v>46092.54910842593</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71580994213</v>
+        <v>46092.549143275464</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1710,13 +1710,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.83218960648</v>
+        <v>46079.66552293982</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.559375868055</v>
+        <v>46193.39270920139</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.559412372684</v>
+        <v>46193.39274570602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1763,13 +1763,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.832187465276</v>
+        <v>46079.66552079861</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54453039352</v>
+        <v>46097.377863726855</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.680783703705</v>
+        <v>46192.51411703703</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1828,13 +1828,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.832187754626</v>
+        <v>46079.66552108796</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.781787141204</v>
+        <v>46191.61512047454</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.680783749995</v>
+        <v>46192.51411708334</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1893,13 +1893,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46114.51559517361</v>
+        <v>46114.348928506945</v>
       </c>
       <c r="C13" s="8">
-        <v>46191.78184763889</v>
+        <v>46191.61518097222</v>
       </c>
       <c r="D13" s="8">
-        <v>46191.781849074076</v>
+        <v>46191.615182407404</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -1948,13 +1948,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46114.5157486574</v>
+        <v>46114.349081990746</v>
       </c>
       <c r="C14" s="5">
-        <v>46191.78186625</v>
+        <v>46191.615199583335</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.781867453705</v>
+        <v>46191.61520078704</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2003,13 +2003,13 @@
         <v>57</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.83218810185</v>
+        <v>46079.665521435185</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.54473850694</v>
+        <v>46097.37807184028</v>
       </c>
       <c r="D15" s="8">
-        <v>46192.680783749995</v>
+        <v>46192.51411708334</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>58</v>
@@ -2068,13 +2068,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.83218881945</v>
+        <v>46079.665522152776</v>
       </c>
       <c r="C16" s="5">
-        <v>46191.78195586806</v>
+        <v>46191.61528920139</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.781968599535</v>
+        <v>46191.61530193287</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>61</v>
@@ -2121,13 +2121,13 @@
         <v>63</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.544778553245</v>
+        <v>46097.37811188657</v>
       </c>
       <c r="D17" s="8">
-        <v>46097.54544605324</v>
+        <v>46097.37877938658</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>64</v>
@@ -2186,13 +2186,13 @@
         <v>66</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.83218971065</v>
+        <v>46079.66552304398</v>
       </c>
       <c r="C18" s="5">
-        <v>46191.781938229164</v>
+        <v>46191.6152715625</v>
       </c>
       <c r="D18" s="5">
-        <v>46191.78195724537</v>
+        <v>46191.6152905787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>67</v>
@@ -2251,13 +2251,13 @@
         <v>69</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.8321903125</v>
+        <v>46079.66552364583</v>
       </c>
       <c r="C19" s="8">
-        <v>46191.78194402778</v>
+        <v>46191.61527736111</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.781959687505</v>
+        <v>46191.61529302083</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -2316,13 +2316,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.83218699074</v>
+        <v>46079.66552032407</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.54480537037</v>
+        <v>46097.3781387037</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.77751619213</v>
+        <v>46100.61084952546</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -2381,13 +2381,13 @@
         <v>78</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.83218734954</v>
+        <v>46079.66552068287</v>
       </c>
       <c r="C21" s="8">
-        <v>46192.68083542824</v>
+        <v>46192.51416876157</v>
       </c>
       <c r="D21" s="8">
-        <v>46192.680850335644</v>
+        <v>46192.51418366898</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>79</v>
@@ -2434,13 +2434,13 @@
         <v>81</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.832187673615</v>
+        <v>46079.665521006944</v>
       </c>
       <c r="C22" s="5">
-        <v>46191.782201967595</v>
+        <v>46191.61553530092</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.78221601852</v>
+        <v>46191.61554935185</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>82</v>
@@ -2499,13 +2499,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.83218790509</v>
+        <v>46079.66552123842</v>
       </c>
       <c r="C23" s="8">
-        <v>46191.78214869213</v>
+        <v>46191.61548202546</v>
       </c>
       <c r="D23" s="8">
-        <v>46191.78215086806</v>
+        <v>46191.61548420139</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -2560,13 +2560,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.83218817129</v>
+        <v>46079.665521504634</v>
       </c>
       <c r="C24" s="5">
-        <v>46191.78218685185</v>
+        <v>46191.61552018518</v>
       </c>
       <c r="D24" s="5">
-        <v>46191.78218898148</v>
+        <v>46191.615522314816</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -2619,13 +2619,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.83218914352</v>
+        <v>46079.66552247685</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.78212915509</v>
+        <v>46191.61546248842</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.78214355324</v>
+        <v>46191.615476886574</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -2684,13 +2684,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.832189374996</v>
+        <v>46079.66552270833</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.782070057874</v>
+        <v>46191.6154033912</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.78207137731</v>
+        <v>46191.61540471065</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -2745,13 +2745,13 @@
         <v>100</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.83218710648</v>
+        <v>46079.66552043981</v>
       </c>
       <c r="C27" s="8">
-        <v>46191.78211299768</v>
+        <v>46191.61544633102</v>
       </c>
       <c r="D27" s="8">
-        <v>46191.7821143287</v>
+        <v>46191.615447662036</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -2806,13 +2806,13 @@
         <v>103</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.83218745371</v>
+        <v>46079.665520787035</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.54557929398</v>
+        <v>46097.37891262732</v>
       </c>
       <c r="D28" s="5">
-        <v>46127.17852545139</v>
+        <v>46127.011858784725</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>104</v>
@@ -2871,13 +2871,13 @@
         <v>106</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.83218777778</v>
+        <v>46079.66552111111</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.545485752315</v>
+        <v>46097.37881908564</v>
       </c>
       <c r="D29" s="8">
-        <v>46097.54548765047</v>
+        <v>46097.378820983795</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>107</v>
@@ -2932,13 +2932,13 @@
         <v>109</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.83218803241</v>
+        <v>46079.665521365736</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.54553935185</v>
+        <v>46097.378872685185</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.54554061343</v>
+        <v>46097.378873946756</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>110</v>
@@ -2993,13 +2993,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.83218831019</v>
+        <v>46079.66552164352</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.54556453704</v>
+        <v>46097.37889787037</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.54556621528</v>
+        <v>46097.37889954861</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>113</v>
@@ -3054,13 +3054,13 @@
         <v>115</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.83218859954</v>
+        <v>46079.66552193287</v>
       </c>
       <c r="C32" s="5">
-        <v>46112.505944282406</v>
+        <v>46112.33927761574</v>
       </c>
       <c r="D32" s="5">
-        <v>46120.17308952546</v>
+        <v>46120.0064228588</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>116</v>
@@ -3119,13 +3119,13 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.83218886574</v>
+        <v>46079.66552219907</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.54567796296</v>
+        <v>46097.379011296296</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.54567954861</v>
+        <v>46097.379012881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3180,13 +3180,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.83218913194</v>
+        <v>46079.66552246528</v>
       </c>
       <c r="C34" s="5">
-        <v>46112.50776791667</v>
+        <v>46112.34110125</v>
       </c>
       <c r="D34" s="5">
-        <v>46112.50776931713</v>
+        <v>46112.34110265046</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3241,11 +3241,11 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46127.689880844904</v>
+        <v>46127.52321417824</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3288,13 +3288,13 @@
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.83218966435</v>
+        <v>46079.66552299769</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.51671186343</v>
+        <v>46114.350045196756</v>
       </c>
       <c r="D36" s="5">
-        <v>46127.68903959491</v>
+        <v>46127.522372928244</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3353,13 +3353,13 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C37" s="8">
-        <v>46127.68911905093</v>
+        <v>46127.52245238426</v>
       </c>
       <c r="D37" s="8">
-        <v>46127.689135925924</v>
+        <v>46127.52246925926</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -3418,13 +3418,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46087.77438462963</v>
+        <v>46087.607717962965</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.689870625</v>
+        <v>46127.523203958335</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.68990261574</v>
+        <v>46127.52323594908</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3483,11 +3483,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.77498508102</v>
+        <v>46087.60831841435</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46196.902704189815</v>
+        <v>46196.73603752315</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3544,13 +3544,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.83218837963</v>
+        <v>46079.66552171296</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.78224238426</v>
+        <v>46191.61557571759</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.78225478009</v>
+        <v>46191.615588113425</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3597,13 +3597,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.83218865741</v>
+        <v>46079.66552199074</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.78222800926</v>
+        <v>46191.615561342594</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.78224288195</v>
+        <v>46191.61557621528</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3662,13 +3662,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.83218892361</v>
+        <v>46079.665522256946</v>
       </c>
       <c r="C42" s="5">
-        <v>46191.781853368055</v>
+        <v>46191.61518670139</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.78224165509</v>
+        <v>46191.61557498843</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3727,13 +3727,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.83218921296</v>
+        <v>46079.6655225463</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.78230420139</v>
+        <v>46191.61563753472</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.782318287034</v>
+        <v>46191.61565162037</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>162</v>
@@ -3780,13 +3780,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.83218950231</v>
+        <v>46079.66552283565</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.782240671295</v>
+        <v>46191.61557400463</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.78225513889</v>
+        <v>46191.615588472225</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3845,13 +3845,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.832189768524</v>
+        <v>46079.66552310185</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.78228831018</v>
+        <v>46191.61562164352</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.78230329861</v>
+        <v>46191.61563663195</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -3910,13 +3910,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.8321887037</v>
+        <v>46079.66552203704</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.78193627315</v>
+        <v>46191.61526960648</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.7823071875</v>
+        <v>46191.61564052083</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -3973,13 +3973,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.83218896991</v>
+        <v>46079.66552230324</v>
       </c>
       <c r="C47" s="8">
-        <v>46191.78245119213</v>
+        <v>46191.615784525464</v>
       </c>
       <c r="D47" s="8">
-        <v>46191.782462372685</v>
+        <v>46191.61579570602</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4026,13 +4026,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.83218923611</v>
+        <v>46079.66552256944</v>
       </c>
       <c r="C48" s="5">
-        <v>46191.78241675926</v>
+        <v>46191.61575009259</v>
       </c>
       <c r="D48" s="5">
-        <v>46191.78243247685</v>
+        <v>46191.61576581019</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4091,13 +4091,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.832189513894</v>
+        <v>46079.66552284722</v>
       </c>
       <c r="C49" s="8">
-        <v>46191.78242726852</v>
+        <v>46191.61576060185</v>
       </c>
       <c r="D49" s="8">
-        <v>46191.78244430556</v>
+        <v>46191.615777638886</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4156,13 +4156,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.83218978009</v>
+        <v>46079.66552311342</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.782435497684</v>
+        <v>46191.61576883102</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.78245195602</v>
+        <v>46191.61578528935</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4221,11 +4221,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.8321903125</v>
+        <v>46079.66552364583</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46191.78261115741</v>
+        <v>46191.61594449074</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4270,13 +4270,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.83219059028</v>
+        <v>46079.66552392361</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.78238421296</v>
+        <v>46191.6157175463</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.7824008912</v>
+        <v>46191.61573422454</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4335,13 +4335,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.832187673615</v>
+        <v>46079.665521006944</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.7824912037</v>
+        <v>46191.61582453703</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.78250809028</v>
+        <v>46191.61584142361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4400,13 +4400,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.78258708333</v>
+        <v>46191.61592041666</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.78260511574</v>
+        <v>46191.615938449075</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4465,13 +4465,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.83218829861</v>
+        <v>46079.66552163195</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.7825933912</v>
+        <v>46191.61592672454</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.782608622685</v>
+        <v>46191.61594195601</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4530,13 +4530,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.83218858796</v>
+        <v>46079.6655219213</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.605380381945</v>
+        <v>46193.43871371528</v>
       </c>
       <c r="D56" s="5">
-        <v>46193.60613947916</v>
+        <v>46193.439472812504</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>
@@ -4595,11 +4595,11 @@
         <v>207</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.83218885417</v>
+        <v>46079.6655221875</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46153.16820564815</v>
+        <v>46153.00153898148</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>208</v>
@@ -4656,11 +4656,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.83218913194</v>
+        <v>46079.66552246528</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46087.781215358795</v>
+        <v>46087.61454869213</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4703,11 +4703,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46154.167939374995</v>
+        <v>46154.00127270834</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -4764,11 +4764,11 @@
         <v>215</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.83218965278</v>
+        <v>46079.665522986106</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.25042148148</v>
+        <v>46155.08375481481</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
@@ -4827,11 +4827,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.83218994213</v>
+        <v>46079.665523275464</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46193.560094953704</v>
+        <v>46193.39342828703</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>219</v>
@@ -4888,11 +4888,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.83219021991</v>
+        <v>46079.66552355324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46157.250577071754</v>
+        <v>46157.0839104051</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>222</v>
@@ -4951,11 +4951,11 @@
         <v>224</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.83218761574</v>
+        <v>46079.66552094907</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.78121486111</v>
+        <v>46087.61454819444</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>225</v>
@@ -4998,11 +4998,11 @@
         <v>227</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.832188368055</v>
+        <v>46079.66552170139</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46192.680783738426</v>
+        <v>46192.514117071754</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>228</v>
@@ -5061,11 +5061,11 @@
         <v>231</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.188807025464</v>
+        <v>46169.02214035879</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>232</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1336,13 +1336,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.66552056713</v>
+        <v>46079.8321872338</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54914192129</v>
+        <v>46092.715808587964</v>
       </c>
       <c r="D4" s="5">
-        <v>46158.83449060185</v>
+        <v>46159.00115726852</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1385,13 +1385,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66552091435</v>
+        <v>46079.83218758102</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54910645833</v>
+        <v>46092.715773125004</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.54914292824</v>
+        <v>46092.71580959491</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1450,13 +1450,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66552115741</v>
+        <v>46079.832187824075</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54910701389</v>
+        <v>46092.71577368055</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.5491424537</v>
+        <v>46092.715809120375</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1515,13 +1515,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66552142361</v>
+        <v>46079.83218809028</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54910741898</v>
+        <v>46092.71577408565</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54914295139</v>
+        <v>46092.71580961805</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1580,13 +1580,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66552167824</v>
+        <v>46079.83218834491</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.54910778935</v>
+        <v>46092.71577445602</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.61045414352</v>
+        <v>46100.777120810184</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1645,13 +1645,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54910842593</v>
+        <v>46092.71577509259</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.549143275464</v>
+        <v>46092.71580994213</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1710,13 +1710,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.66552293982</v>
+        <v>46079.83218960648</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.39270920139</v>
+        <v>46193.559375868055</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.39274570602</v>
+        <v>46193.559412372684</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1763,13 +1763,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66552079861</v>
+        <v>46079.832187465276</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.377863726855</v>
+        <v>46097.54453039352</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.51411703703</v>
+        <v>46192.680783703705</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1828,13 +1828,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66552108796</v>
+        <v>46079.832187754626</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.61512047454</v>
+        <v>46191.781787141204</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.51411708334</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1893,13 +1893,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46114.348928506945</v>
+        <v>46114.51559517361</v>
       </c>
       <c r="C13" s="8">
-        <v>46191.61518097222</v>
+        <v>46191.78184763889</v>
       </c>
       <c r="D13" s="8">
-        <v>46191.615182407404</v>
+        <v>46191.781849074076</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -1948,13 +1948,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46114.349081990746</v>
+        <v>46114.5157486574</v>
       </c>
       <c r="C14" s="5">
-        <v>46191.615199583335</v>
+        <v>46191.78186625</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.61520078704</v>
+        <v>46191.781867453705</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2003,13 +2003,13 @@
         <v>57</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.665521435185</v>
+        <v>46079.83218810185</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.37807184028</v>
+        <v>46097.54473850694</v>
       </c>
       <c r="D15" s="8">
-        <v>46192.51411708334</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>58</v>
@@ -2068,13 +2068,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.665522152776</v>
+        <v>46079.83218881945</v>
       </c>
       <c r="C16" s="5">
-        <v>46191.61528920139</v>
+        <v>46191.78195586806</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.61530193287</v>
+        <v>46191.781968599535</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>61</v>
@@ -2121,13 +2121,13 @@
         <v>63</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.37811188657</v>
+        <v>46097.544778553245</v>
       </c>
       <c r="D17" s="8">
-        <v>46097.37877938658</v>
+        <v>46097.54544605324</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>64</v>
@@ -2186,13 +2186,13 @@
         <v>66</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.66552304398</v>
+        <v>46079.83218971065</v>
       </c>
       <c r="C18" s="5">
-        <v>46191.6152715625</v>
+        <v>46191.781938229164</v>
       </c>
       <c r="D18" s="5">
-        <v>46191.6152905787</v>
+        <v>46191.78195724537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>67</v>
@@ -2251,13 +2251,13 @@
         <v>69</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C19" s="8">
-        <v>46191.61527736111</v>
+        <v>46191.78194402778</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.61529302083</v>
+        <v>46191.781959687505</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -2316,13 +2316,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66552032407</v>
+        <v>46079.83218699074</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3781387037</v>
+        <v>46097.54480537037</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.61084952546</v>
+        <v>46100.77751619213</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -2381,13 +2381,13 @@
         <v>78</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66552068287</v>
+        <v>46079.83218734954</v>
       </c>
       <c r="C21" s="8">
-        <v>46192.51416876157</v>
+        <v>46192.68083542824</v>
       </c>
       <c r="D21" s="8">
-        <v>46192.51418366898</v>
+        <v>46192.680850335644</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>79</v>
@@ -2434,13 +2434,13 @@
         <v>81</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C22" s="5">
-        <v>46191.61553530092</v>
+        <v>46191.782201967595</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.61554935185</v>
+        <v>46191.78221601852</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>82</v>
@@ -2499,13 +2499,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.66552123842</v>
+        <v>46079.83218790509</v>
       </c>
       <c r="C23" s="8">
-        <v>46191.61548202546</v>
+        <v>46191.78214869213</v>
       </c>
       <c r="D23" s="8">
-        <v>46191.61548420139</v>
+        <v>46191.78215086806</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -2560,13 +2560,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.665521504634</v>
+        <v>46079.83218817129</v>
       </c>
       <c r="C24" s="5">
-        <v>46191.61552018518</v>
+        <v>46191.78218685185</v>
       </c>
       <c r="D24" s="5">
-        <v>46191.615522314816</v>
+        <v>46191.78218898148</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -2619,13 +2619,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.66552247685</v>
+        <v>46079.83218914352</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.61546248842</v>
+        <v>46191.78212915509</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.615476886574</v>
+        <v>46191.78214355324</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -2684,13 +2684,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.66552270833</v>
+        <v>46079.832189374996</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.6154033912</v>
+        <v>46191.782070057874</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.61540471065</v>
+        <v>46191.78207137731</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -2745,13 +2745,13 @@
         <v>100</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.66552043981</v>
+        <v>46079.83218710648</v>
       </c>
       <c r="C27" s="8">
-        <v>46191.61544633102</v>
+        <v>46191.78211299768</v>
       </c>
       <c r="D27" s="8">
-        <v>46191.615447662036</v>
+        <v>46191.7821143287</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -2806,13 +2806,13 @@
         <v>103</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.665520787035</v>
+        <v>46079.83218745371</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.37891262732</v>
+        <v>46097.54557929398</v>
       </c>
       <c r="D28" s="5">
-        <v>46127.011858784725</v>
+        <v>46127.17852545139</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>104</v>
@@ -2871,13 +2871,13 @@
         <v>106</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.66552111111</v>
+        <v>46079.83218777778</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37881908564</v>
+        <v>46097.545485752315</v>
       </c>
       <c r="D29" s="8">
-        <v>46097.378820983795</v>
+        <v>46097.54548765047</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>107</v>
@@ -2932,13 +2932,13 @@
         <v>109</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.665521365736</v>
+        <v>46079.83218803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.378872685185</v>
+        <v>46097.54553935185</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.378873946756</v>
+        <v>46097.54554061343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>110</v>
@@ -2993,13 +2993,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.66552164352</v>
+        <v>46079.83218831019</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.37889787037</v>
+        <v>46097.54556453704</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.37889954861</v>
+        <v>46097.54556621528</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>113</v>
@@ -3054,13 +3054,13 @@
         <v>115</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.66552193287</v>
+        <v>46079.83218859954</v>
       </c>
       <c r="C32" s="5">
-        <v>46112.33927761574</v>
+        <v>46112.505944282406</v>
       </c>
       <c r="D32" s="5">
-        <v>46120.0064228588</v>
+        <v>46120.17308952546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>116</v>
@@ -3119,13 +3119,13 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66552219907</v>
+        <v>46079.83218886574</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.379011296296</v>
+        <v>46097.54567796296</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.379012881946</v>
+        <v>46097.54567954861</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3180,13 +3180,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C34" s="5">
-        <v>46112.34110125</v>
+        <v>46112.50776791667</v>
       </c>
       <c r="D34" s="5">
-        <v>46112.34110265046</v>
+        <v>46112.50776931713</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3241,11 +3241,11 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46127.52321417824</v>
+        <v>46127.689880844904</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3288,13 +3288,13 @@
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66552299769</v>
+        <v>46079.83218966435</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.350045196756</v>
+        <v>46114.51671186343</v>
       </c>
       <c r="D36" s="5">
-        <v>46127.522372928244</v>
+        <v>46127.68903959491</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3353,13 +3353,13 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C37" s="8">
-        <v>46127.52245238426</v>
+        <v>46127.68911905093</v>
       </c>
       <c r="D37" s="8">
-        <v>46127.52246925926</v>
+        <v>46127.689135925924</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -3418,13 +3418,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46087.607717962965</v>
+        <v>46087.77438462963</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.523203958335</v>
+        <v>46127.689870625</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.52323594908</v>
+        <v>46127.68990261574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3483,11 +3483,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.60831841435</v>
+        <v>46087.77498508102</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46196.73603752315</v>
+        <v>46196.902704189815</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3544,13 +3544,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.66552171296</v>
+        <v>46079.83218837963</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.61557571759</v>
+        <v>46191.78224238426</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.615588113425</v>
+        <v>46191.78225478009</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3597,13 +3597,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.66552199074</v>
+        <v>46079.83218865741</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.615561342594</v>
+        <v>46191.78222800926</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.61557621528</v>
+        <v>46191.78224288195</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3662,13 +3662,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.665522256946</v>
+        <v>46079.83218892361</v>
       </c>
       <c r="C42" s="5">
-        <v>46191.61518670139</v>
+        <v>46191.781853368055</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.61557498843</v>
+        <v>46191.78224165509</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3727,13 +3727,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.6655225463</v>
+        <v>46079.83218921296</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.61563753472</v>
+        <v>46191.78230420139</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.61565162037</v>
+        <v>46191.782318287034</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>162</v>
@@ -3780,13 +3780,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.66552283565</v>
+        <v>46079.83218950231</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.61557400463</v>
+        <v>46191.782240671295</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.615588472225</v>
+        <v>46191.78225513889</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3845,13 +3845,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.66552310185</v>
+        <v>46079.832189768524</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.61562164352</v>
+        <v>46191.78228831018</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.61563663195</v>
+        <v>46191.78230329861</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -3910,13 +3910,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.66552203704</v>
+        <v>46079.8321887037</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.61526960648</v>
+        <v>46191.78193627315</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.61564052083</v>
+        <v>46191.7823071875</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -3973,13 +3973,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.66552230324</v>
+        <v>46079.83218896991</v>
       </c>
       <c r="C47" s="8">
-        <v>46191.615784525464</v>
+        <v>46191.78245119213</v>
       </c>
       <c r="D47" s="8">
-        <v>46191.61579570602</v>
+        <v>46191.782462372685</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4026,13 +4026,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.66552256944</v>
+        <v>46079.83218923611</v>
       </c>
       <c r="C48" s="5">
-        <v>46191.61575009259</v>
+        <v>46191.78241675926</v>
       </c>
       <c r="D48" s="5">
-        <v>46191.61576581019</v>
+        <v>46191.78243247685</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4091,13 +4091,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.66552284722</v>
+        <v>46079.832189513894</v>
       </c>
       <c r="C49" s="8">
-        <v>46191.61576060185</v>
+        <v>46191.78242726852</v>
       </c>
       <c r="D49" s="8">
-        <v>46191.615777638886</v>
+        <v>46191.78244430556</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4156,13 +4156,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.66552311342</v>
+        <v>46079.83218978009</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.61576883102</v>
+        <v>46191.782435497684</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.61578528935</v>
+        <v>46191.78245195602</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4221,11 +4221,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46191.61594449074</v>
+        <v>46191.78261115741</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4270,13 +4270,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66552392361</v>
+        <v>46079.83219059028</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.6157175463</v>
+        <v>46191.78238421296</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.61573422454</v>
+        <v>46191.7824008912</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4335,13 +4335,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.61582453703</v>
+        <v>46191.7824912037</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.61584142361</v>
+        <v>46191.78250809028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4400,13 +4400,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.61592041666</v>
+        <v>46191.78258708333</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.615938449075</v>
+        <v>46191.78260511574</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4465,13 +4465,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.66552163195</v>
+        <v>46079.83218829861</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.61592672454</v>
+        <v>46191.7825933912</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.61594195601</v>
+        <v>46191.782608622685</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4530,13 +4530,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.43871371528</v>
+        <v>46193.605380381945</v>
       </c>
       <c r="D56" s="5">
-        <v>46193.439472812504</v>
+        <v>46193.60613947916</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>
@@ -4595,11 +4595,11 @@
         <v>207</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.6655221875</v>
+        <v>46079.83218885417</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46153.00153898148</v>
+        <v>46153.16820564815</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>208</v>
@@ -4656,11 +4656,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46087.61454869213</v>
+        <v>46087.781215358795</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4703,11 +4703,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46154.00127270834</v>
+        <v>46154.167939374995</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -4764,11 +4764,11 @@
         <v>215</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.665522986106</v>
+        <v>46079.83218965278</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.08375481481</v>
+        <v>46155.25042148148</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
@@ -4827,11 +4827,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.665523275464</v>
+        <v>46079.83218994213</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46193.39342828703</v>
+        <v>46193.560094953704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>219</v>
@@ -4888,11 +4888,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.66552355324</v>
+        <v>46079.83219021991</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46157.0839104051</v>
+        <v>46157.250577071754</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>222</v>
@@ -4951,11 +4951,11 @@
         <v>224</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66552094907</v>
+        <v>46079.83218761574</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.61454819444</v>
+        <v>46087.78121486111</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>225</v>
@@ -4998,11 +4998,11 @@
         <v>227</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66552170139</v>
+        <v>46079.832188368055</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46192.514117071754</v>
+        <v>46192.680783738426</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>228</v>
@@ -5061,11 +5061,11 @@
         <v>231</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.02214035879</v>
+        <v>46169.188807025464</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>232</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46196.902704189815</v>
+        <v>46197.90990825232</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4536,7 +4536,7 @@
         <v>46193.605380381945</v>
       </c>
       <c r="D56" s="5">
-        <v>46193.60613947916</v>
+        <v>46198.54290325231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1336,13 +1336,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.8321872338</v>
+        <v>46079.66552056713</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.715808587964</v>
+        <v>46092.54914192129</v>
       </c>
       <c r="D4" s="5">
-        <v>46159.00115726852</v>
+        <v>46158.83449060185</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1385,13 +1385,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.83218758102</v>
+        <v>46079.66552091435</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.715773125004</v>
+        <v>46092.54910645833</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.71580959491</v>
+        <v>46092.54914292824</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1450,13 +1450,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.832187824075</v>
+        <v>46079.66552115741</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.71577368055</v>
+        <v>46092.54910701389</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.715809120375</v>
+        <v>46092.5491424537</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1515,13 +1515,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.83218809028</v>
+        <v>46079.66552142361</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71577408565</v>
+        <v>46092.54910741898</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71580961805</v>
+        <v>46092.54914295139</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1580,13 +1580,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.83218834491</v>
+        <v>46079.66552167824</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71577445602</v>
+        <v>46092.54910778935</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.777120810184</v>
+        <v>46100.61045414352</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1645,13 +1645,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.83218858796</v>
+        <v>46079.6655219213</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71577509259</v>
+        <v>46092.54910842593</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71580994213</v>
+        <v>46092.549143275464</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1710,13 +1710,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.83218960648</v>
+        <v>46079.66552293982</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.559375868055</v>
+        <v>46193.39270920139</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.559412372684</v>
+        <v>46193.39274570602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1763,13 +1763,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.832187465276</v>
+        <v>46079.66552079861</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54453039352</v>
+        <v>46097.377863726855</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.680783703705</v>
+        <v>46192.51411703703</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1828,13 +1828,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.832187754626</v>
+        <v>46079.66552108796</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.781787141204</v>
+        <v>46191.61512047454</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.680783749995</v>
+        <v>46192.51411708334</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1893,13 +1893,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46114.51559517361</v>
+        <v>46114.348928506945</v>
       </c>
       <c r="C13" s="8">
-        <v>46191.78184763889</v>
+        <v>46191.61518097222</v>
       </c>
       <c r="D13" s="8">
-        <v>46191.781849074076</v>
+        <v>46191.615182407404</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -1948,13 +1948,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46114.5157486574</v>
+        <v>46114.349081990746</v>
       </c>
       <c r="C14" s="5">
-        <v>46191.78186625</v>
+        <v>46191.615199583335</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.781867453705</v>
+        <v>46191.61520078704</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2003,13 +2003,13 @@
         <v>57</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.83218810185</v>
+        <v>46079.665521435185</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.54473850694</v>
+        <v>46097.37807184028</v>
       </c>
       <c r="D15" s="8">
-        <v>46192.680783749995</v>
+        <v>46192.51411708334</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>58</v>
@@ -2068,13 +2068,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.83218881945</v>
+        <v>46079.665522152776</v>
       </c>
       <c r="C16" s="5">
-        <v>46191.78195586806</v>
+        <v>46191.61528920139</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.781968599535</v>
+        <v>46191.61530193287</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>61</v>
@@ -2121,13 +2121,13 @@
         <v>63</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.544778553245</v>
+        <v>46097.37811188657</v>
       </c>
       <c r="D17" s="8">
-        <v>46097.54544605324</v>
+        <v>46097.37877938658</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>64</v>
@@ -2186,13 +2186,13 @@
         <v>66</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.83218971065</v>
+        <v>46079.66552304398</v>
       </c>
       <c r="C18" s="5">
-        <v>46191.781938229164</v>
+        <v>46191.6152715625</v>
       </c>
       <c r="D18" s="5">
-        <v>46191.78195724537</v>
+        <v>46191.6152905787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>67</v>
@@ -2251,13 +2251,13 @@
         <v>69</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.8321903125</v>
+        <v>46079.66552364583</v>
       </c>
       <c r="C19" s="8">
-        <v>46191.78194402778</v>
+        <v>46191.61527736111</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.781959687505</v>
+        <v>46191.61529302083</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -2316,13 +2316,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.83218699074</v>
+        <v>46079.66552032407</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.54480537037</v>
+        <v>46097.3781387037</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.77751619213</v>
+        <v>46100.61084952546</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -2381,13 +2381,13 @@
         <v>78</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.83218734954</v>
+        <v>46079.66552068287</v>
       </c>
       <c r="C21" s="8">
-        <v>46192.68083542824</v>
+        <v>46192.51416876157</v>
       </c>
       <c r="D21" s="8">
-        <v>46192.680850335644</v>
+        <v>46192.51418366898</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>79</v>
@@ -2434,13 +2434,13 @@
         <v>81</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.832187673615</v>
+        <v>46079.665521006944</v>
       </c>
       <c r="C22" s="5">
-        <v>46191.782201967595</v>
+        <v>46191.61553530092</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.78221601852</v>
+        <v>46191.61554935185</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>82</v>
@@ -2499,13 +2499,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.83218790509</v>
+        <v>46079.66552123842</v>
       </c>
       <c r="C23" s="8">
-        <v>46191.78214869213</v>
+        <v>46191.61548202546</v>
       </c>
       <c r="D23" s="8">
-        <v>46191.78215086806</v>
+        <v>46191.61548420139</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -2560,13 +2560,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.83218817129</v>
+        <v>46079.665521504634</v>
       </c>
       <c r="C24" s="5">
-        <v>46191.78218685185</v>
+        <v>46191.61552018518</v>
       </c>
       <c r="D24" s="5">
-        <v>46191.78218898148</v>
+        <v>46191.615522314816</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -2619,13 +2619,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.83218914352</v>
+        <v>46079.66552247685</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.78212915509</v>
+        <v>46191.61546248842</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.78214355324</v>
+        <v>46191.615476886574</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -2684,13 +2684,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.832189374996</v>
+        <v>46079.66552270833</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.782070057874</v>
+        <v>46191.6154033912</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.78207137731</v>
+        <v>46191.61540471065</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -2745,13 +2745,13 @@
         <v>100</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.83218710648</v>
+        <v>46079.66552043981</v>
       </c>
       <c r="C27" s="8">
-        <v>46191.78211299768</v>
+        <v>46191.61544633102</v>
       </c>
       <c r="D27" s="8">
-        <v>46191.7821143287</v>
+        <v>46191.615447662036</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -2806,13 +2806,13 @@
         <v>103</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.83218745371</v>
+        <v>46079.665520787035</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.54557929398</v>
+        <v>46097.37891262732</v>
       </c>
       <c r="D28" s="5">
-        <v>46127.17852545139</v>
+        <v>46127.011858784725</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>104</v>
@@ -2871,13 +2871,13 @@
         <v>106</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.83218777778</v>
+        <v>46079.66552111111</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.545485752315</v>
+        <v>46097.37881908564</v>
       </c>
       <c r="D29" s="8">
-        <v>46097.54548765047</v>
+        <v>46097.378820983795</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>107</v>
@@ -2932,13 +2932,13 @@
         <v>109</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.83218803241</v>
+        <v>46079.665521365736</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.54553935185</v>
+        <v>46097.378872685185</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.54554061343</v>
+        <v>46097.378873946756</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>110</v>
@@ -2993,13 +2993,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.83218831019</v>
+        <v>46079.66552164352</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.54556453704</v>
+        <v>46097.37889787037</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.54556621528</v>
+        <v>46097.37889954861</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>113</v>
@@ -3054,13 +3054,13 @@
         <v>115</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.83218859954</v>
+        <v>46079.66552193287</v>
       </c>
       <c r="C32" s="5">
-        <v>46112.505944282406</v>
+        <v>46112.33927761574</v>
       </c>
       <c r="D32" s="5">
-        <v>46120.17308952546</v>
+        <v>46120.0064228588</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>116</v>
@@ -3119,13 +3119,13 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.83218886574</v>
+        <v>46079.66552219907</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.54567796296</v>
+        <v>46097.379011296296</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.54567954861</v>
+        <v>46097.379012881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3180,13 +3180,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.83218913194</v>
+        <v>46079.66552246528</v>
       </c>
       <c r="C34" s="5">
-        <v>46112.50776791667</v>
+        <v>46112.34110125</v>
       </c>
       <c r="D34" s="5">
-        <v>46112.50776931713</v>
+        <v>46112.34110265046</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3241,11 +3241,11 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46127.689880844904</v>
+        <v>46127.52321417824</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3288,13 +3288,13 @@
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.83218966435</v>
+        <v>46079.66552299769</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.51671186343</v>
+        <v>46114.350045196756</v>
       </c>
       <c r="D36" s="5">
-        <v>46127.68903959491</v>
+        <v>46127.522372928244</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3353,13 +3353,13 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C37" s="8">
-        <v>46127.68911905093</v>
+        <v>46127.52245238426</v>
       </c>
       <c r="D37" s="8">
-        <v>46127.689135925924</v>
+        <v>46127.52246925926</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -3418,13 +3418,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46087.77438462963</v>
+        <v>46087.607717962965</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.689870625</v>
+        <v>46127.523203958335</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.68990261574</v>
+        <v>46127.52323594908</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3483,11 +3483,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.77498508102</v>
+        <v>46087.60831841435</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46197.90990825232</v>
+        <v>46197.743241585646</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3544,13 +3544,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.83218837963</v>
+        <v>46079.66552171296</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.78224238426</v>
+        <v>46191.61557571759</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.78225478009</v>
+        <v>46191.615588113425</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3597,13 +3597,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.83218865741</v>
+        <v>46079.66552199074</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.78222800926</v>
+        <v>46191.615561342594</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.78224288195</v>
+        <v>46191.61557621528</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3662,13 +3662,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.83218892361</v>
+        <v>46079.665522256946</v>
       </c>
       <c r="C42" s="5">
-        <v>46191.781853368055</v>
+        <v>46191.61518670139</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.78224165509</v>
+        <v>46191.61557498843</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3727,13 +3727,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.83218921296</v>
+        <v>46079.6655225463</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.78230420139</v>
+        <v>46191.61563753472</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.782318287034</v>
+        <v>46191.61565162037</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>162</v>
@@ -3780,13 +3780,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.83218950231</v>
+        <v>46079.66552283565</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.782240671295</v>
+        <v>46191.61557400463</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.78225513889</v>
+        <v>46191.615588472225</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3845,13 +3845,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.832189768524</v>
+        <v>46079.66552310185</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.78228831018</v>
+        <v>46191.61562164352</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.78230329861</v>
+        <v>46191.61563663195</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -3910,13 +3910,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.8321887037</v>
+        <v>46079.66552203704</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.78193627315</v>
+        <v>46191.61526960648</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.7823071875</v>
+        <v>46191.61564052083</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -3973,13 +3973,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.83218896991</v>
+        <v>46079.66552230324</v>
       </c>
       <c r="C47" s="8">
-        <v>46191.78245119213</v>
+        <v>46191.615784525464</v>
       </c>
       <c r="D47" s="8">
-        <v>46191.782462372685</v>
+        <v>46191.61579570602</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4026,13 +4026,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.83218923611</v>
+        <v>46079.66552256944</v>
       </c>
       <c r="C48" s="5">
-        <v>46191.78241675926</v>
+        <v>46191.61575009259</v>
       </c>
       <c r="D48" s="5">
-        <v>46191.78243247685</v>
+        <v>46191.61576581019</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4091,13 +4091,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.832189513894</v>
+        <v>46079.66552284722</v>
       </c>
       <c r="C49" s="8">
-        <v>46191.78242726852</v>
+        <v>46191.61576060185</v>
       </c>
       <c r="D49" s="8">
-        <v>46191.78244430556</v>
+        <v>46191.615777638886</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4156,13 +4156,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.83218978009</v>
+        <v>46079.66552311342</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.782435497684</v>
+        <v>46191.61576883102</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.78245195602</v>
+        <v>46191.61578528935</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4221,11 +4221,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.8321903125</v>
+        <v>46079.66552364583</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46191.78261115741</v>
+        <v>46191.61594449074</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4270,13 +4270,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.83219059028</v>
+        <v>46079.66552392361</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.78238421296</v>
+        <v>46191.6157175463</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.7824008912</v>
+        <v>46191.61573422454</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4335,13 +4335,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.832187673615</v>
+        <v>46079.665521006944</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.7824912037</v>
+        <v>46191.61582453703</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.78250809028</v>
+        <v>46191.61584142361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4400,13 +4400,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.78258708333</v>
+        <v>46191.61592041666</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.78260511574</v>
+        <v>46191.615938449075</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4465,13 +4465,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.83218829861</v>
+        <v>46079.66552163195</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.7825933912</v>
+        <v>46191.61592672454</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.782608622685</v>
+        <v>46191.61594195601</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4530,13 +4530,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.83218858796</v>
+        <v>46079.6655219213</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.605380381945</v>
+        <v>46193.43871371528</v>
       </c>
       <c r="D56" s="5">
-        <v>46198.54290325231</v>
+        <v>46198.37623658565</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>
@@ -4595,11 +4595,11 @@
         <v>207</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.83218885417</v>
+        <v>46079.6655221875</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46153.16820564815</v>
+        <v>46153.00153898148</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>208</v>
@@ -4656,11 +4656,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.83218913194</v>
+        <v>46079.66552246528</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46087.781215358795</v>
+        <v>46087.61454869213</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4703,11 +4703,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46154.167939374995</v>
+        <v>46154.00127270834</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -4764,11 +4764,11 @@
         <v>215</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.83218965278</v>
+        <v>46079.665522986106</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.25042148148</v>
+        <v>46155.08375481481</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
@@ -4827,11 +4827,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.83218994213</v>
+        <v>46079.665523275464</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46193.560094953704</v>
+        <v>46193.39342828703</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>219</v>
@@ -4888,11 +4888,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.83219021991</v>
+        <v>46079.66552355324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46157.250577071754</v>
+        <v>46157.0839104051</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>222</v>
@@ -4951,11 +4951,11 @@
         <v>224</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.83218761574</v>
+        <v>46079.66552094907</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.78121486111</v>
+        <v>46087.61454819444</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>225</v>
@@ -4998,11 +4998,11 @@
         <v>227</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.832188368055</v>
+        <v>46079.66552170139</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46192.680783738426</v>
+        <v>46192.514117071754</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>228</v>
@@ -5061,11 +5061,11 @@
         <v>231</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.188807025464</v>
+        <v>46169.02214035879</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>232</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1336,13 +1336,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.66552056713</v>
+        <v>46079.8321872338</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54914192129</v>
+        <v>46092.715808587964</v>
       </c>
       <c r="D4" s="5">
-        <v>46158.83449060185</v>
+        <v>46159.00115726852</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1385,13 +1385,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66552091435</v>
+        <v>46079.83218758102</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54910645833</v>
+        <v>46092.715773125004</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.54914292824</v>
+        <v>46092.71580959491</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1450,13 +1450,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66552115741</v>
+        <v>46079.832187824075</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54910701389</v>
+        <v>46092.71577368055</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.5491424537</v>
+        <v>46092.715809120375</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1515,13 +1515,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66552142361</v>
+        <v>46079.83218809028</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54910741898</v>
+        <v>46092.71577408565</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54914295139</v>
+        <v>46092.71580961805</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1580,13 +1580,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66552167824</v>
+        <v>46079.83218834491</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.54910778935</v>
+        <v>46092.71577445602</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.61045414352</v>
+        <v>46100.777120810184</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1645,13 +1645,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54910842593</v>
+        <v>46092.71577509259</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.549143275464</v>
+        <v>46092.71580994213</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1710,13 +1710,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.66552293982</v>
+        <v>46079.83218960648</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.39270920139</v>
+        <v>46193.559375868055</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.39274570602</v>
+        <v>46193.559412372684</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1763,13 +1763,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66552079861</v>
+        <v>46079.832187465276</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.377863726855</v>
+        <v>46097.54453039352</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.51411703703</v>
+        <v>46192.680783703705</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1828,13 +1828,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66552108796</v>
+        <v>46079.832187754626</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.61512047454</v>
+        <v>46191.781787141204</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.51411708334</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1893,13 +1893,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46114.348928506945</v>
+        <v>46114.51559517361</v>
       </c>
       <c r="C13" s="8">
-        <v>46191.61518097222</v>
+        <v>46191.78184763889</v>
       </c>
       <c r="D13" s="8">
-        <v>46191.615182407404</v>
+        <v>46191.781849074076</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -1948,13 +1948,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46114.349081990746</v>
+        <v>46114.5157486574</v>
       </c>
       <c r="C14" s="5">
-        <v>46191.615199583335</v>
+        <v>46191.78186625</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.61520078704</v>
+        <v>46191.781867453705</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2003,13 +2003,13 @@
         <v>57</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.665521435185</v>
+        <v>46079.83218810185</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.37807184028</v>
+        <v>46097.54473850694</v>
       </c>
       <c r="D15" s="8">
-        <v>46192.51411708334</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>58</v>
@@ -2068,13 +2068,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.665522152776</v>
+        <v>46079.83218881945</v>
       </c>
       <c r="C16" s="5">
-        <v>46191.61528920139</v>
+        <v>46191.78195586806</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.61530193287</v>
+        <v>46191.781968599535</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>61</v>
@@ -2121,13 +2121,13 @@
         <v>63</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.37811188657</v>
+        <v>46097.544778553245</v>
       </c>
       <c r="D17" s="8">
-        <v>46097.37877938658</v>
+        <v>46097.54544605324</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>64</v>
@@ -2186,13 +2186,13 @@
         <v>66</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.66552304398</v>
+        <v>46079.83218971065</v>
       </c>
       <c r="C18" s="5">
-        <v>46191.6152715625</v>
+        <v>46191.781938229164</v>
       </c>
       <c r="D18" s="5">
-        <v>46191.6152905787</v>
+        <v>46191.78195724537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>67</v>
@@ -2251,13 +2251,13 @@
         <v>69</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C19" s="8">
-        <v>46191.61527736111</v>
+        <v>46191.78194402778</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.61529302083</v>
+        <v>46191.781959687505</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -2316,13 +2316,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66552032407</v>
+        <v>46079.83218699074</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3781387037</v>
+        <v>46097.54480537037</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.61084952546</v>
+        <v>46100.77751619213</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -2381,13 +2381,13 @@
         <v>78</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66552068287</v>
+        <v>46079.83218734954</v>
       </c>
       <c r="C21" s="8">
-        <v>46192.51416876157</v>
+        <v>46192.68083542824</v>
       </c>
       <c r="D21" s="8">
-        <v>46192.51418366898</v>
+        <v>46192.680850335644</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>79</v>
@@ -2434,13 +2434,13 @@
         <v>81</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C22" s="5">
-        <v>46191.61553530092</v>
+        <v>46191.782201967595</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.61554935185</v>
+        <v>46191.78221601852</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>82</v>
@@ -2499,13 +2499,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.66552123842</v>
+        <v>46079.83218790509</v>
       </c>
       <c r="C23" s="8">
-        <v>46191.61548202546</v>
+        <v>46191.78214869213</v>
       </c>
       <c r="D23" s="8">
-        <v>46191.61548420139</v>
+        <v>46191.78215086806</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -2560,13 +2560,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.665521504634</v>
+        <v>46079.83218817129</v>
       </c>
       <c r="C24" s="5">
-        <v>46191.61552018518</v>
+        <v>46191.78218685185</v>
       </c>
       <c r="D24" s="5">
-        <v>46191.615522314816</v>
+        <v>46191.78218898148</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -2619,13 +2619,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.66552247685</v>
+        <v>46079.83218914352</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.61546248842</v>
+        <v>46191.78212915509</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.615476886574</v>
+        <v>46191.78214355324</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -2684,13 +2684,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.66552270833</v>
+        <v>46079.832189374996</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.6154033912</v>
+        <v>46191.782070057874</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.61540471065</v>
+        <v>46191.78207137731</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -2745,13 +2745,13 @@
         <v>100</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.66552043981</v>
+        <v>46079.83218710648</v>
       </c>
       <c r="C27" s="8">
-        <v>46191.61544633102</v>
+        <v>46191.78211299768</v>
       </c>
       <c r="D27" s="8">
-        <v>46191.615447662036</v>
+        <v>46191.7821143287</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -2806,13 +2806,13 @@
         <v>103</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.665520787035</v>
+        <v>46079.83218745371</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.37891262732</v>
+        <v>46097.54557929398</v>
       </c>
       <c r="D28" s="5">
-        <v>46127.011858784725</v>
+        <v>46127.17852545139</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>104</v>
@@ -2871,13 +2871,13 @@
         <v>106</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.66552111111</v>
+        <v>46079.83218777778</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37881908564</v>
+        <v>46097.545485752315</v>
       </c>
       <c r="D29" s="8">
-        <v>46097.378820983795</v>
+        <v>46097.54548765047</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>107</v>
@@ -2932,13 +2932,13 @@
         <v>109</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.665521365736</v>
+        <v>46079.83218803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.378872685185</v>
+        <v>46097.54553935185</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.378873946756</v>
+        <v>46097.54554061343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>110</v>
@@ -2993,13 +2993,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.66552164352</v>
+        <v>46079.83218831019</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.37889787037</v>
+        <v>46097.54556453704</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.37889954861</v>
+        <v>46097.54556621528</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>113</v>
@@ -3054,13 +3054,13 @@
         <v>115</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.66552193287</v>
+        <v>46079.83218859954</v>
       </c>
       <c r="C32" s="5">
-        <v>46112.33927761574</v>
+        <v>46112.505944282406</v>
       </c>
       <c r="D32" s="5">
-        <v>46120.0064228588</v>
+        <v>46120.17308952546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>116</v>
@@ -3119,13 +3119,13 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66552219907</v>
+        <v>46079.83218886574</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.379011296296</v>
+        <v>46097.54567796296</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.379012881946</v>
+        <v>46097.54567954861</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3180,13 +3180,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C34" s="5">
-        <v>46112.34110125</v>
+        <v>46112.50776791667</v>
       </c>
       <c r="D34" s="5">
-        <v>46112.34110265046</v>
+        <v>46112.50776931713</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3241,11 +3241,11 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46127.52321417824</v>
+        <v>46127.689880844904</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3288,13 +3288,13 @@
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66552299769</v>
+        <v>46079.83218966435</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.350045196756</v>
+        <v>46114.51671186343</v>
       </c>
       <c r="D36" s="5">
-        <v>46127.522372928244</v>
+        <v>46127.68903959491</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3353,13 +3353,13 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C37" s="8">
-        <v>46127.52245238426</v>
+        <v>46127.68911905093</v>
       </c>
       <c r="D37" s="8">
-        <v>46127.52246925926</v>
+        <v>46127.689135925924</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -3418,13 +3418,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46087.607717962965</v>
+        <v>46087.77438462963</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.523203958335</v>
+        <v>46127.689870625</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.52323594908</v>
+        <v>46127.68990261574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3483,11 +3483,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.60831841435</v>
+        <v>46087.77498508102</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46197.743241585646</v>
+        <v>46197.90990825232</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3544,13 +3544,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.66552171296</v>
+        <v>46079.83218837963</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.61557571759</v>
+        <v>46191.78224238426</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.615588113425</v>
+        <v>46191.78225478009</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3597,13 +3597,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.66552199074</v>
+        <v>46079.83218865741</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.615561342594</v>
+        <v>46191.78222800926</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.61557621528</v>
+        <v>46191.78224288195</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3662,13 +3662,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.665522256946</v>
+        <v>46079.83218892361</v>
       </c>
       <c r="C42" s="5">
-        <v>46191.61518670139</v>
+        <v>46191.781853368055</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.61557498843</v>
+        <v>46191.78224165509</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3727,13 +3727,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.6655225463</v>
+        <v>46079.83218921296</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.61563753472</v>
+        <v>46191.78230420139</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.61565162037</v>
+        <v>46191.782318287034</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>162</v>
@@ -3780,13 +3780,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.66552283565</v>
+        <v>46079.83218950231</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.61557400463</v>
+        <v>46191.782240671295</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.615588472225</v>
+        <v>46191.78225513889</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3845,13 +3845,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.66552310185</v>
+        <v>46079.832189768524</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.61562164352</v>
+        <v>46191.78228831018</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.61563663195</v>
+        <v>46191.78230329861</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -3910,13 +3910,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.66552203704</v>
+        <v>46079.8321887037</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.61526960648</v>
+        <v>46191.78193627315</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.61564052083</v>
+        <v>46191.7823071875</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -3973,13 +3973,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.66552230324</v>
+        <v>46079.83218896991</v>
       </c>
       <c r="C47" s="8">
-        <v>46191.615784525464</v>
+        <v>46191.78245119213</v>
       </c>
       <c r="D47" s="8">
-        <v>46191.61579570602</v>
+        <v>46191.782462372685</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4026,13 +4026,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.66552256944</v>
+        <v>46079.83218923611</v>
       </c>
       <c r="C48" s="5">
-        <v>46191.61575009259</v>
+        <v>46191.78241675926</v>
       </c>
       <c r="D48" s="5">
-        <v>46191.61576581019</v>
+        <v>46191.78243247685</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4091,13 +4091,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.66552284722</v>
+        <v>46079.832189513894</v>
       </c>
       <c r="C49" s="8">
-        <v>46191.61576060185</v>
+        <v>46191.78242726852</v>
       </c>
       <c r="D49" s="8">
-        <v>46191.615777638886</v>
+        <v>46191.78244430556</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4156,13 +4156,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.66552311342</v>
+        <v>46079.83218978009</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.61576883102</v>
+        <v>46191.782435497684</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.61578528935</v>
+        <v>46191.78245195602</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4221,11 +4221,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46191.61594449074</v>
+        <v>46191.78261115741</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4270,13 +4270,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66552392361</v>
+        <v>46079.83219059028</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.6157175463</v>
+        <v>46191.78238421296</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.61573422454</v>
+        <v>46191.7824008912</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4335,13 +4335,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.61582453703</v>
+        <v>46191.7824912037</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.61584142361</v>
+        <v>46191.78250809028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4400,13 +4400,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.61592041666</v>
+        <v>46191.78258708333</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.615938449075</v>
+        <v>46191.78260511574</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4465,13 +4465,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.66552163195</v>
+        <v>46079.83218829861</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.61592672454</v>
+        <v>46191.7825933912</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.61594195601</v>
+        <v>46191.782608622685</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4530,13 +4530,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.43871371528</v>
+        <v>46193.605380381945</v>
       </c>
       <c r="D56" s="5">
-        <v>46198.37623658565</v>
+        <v>46198.54290325231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>
@@ -4595,11 +4595,11 @@
         <v>207</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.6655221875</v>
+        <v>46079.83218885417</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46153.00153898148</v>
+        <v>46153.16820564815</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>208</v>
@@ -4656,11 +4656,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46087.61454869213</v>
+        <v>46087.781215358795</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4703,11 +4703,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46154.00127270834</v>
+        <v>46154.167939374995</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -4764,11 +4764,11 @@
         <v>215</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.665522986106</v>
+        <v>46079.83218965278</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.08375481481</v>
+        <v>46155.25042148148</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
@@ -4827,11 +4827,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.665523275464</v>
+        <v>46079.83218994213</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46193.39342828703</v>
+        <v>46193.560094953704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>219</v>
@@ -4888,11 +4888,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.66552355324</v>
+        <v>46079.83219021991</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46157.0839104051</v>
+        <v>46157.250577071754</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>222</v>
@@ -4951,11 +4951,11 @@
         <v>224</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66552094907</v>
+        <v>46079.83218761574</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.61454819444</v>
+        <v>46087.78121486111</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>225</v>
@@ -4998,11 +4998,11 @@
         <v>227</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66552170139</v>
+        <v>46079.832188368055</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46192.514117071754</v>
+        <v>46192.680783738426</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>228</v>
@@ -5061,11 +5061,11 @@
         <v>231</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.02214035879</v>
+        <v>46169.188807025464</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>232</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="235">
   <si>
     <t>50001520 -  XEMORTIZ DDG</t>
   </si>
@@ -653,6 +653,12 @@
   </si>
   <si>
     <t>1213458939855366</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
   </si>
   <si>
     <t>Embalaje,Logistica:</t>
@@ -3243,9 +3249,11 @@
       <c r="B35" s="8">
         <v>46079.83218939815</v>
       </c>
-      <c r="C35" s="9"/>
+      <c r="C35" s="8">
+        <v>46204.70985539352</v>
+      </c>
       <c r="D35" s="8">
-        <v>46127.689880844904</v>
+        <v>46204.709868715276</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3279,9 +3287,13 @@
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
+      <c r="S35" s="9">
+        <v>1</v>
+      </c>
       <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
+      <c r="U35" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -3485,9 +3497,11 @@
       <c r="B39" s="8">
         <v>46087.77498508102</v>
       </c>
-      <c r="C39" s="9"/>
+      <c r="C39" s="8">
+        <v>46204.709836469905</v>
+      </c>
       <c r="D39" s="8">
-        <v>46197.90990825232</v>
+        <v>46204.710801249996</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3530,13 +3544,13 @@
         <v>46150</v>
       </c>
       <c r="S39" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="U39" s="12" t="s">
-        <v>120</v>
+      <c r="U39" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4599,7 +4613,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46153.16820564815</v>
+        <v>46204.70985621528</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>208</v>
@@ -4647,8 +4661,8 @@
       <c r="T57" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="U57" s="10" t="s">
-        <v>90</v>
+      <c r="U57" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4707,7 +4721,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46154.167939374995</v>
+        <v>46204.71238518519</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -4716,10 +4730,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>35</v>
+        <v>214</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>36</v>
+        <v>215</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -4741,7 +4755,7 @@
         <v>208</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q59" s="8">
         <v>46154</v>
@@ -4761,7 +4775,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83218965278</v>
@@ -4771,7 +4785,7 @@
         <v>46155.25042148148</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4804,7 +4818,7 @@
         <v>209</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q60" s="5">
         <v>46155</v>
@@ -4824,7 +4838,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B61" s="8">
         <v>46079.83218994213</v>
@@ -4834,7 +4848,7 @@
         <v>46193.560094953704</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -4862,10 +4876,10 @@
         <v>211</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="8">
         <v>46155</v>
@@ -4885,7 +4899,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46079.83219021991</v>
@@ -4895,7 +4909,7 @@
         <v>46157.250577071754</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4925,10 +4939,10 @@
         <v>211</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q62" s="5">
         <v>46157</v>
@@ -4948,7 +4962,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83218761574</v>
@@ -4958,7 +4972,7 @@
         <v>46087.78121486111</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -4982,7 +4996,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -4995,7 +5009,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46079.832188368055</v>
@@ -5005,16 +5019,16 @@
         <v>46192.680783738426</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I64" s="5">
         <v>46160</v>
@@ -5032,13 +5046,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="5">
         <v>46160</v>
@@ -5058,7 +5072,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B65" s="8">
         <v>46079.832188009255</v>
@@ -5068,16 +5082,16 @@
         <v>46169.188807025464</v>
       </c>
       <c r="E65" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="I65" s="8">
         <v>46160</v>
@@ -5095,13 +5109,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q65" s="8">
         <v>46160</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1342,13 +1342,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.8321872338</v>
+        <v>46079.66552056713</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.715808587964</v>
+        <v>46092.54914192129</v>
       </c>
       <c r="D4" s="5">
-        <v>46159.00115726852</v>
+        <v>46158.83449060185</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1391,13 +1391,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.83218758102</v>
+        <v>46079.66552091435</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.715773125004</v>
+        <v>46092.54910645833</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.71580959491</v>
+        <v>46092.54914292824</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1456,13 +1456,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.832187824075</v>
+        <v>46079.66552115741</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.71577368055</v>
+        <v>46092.54910701389</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.715809120375</v>
+        <v>46092.5491424537</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1521,13 +1521,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.83218809028</v>
+        <v>46079.66552142361</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71577408565</v>
+        <v>46092.54910741898</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71580961805</v>
+        <v>46092.54914295139</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1586,13 +1586,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.83218834491</v>
+        <v>46079.66552167824</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71577445602</v>
+        <v>46092.54910778935</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.777120810184</v>
+        <v>46100.61045414352</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1651,13 +1651,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.83218858796</v>
+        <v>46079.6655219213</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71577509259</v>
+        <v>46092.54910842593</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71580994213</v>
+        <v>46092.549143275464</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1716,13 +1716,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.83218960648</v>
+        <v>46079.66552293982</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.559375868055</v>
+        <v>46193.39270920139</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.559412372684</v>
+        <v>46193.39274570602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1769,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.832187465276</v>
+        <v>46079.66552079861</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54453039352</v>
+        <v>46097.377863726855</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.680783703705</v>
+        <v>46192.51411703703</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1834,13 +1834,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.832187754626</v>
+        <v>46079.66552108796</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.781787141204</v>
+        <v>46191.61512047454</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.680783749995</v>
+        <v>46192.51411708334</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1899,13 +1899,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46114.51559517361</v>
+        <v>46114.348928506945</v>
       </c>
       <c r="C13" s="8">
-        <v>46191.78184763889</v>
+        <v>46191.61518097222</v>
       </c>
       <c r="D13" s="8">
-        <v>46191.781849074076</v>
+        <v>46191.615182407404</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -1954,13 +1954,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46114.5157486574</v>
+        <v>46114.349081990746</v>
       </c>
       <c r="C14" s="5">
-        <v>46191.78186625</v>
+        <v>46191.615199583335</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.781867453705</v>
+        <v>46191.61520078704</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2009,13 +2009,13 @@
         <v>57</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.83218810185</v>
+        <v>46079.665521435185</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.54473850694</v>
+        <v>46097.37807184028</v>
       </c>
       <c r="D15" s="8">
-        <v>46192.680783749995</v>
+        <v>46192.51411708334</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>58</v>
@@ -2074,13 +2074,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.83218881945</v>
+        <v>46079.665522152776</v>
       </c>
       <c r="C16" s="5">
-        <v>46191.78195586806</v>
+        <v>46191.61528920139</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.781968599535</v>
+        <v>46191.61530193287</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>61</v>
@@ -2127,13 +2127,13 @@
         <v>63</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.544778553245</v>
+        <v>46097.37811188657</v>
       </c>
       <c r="D17" s="8">
-        <v>46097.54544605324</v>
+        <v>46097.37877938658</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>64</v>
@@ -2192,13 +2192,13 @@
         <v>66</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.83218971065</v>
+        <v>46079.66552304398</v>
       </c>
       <c r="C18" s="5">
-        <v>46191.781938229164</v>
+        <v>46191.6152715625</v>
       </c>
       <c r="D18" s="5">
-        <v>46191.78195724537</v>
+        <v>46191.6152905787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>67</v>
@@ -2257,13 +2257,13 @@
         <v>69</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.8321903125</v>
+        <v>46079.66552364583</v>
       </c>
       <c r="C19" s="8">
-        <v>46191.78194402778</v>
+        <v>46191.61527736111</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.781959687505</v>
+        <v>46191.61529302083</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -2322,13 +2322,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.83218699074</v>
+        <v>46079.66552032407</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.54480537037</v>
+        <v>46097.3781387037</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.77751619213</v>
+        <v>46100.61084952546</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -2387,13 +2387,13 @@
         <v>78</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.83218734954</v>
+        <v>46079.66552068287</v>
       </c>
       <c r="C21" s="8">
-        <v>46192.68083542824</v>
+        <v>46192.51416876157</v>
       </c>
       <c r="D21" s="8">
-        <v>46192.680850335644</v>
+        <v>46192.51418366898</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>79</v>
@@ -2440,13 +2440,13 @@
         <v>81</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.832187673615</v>
+        <v>46079.665521006944</v>
       </c>
       <c r="C22" s="5">
-        <v>46191.782201967595</v>
+        <v>46191.61553530092</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.78221601852</v>
+        <v>46191.61554935185</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>82</v>
@@ -2505,13 +2505,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.83218790509</v>
+        <v>46079.66552123842</v>
       </c>
       <c r="C23" s="8">
-        <v>46191.78214869213</v>
+        <v>46191.61548202546</v>
       </c>
       <c r="D23" s="8">
-        <v>46191.78215086806</v>
+        <v>46191.61548420139</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -2566,13 +2566,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.83218817129</v>
+        <v>46079.665521504634</v>
       </c>
       <c r="C24" s="5">
-        <v>46191.78218685185</v>
+        <v>46191.61552018518</v>
       </c>
       <c r="D24" s="5">
-        <v>46191.78218898148</v>
+        <v>46191.615522314816</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -2625,13 +2625,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.83218914352</v>
+        <v>46079.66552247685</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.78212915509</v>
+        <v>46191.61546248842</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.78214355324</v>
+        <v>46191.615476886574</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -2690,13 +2690,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.832189374996</v>
+        <v>46079.66552270833</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.782070057874</v>
+        <v>46191.6154033912</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.78207137731</v>
+        <v>46191.61540471065</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -2751,13 +2751,13 @@
         <v>100</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.83218710648</v>
+        <v>46079.66552043981</v>
       </c>
       <c r="C27" s="8">
-        <v>46191.78211299768</v>
+        <v>46191.61544633102</v>
       </c>
       <c r="D27" s="8">
-        <v>46191.7821143287</v>
+        <v>46191.615447662036</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -2812,13 +2812,13 @@
         <v>103</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.83218745371</v>
+        <v>46079.665520787035</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.54557929398</v>
+        <v>46097.37891262732</v>
       </c>
       <c r="D28" s="5">
-        <v>46127.17852545139</v>
+        <v>46127.011858784725</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>104</v>
@@ -2877,13 +2877,13 @@
         <v>106</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.83218777778</v>
+        <v>46079.66552111111</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.545485752315</v>
+        <v>46097.37881908564</v>
       </c>
       <c r="D29" s="8">
-        <v>46097.54548765047</v>
+        <v>46097.378820983795</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>107</v>
@@ -2938,13 +2938,13 @@
         <v>109</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.83218803241</v>
+        <v>46079.665521365736</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.54553935185</v>
+        <v>46097.378872685185</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.54554061343</v>
+        <v>46097.378873946756</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>110</v>
@@ -2999,13 +2999,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.83218831019</v>
+        <v>46079.66552164352</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.54556453704</v>
+        <v>46097.37889787037</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.54556621528</v>
+        <v>46097.37889954861</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>113</v>
@@ -3060,13 +3060,13 @@
         <v>115</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.83218859954</v>
+        <v>46079.66552193287</v>
       </c>
       <c r="C32" s="5">
-        <v>46112.505944282406</v>
+        <v>46112.33927761574</v>
       </c>
       <c r="D32" s="5">
-        <v>46120.17308952546</v>
+        <v>46120.0064228588</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>116</v>
@@ -3125,13 +3125,13 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.83218886574</v>
+        <v>46079.66552219907</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.54567796296</v>
+        <v>46097.379011296296</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.54567954861</v>
+        <v>46097.379012881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3186,13 +3186,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.83218913194</v>
+        <v>46079.66552246528</v>
       </c>
       <c r="C34" s="5">
-        <v>46112.50776791667</v>
+        <v>46112.34110125</v>
       </c>
       <c r="D34" s="5">
-        <v>46112.50776931713</v>
+        <v>46112.34110265046</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3247,13 +3247,13 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C35" s="8">
-        <v>46204.70985539352</v>
+        <v>46204.54318872685</v>
       </c>
       <c r="D35" s="8">
-        <v>46204.709868715276</v>
+        <v>46204.54320204861</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3300,13 +3300,13 @@
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.83218966435</v>
+        <v>46079.66552299769</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.51671186343</v>
+        <v>46114.350045196756</v>
       </c>
       <c r="D36" s="5">
-        <v>46127.68903959491</v>
+        <v>46127.522372928244</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3365,13 +3365,13 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C37" s="8">
-        <v>46127.68911905093</v>
+        <v>46127.52245238426</v>
       </c>
       <c r="D37" s="8">
-        <v>46127.689135925924</v>
+        <v>46127.52246925926</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -3430,13 +3430,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46087.77438462963</v>
+        <v>46087.607717962965</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.689870625</v>
+        <v>46127.523203958335</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.68990261574</v>
+        <v>46127.52323594908</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3495,13 +3495,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.77498508102</v>
+        <v>46087.60831841435</v>
       </c>
       <c r="C39" s="8">
-        <v>46204.709836469905</v>
+        <v>46204.54316980324</v>
       </c>
       <c r="D39" s="8">
-        <v>46204.710801249996</v>
+        <v>46204.54413458334</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3558,13 +3558,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.83218837963</v>
+        <v>46079.66552171296</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.78224238426</v>
+        <v>46191.61557571759</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.78225478009</v>
+        <v>46191.615588113425</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3611,13 +3611,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.83218865741</v>
+        <v>46079.66552199074</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.78222800926</v>
+        <v>46191.615561342594</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.78224288195</v>
+        <v>46191.61557621528</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3676,13 +3676,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.83218892361</v>
+        <v>46079.665522256946</v>
       </c>
       <c r="C42" s="5">
-        <v>46191.781853368055</v>
+        <v>46191.61518670139</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.78224165509</v>
+        <v>46191.61557498843</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3741,13 +3741,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.83218921296</v>
+        <v>46079.6655225463</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.78230420139</v>
+        <v>46191.61563753472</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.782318287034</v>
+        <v>46191.61565162037</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>162</v>
@@ -3794,13 +3794,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.83218950231</v>
+        <v>46079.66552283565</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.782240671295</v>
+        <v>46191.61557400463</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.78225513889</v>
+        <v>46191.615588472225</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3859,13 +3859,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.832189768524</v>
+        <v>46079.66552310185</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.78228831018</v>
+        <v>46191.61562164352</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.78230329861</v>
+        <v>46191.61563663195</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -3924,13 +3924,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.8321887037</v>
+        <v>46079.66552203704</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.78193627315</v>
+        <v>46191.61526960648</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.7823071875</v>
+        <v>46191.61564052083</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -3987,13 +3987,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.83218896991</v>
+        <v>46079.66552230324</v>
       </c>
       <c r="C47" s="8">
-        <v>46191.78245119213</v>
+        <v>46191.615784525464</v>
       </c>
       <c r="D47" s="8">
-        <v>46191.782462372685</v>
+        <v>46191.61579570602</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4040,13 +4040,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.83218923611</v>
+        <v>46079.66552256944</v>
       </c>
       <c r="C48" s="5">
-        <v>46191.78241675926</v>
+        <v>46191.61575009259</v>
       </c>
       <c r="D48" s="5">
-        <v>46191.78243247685</v>
+        <v>46191.61576581019</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4105,13 +4105,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.832189513894</v>
+        <v>46079.66552284722</v>
       </c>
       <c r="C49" s="8">
-        <v>46191.78242726852</v>
+        <v>46191.61576060185</v>
       </c>
       <c r="D49" s="8">
-        <v>46191.78244430556</v>
+        <v>46191.615777638886</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4170,13 +4170,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.83218978009</v>
+        <v>46079.66552311342</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.782435497684</v>
+        <v>46191.61576883102</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.78245195602</v>
+        <v>46191.61578528935</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4235,11 +4235,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.8321903125</v>
-      </c>
-      <c r="C51" s="9"/>
+        <v>46079.66552364583</v>
+      </c>
+      <c r="C51" s="8">
+        <v>46205.32093702546</v>
+      </c>
       <c r="D51" s="8">
-        <v>46191.78261115741</v>
+        <v>46205.32094751157</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4273,10 +4275,12 @@
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
+      <c r="S51" s="9">
+        <v>1</v>
+      </c>
       <c r="T51" s="9"/>
-      <c r="U51" s="12" t="s">
-        <v>120</v>
+      <c r="U51" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4284,13 +4288,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.83219059028</v>
+        <v>46079.66552392361</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.78238421296</v>
+        <v>46191.6157175463</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.7824008912</v>
+        <v>46191.61573422454</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4349,13 +4353,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.832187673615</v>
+        <v>46079.665521006944</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.7824912037</v>
+        <v>46191.61582453703</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.78250809028</v>
+        <v>46191.61584142361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4414,13 +4418,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.78258708333</v>
+        <v>46191.61592041666</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.78260511574</v>
+        <v>46191.615938449075</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4479,13 +4483,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.83218829861</v>
+        <v>46079.66552163195</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.7825933912</v>
+        <v>46191.61592672454</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.782608622685</v>
+        <v>46191.61594195601</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4544,13 +4548,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.83218858796</v>
+        <v>46079.6655219213</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.605380381945</v>
+        <v>46193.43871371528</v>
       </c>
       <c r="D56" s="5">
-        <v>46198.54290325231</v>
+        <v>46198.37623658565</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>
@@ -4609,11 +4613,13 @@
         <v>207</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.83218885417</v>
-      </c>
-      <c r="C57" s="9"/>
+        <v>46079.6655221875</v>
+      </c>
+      <c r="C57" s="8">
+        <v>46205.32091728009</v>
+      </c>
       <c r="D57" s="8">
-        <v>46204.70985621528</v>
+        <v>46205.32093765047</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>208</v>
@@ -4656,13 +4662,13 @@
         <v>46153</v>
       </c>
       <c r="S57" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="U57" s="12" t="s">
-        <v>120</v>
+      <c r="U57" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4670,11 +4676,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.83218913194</v>
+        <v>46079.66552246528</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46087.781215358795</v>
+        <v>46087.61454869213</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4717,11 +4723,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46204.71238518519</v>
+        <v>46205.32093498843</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -4769,8 +4775,8 @@
       <c r="T59" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="U59" s="10" t="s">
-        <v>90</v>
+      <c r="U59" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4778,11 +4784,11 @@
         <v>217</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.83218965278</v>
+        <v>46079.665522986106</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.25042148148</v>
+        <v>46155.08375481481</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -4841,11 +4847,11 @@
         <v>220</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.83218994213</v>
+        <v>46079.665523275464</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46193.560094953704</v>
+        <v>46193.39342828703</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>221</v>
@@ -4902,11 +4908,11 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.83219021991</v>
+        <v>46079.66552355324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46157.250577071754</v>
+        <v>46157.0839104051</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -4965,11 +4971,11 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.83218761574</v>
+        <v>46079.66552094907</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.78121486111</v>
+        <v>46087.61454819444</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5012,11 +5018,11 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.832188368055</v>
+        <v>46079.66552170139</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46192.680783738426</v>
+        <v>46192.514117071754</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5075,11 +5081,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.188807025464</v>
+        <v>46169.02214035879</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1342,13 +1342,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.66552056713</v>
+        <v>46079.8321872338</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54914192129</v>
+        <v>46092.715808587964</v>
       </c>
       <c r="D4" s="5">
-        <v>46158.83449060185</v>
+        <v>46159.00115726852</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1391,13 +1391,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66552091435</v>
+        <v>46079.83218758102</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54910645833</v>
+        <v>46092.715773125004</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.54914292824</v>
+        <v>46092.71580959491</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1456,13 +1456,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66552115741</v>
+        <v>46079.832187824075</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54910701389</v>
+        <v>46092.71577368055</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.5491424537</v>
+        <v>46092.715809120375</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1521,13 +1521,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66552142361</v>
+        <v>46079.83218809028</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54910741898</v>
+        <v>46092.71577408565</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54914295139</v>
+        <v>46092.71580961805</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1586,13 +1586,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66552167824</v>
+        <v>46079.83218834491</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.54910778935</v>
+        <v>46092.71577445602</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.61045414352</v>
+        <v>46100.777120810184</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1651,13 +1651,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54910842593</v>
+        <v>46092.71577509259</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.549143275464</v>
+        <v>46092.71580994213</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1716,13 +1716,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.66552293982</v>
+        <v>46079.83218960648</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.39270920139</v>
+        <v>46193.559375868055</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.39274570602</v>
+        <v>46193.559412372684</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1769,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66552079861</v>
+        <v>46079.832187465276</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.377863726855</v>
+        <v>46097.54453039352</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.51411703703</v>
+        <v>46192.680783703705</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1834,13 +1834,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66552108796</v>
+        <v>46079.832187754626</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.61512047454</v>
+        <v>46191.781787141204</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.51411708334</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1899,13 +1899,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46114.348928506945</v>
+        <v>46114.51559517361</v>
       </c>
       <c r="C13" s="8">
-        <v>46191.61518097222</v>
+        <v>46191.78184763889</v>
       </c>
       <c r="D13" s="8">
-        <v>46191.615182407404</v>
+        <v>46191.781849074076</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -1954,13 +1954,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46114.349081990746</v>
+        <v>46114.5157486574</v>
       </c>
       <c r="C14" s="5">
-        <v>46191.615199583335</v>
+        <v>46191.78186625</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.61520078704</v>
+        <v>46191.781867453705</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2009,13 +2009,13 @@
         <v>57</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.665521435185</v>
+        <v>46079.83218810185</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.37807184028</v>
+        <v>46097.54473850694</v>
       </c>
       <c r="D15" s="8">
-        <v>46192.51411708334</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>58</v>
@@ -2074,13 +2074,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.665522152776</v>
+        <v>46079.83218881945</v>
       </c>
       <c r="C16" s="5">
-        <v>46191.61528920139</v>
+        <v>46191.78195586806</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.61530193287</v>
+        <v>46191.781968599535</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>61</v>
@@ -2127,13 +2127,13 @@
         <v>63</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.37811188657</v>
+        <v>46097.544778553245</v>
       </c>
       <c r="D17" s="8">
-        <v>46097.37877938658</v>
+        <v>46097.54544605324</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>64</v>
@@ -2192,13 +2192,13 @@
         <v>66</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.66552304398</v>
+        <v>46079.83218971065</v>
       </c>
       <c r="C18" s="5">
-        <v>46191.6152715625</v>
+        <v>46191.781938229164</v>
       </c>
       <c r="D18" s="5">
-        <v>46191.6152905787</v>
+        <v>46191.78195724537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>67</v>
@@ -2257,13 +2257,13 @@
         <v>69</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C19" s="8">
-        <v>46191.61527736111</v>
+        <v>46191.78194402778</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.61529302083</v>
+        <v>46191.781959687505</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -2322,13 +2322,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66552032407</v>
+        <v>46079.83218699074</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3781387037</v>
+        <v>46097.54480537037</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.61084952546</v>
+        <v>46100.77751619213</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -2387,13 +2387,13 @@
         <v>78</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66552068287</v>
+        <v>46079.83218734954</v>
       </c>
       <c r="C21" s="8">
-        <v>46192.51416876157</v>
+        <v>46192.68083542824</v>
       </c>
       <c r="D21" s="8">
-        <v>46192.51418366898</v>
+        <v>46192.680850335644</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>79</v>
@@ -2440,13 +2440,13 @@
         <v>81</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C22" s="5">
-        <v>46191.61553530092</v>
+        <v>46191.782201967595</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.61554935185</v>
+        <v>46191.78221601852</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>82</v>
@@ -2505,13 +2505,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.66552123842</v>
+        <v>46079.83218790509</v>
       </c>
       <c r="C23" s="8">
-        <v>46191.61548202546</v>
+        <v>46191.78214869213</v>
       </c>
       <c r="D23" s="8">
-        <v>46191.61548420139</v>
+        <v>46191.78215086806</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -2566,13 +2566,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.665521504634</v>
+        <v>46079.83218817129</v>
       </c>
       <c r="C24" s="5">
-        <v>46191.61552018518</v>
+        <v>46191.78218685185</v>
       </c>
       <c r="D24" s="5">
-        <v>46191.615522314816</v>
+        <v>46191.78218898148</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -2625,13 +2625,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.66552247685</v>
+        <v>46079.83218914352</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.61546248842</v>
+        <v>46191.78212915509</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.615476886574</v>
+        <v>46191.78214355324</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -2690,13 +2690,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.66552270833</v>
+        <v>46079.832189374996</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.6154033912</v>
+        <v>46191.782070057874</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.61540471065</v>
+        <v>46191.78207137731</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -2751,13 +2751,13 @@
         <v>100</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.66552043981</v>
+        <v>46079.83218710648</v>
       </c>
       <c r="C27" s="8">
-        <v>46191.61544633102</v>
+        <v>46191.78211299768</v>
       </c>
       <c r="D27" s="8">
-        <v>46191.615447662036</v>
+        <v>46191.7821143287</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -2812,13 +2812,13 @@
         <v>103</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.665520787035</v>
+        <v>46079.83218745371</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.37891262732</v>
+        <v>46097.54557929398</v>
       </c>
       <c r="D28" s="5">
-        <v>46127.011858784725</v>
+        <v>46127.17852545139</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>104</v>
@@ -2877,13 +2877,13 @@
         <v>106</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.66552111111</v>
+        <v>46079.83218777778</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37881908564</v>
+        <v>46097.545485752315</v>
       </c>
       <c r="D29" s="8">
-        <v>46097.378820983795</v>
+        <v>46097.54548765047</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>107</v>
@@ -2938,13 +2938,13 @@
         <v>109</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.665521365736</v>
+        <v>46079.83218803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.378872685185</v>
+        <v>46097.54553935185</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.378873946756</v>
+        <v>46097.54554061343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>110</v>
@@ -2999,13 +2999,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.66552164352</v>
+        <v>46079.83218831019</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.37889787037</v>
+        <v>46097.54556453704</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.37889954861</v>
+        <v>46097.54556621528</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>113</v>
@@ -3060,13 +3060,13 @@
         <v>115</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.66552193287</v>
+        <v>46079.83218859954</v>
       </c>
       <c r="C32" s="5">
-        <v>46112.33927761574</v>
+        <v>46112.505944282406</v>
       </c>
       <c r="D32" s="5">
-        <v>46120.0064228588</v>
+        <v>46120.17308952546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>116</v>
@@ -3125,13 +3125,13 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66552219907</v>
+        <v>46079.83218886574</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.379011296296</v>
+        <v>46097.54567796296</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.379012881946</v>
+        <v>46097.54567954861</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3186,13 +3186,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C34" s="5">
-        <v>46112.34110125</v>
+        <v>46112.50776791667</v>
       </c>
       <c r="D34" s="5">
-        <v>46112.34110265046</v>
+        <v>46112.50776931713</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3247,13 +3247,13 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C35" s="8">
-        <v>46204.54318872685</v>
+        <v>46204.70985539352</v>
       </c>
       <c r="D35" s="8">
-        <v>46204.54320204861</v>
+        <v>46204.709868715276</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3300,13 +3300,13 @@
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66552299769</v>
+        <v>46079.83218966435</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.350045196756</v>
+        <v>46114.51671186343</v>
       </c>
       <c r="D36" s="5">
-        <v>46127.522372928244</v>
+        <v>46127.68903959491</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3365,13 +3365,13 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C37" s="8">
-        <v>46127.52245238426</v>
+        <v>46127.68911905093</v>
       </c>
       <c r="D37" s="8">
-        <v>46127.52246925926</v>
+        <v>46127.689135925924</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -3430,13 +3430,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46087.607717962965</v>
+        <v>46087.77438462963</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.523203958335</v>
+        <v>46127.689870625</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.52323594908</v>
+        <v>46127.68990261574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3495,13 +3495,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.60831841435</v>
+        <v>46087.77498508102</v>
       </c>
       <c r="C39" s="8">
-        <v>46204.54316980324</v>
+        <v>46204.709836469905</v>
       </c>
       <c r="D39" s="8">
-        <v>46204.54413458334</v>
+        <v>46204.710801249996</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3558,13 +3558,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.66552171296</v>
+        <v>46079.83218837963</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.61557571759</v>
+        <v>46191.78224238426</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.615588113425</v>
+        <v>46191.78225478009</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3611,13 +3611,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.66552199074</v>
+        <v>46079.83218865741</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.615561342594</v>
+        <v>46191.78222800926</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.61557621528</v>
+        <v>46191.78224288195</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3676,13 +3676,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.665522256946</v>
+        <v>46079.83218892361</v>
       </c>
       <c r="C42" s="5">
-        <v>46191.61518670139</v>
+        <v>46191.781853368055</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.61557498843</v>
+        <v>46191.78224165509</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3741,13 +3741,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.6655225463</v>
+        <v>46079.83218921296</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.61563753472</v>
+        <v>46191.78230420139</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.61565162037</v>
+        <v>46191.782318287034</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>162</v>
@@ -3794,13 +3794,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.66552283565</v>
+        <v>46079.83218950231</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.61557400463</v>
+        <v>46191.782240671295</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.615588472225</v>
+        <v>46191.78225513889</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3859,13 +3859,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.66552310185</v>
+        <v>46079.832189768524</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.61562164352</v>
+        <v>46191.78228831018</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.61563663195</v>
+        <v>46191.78230329861</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -3924,13 +3924,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.66552203704</v>
+        <v>46079.8321887037</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.61526960648</v>
+        <v>46191.78193627315</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.61564052083</v>
+        <v>46191.7823071875</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -3987,13 +3987,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.66552230324</v>
+        <v>46079.83218896991</v>
       </c>
       <c r="C47" s="8">
-        <v>46191.615784525464</v>
+        <v>46191.78245119213</v>
       </c>
       <c r="D47" s="8">
-        <v>46191.61579570602</v>
+        <v>46191.782462372685</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4040,13 +4040,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.66552256944</v>
+        <v>46079.83218923611</v>
       </c>
       <c r="C48" s="5">
-        <v>46191.61575009259</v>
+        <v>46191.78241675926</v>
       </c>
       <c r="D48" s="5">
-        <v>46191.61576581019</v>
+        <v>46191.78243247685</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4105,13 +4105,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.66552284722</v>
+        <v>46079.832189513894</v>
       </c>
       <c r="C49" s="8">
-        <v>46191.61576060185</v>
+        <v>46191.78242726852</v>
       </c>
       <c r="D49" s="8">
-        <v>46191.615777638886</v>
+        <v>46191.78244430556</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4170,13 +4170,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.66552311342</v>
+        <v>46079.83218978009</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.61576883102</v>
+        <v>46191.782435497684</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.61578528935</v>
+        <v>46191.78245195602</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4235,13 +4235,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C51" s="8">
-        <v>46205.32093702546</v>
+        <v>46205.487603692134</v>
       </c>
       <c r="D51" s="8">
-        <v>46205.32094751157</v>
+        <v>46205.487614178244</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4288,13 +4288,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66552392361</v>
+        <v>46079.83219059028</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.6157175463</v>
+        <v>46191.78238421296</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.61573422454</v>
+        <v>46191.7824008912</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4353,13 +4353,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.61582453703</v>
+        <v>46191.7824912037</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.61584142361</v>
+        <v>46191.78250809028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4418,13 +4418,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.61592041666</v>
+        <v>46191.78258708333</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.615938449075</v>
+        <v>46191.78260511574</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4483,13 +4483,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.66552163195</v>
+        <v>46079.83218829861</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.61592672454</v>
+        <v>46191.7825933912</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.61594195601</v>
+        <v>46191.782608622685</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4548,13 +4548,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.43871371528</v>
+        <v>46193.605380381945</v>
       </c>
       <c r="D56" s="5">
-        <v>46198.37623658565</v>
+        <v>46198.54290325231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>
@@ -4613,13 +4613,13 @@
         <v>207</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.6655221875</v>
+        <v>46079.83218885417</v>
       </c>
       <c r="C57" s="8">
-        <v>46205.32091728009</v>
+        <v>46205.48758394676</v>
       </c>
       <c r="D57" s="8">
-        <v>46205.32093765047</v>
+        <v>46205.487604317124</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>208</v>
@@ -4676,11 +4676,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46087.61454869213</v>
+        <v>46087.781215358795</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4723,11 +4723,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46205.32093498843</v>
+        <v>46205.48760165509</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -4784,11 +4784,11 @@
         <v>217</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.665522986106</v>
+        <v>46079.83218965278</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.08375481481</v>
+        <v>46155.25042148148</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -4847,11 +4847,11 @@
         <v>220</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.665523275464</v>
+        <v>46079.83218994213</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46193.39342828703</v>
+        <v>46193.560094953704</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>221</v>
@@ -4908,11 +4908,11 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.66552355324</v>
+        <v>46079.83219021991</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46157.0839104051</v>
+        <v>46157.250577071754</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -4971,11 +4971,11 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66552094907</v>
+        <v>46079.83218761574</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.61454819444</v>
+        <v>46087.78121486111</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5018,11 +5018,11 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66552170139</v>
+        <v>46079.832188368055</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46192.514117071754</v>
+        <v>46192.680783738426</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5081,11 +5081,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.02214035879</v>
+        <v>46169.188807025464</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46193.560094953704</v>
+        <v>46205.90231046296</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>221</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46087.781215358795</v>
+        <v>46205.915604953705</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4849,9 +4849,11 @@
       <c r="B61" s="8">
         <v>46079.83218994213</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="8">
+        <v>46205.91559434027</v>
+      </c>
       <c r="D61" s="8">
-        <v>46205.90231046296</v>
+        <v>46205.91561125</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>221</v>
@@ -4894,13 +4896,13 @@
         <v>46155</v>
       </c>
       <c r="S61" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="U61" s="10" t="s">
-        <v>90</v>
+      <c r="U61" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -4912,7 +4914,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46157.250577071754</v>
+        <v>46205.91561136574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -4962,8 +4964,8 @@
       <c r="T62" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="U62" s="10" t="s">
-        <v>90</v>
+      <c r="U62" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1342,13 +1342,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.8321872338</v>
+        <v>46079.66552056713</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.715808587964</v>
+        <v>46092.54914192129</v>
       </c>
       <c r="D4" s="5">
-        <v>46159.00115726852</v>
+        <v>46158.83449060185</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1391,13 +1391,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.83218758102</v>
+        <v>46079.66552091435</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.715773125004</v>
+        <v>46092.54910645833</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.71580959491</v>
+        <v>46092.54914292824</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1456,13 +1456,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.832187824075</v>
+        <v>46079.66552115741</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.71577368055</v>
+        <v>46092.54910701389</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.715809120375</v>
+        <v>46092.5491424537</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1521,13 +1521,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.83218809028</v>
+        <v>46079.66552142361</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71577408565</v>
+        <v>46092.54910741898</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71580961805</v>
+        <v>46092.54914295139</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1586,13 +1586,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.83218834491</v>
+        <v>46079.66552167824</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71577445602</v>
+        <v>46092.54910778935</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.777120810184</v>
+        <v>46100.61045414352</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1651,13 +1651,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.83218858796</v>
+        <v>46079.6655219213</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71577509259</v>
+        <v>46092.54910842593</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71580994213</v>
+        <v>46092.549143275464</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1716,13 +1716,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.83218960648</v>
+        <v>46079.66552293982</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.559375868055</v>
+        <v>46193.39270920139</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.559412372684</v>
+        <v>46193.39274570602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1769,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.832187465276</v>
+        <v>46079.66552079861</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54453039352</v>
+        <v>46097.377863726855</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.680783703705</v>
+        <v>46192.51411703703</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1834,13 +1834,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.832187754626</v>
+        <v>46079.66552108796</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.781787141204</v>
+        <v>46191.61512047454</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.680783749995</v>
+        <v>46192.51411708334</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1899,13 +1899,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46114.51559517361</v>
+        <v>46114.348928506945</v>
       </c>
       <c r="C13" s="8">
-        <v>46191.78184763889</v>
+        <v>46191.61518097222</v>
       </c>
       <c r="D13" s="8">
-        <v>46191.781849074076</v>
+        <v>46191.615182407404</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -1954,13 +1954,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46114.5157486574</v>
+        <v>46114.349081990746</v>
       </c>
       <c r="C14" s="5">
-        <v>46191.78186625</v>
+        <v>46191.615199583335</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.781867453705</v>
+        <v>46191.61520078704</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2009,13 +2009,13 @@
         <v>57</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.83218810185</v>
+        <v>46079.665521435185</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.54473850694</v>
+        <v>46097.37807184028</v>
       </c>
       <c r="D15" s="8">
-        <v>46192.680783749995</v>
+        <v>46192.51411708334</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>58</v>
@@ -2074,13 +2074,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.83218881945</v>
+        <v>46079.665522152776</v>
       </c>
       <c r="C16" s="5">
-        <v>46191.78195586806</v>
+        <v>46191.61528920139</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.781968599535</v>
+        <v>46191.61530193287</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>61</v>
@@ -2127,13 +2127,13 @@
         <v>63</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.544778553245</v>
+        <v>46097.37811188657</v>
       </c>
       <c r="D17" s="8">
-        <v>46097.54544605324</v>
+        <v>46097.37877938658</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>64</v>
@@ -2192,13 +2192,13 @@
         <v>66</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.83218971065</v>
+        <v>46079.66552304398</v>
       </c>
       <c r="C18" s="5">
-        <v>46191.781938229164</v>
+        <v>46191.6152715625</v>
       </c>
       <c r="D18" s="5">
-        <v>46191.78195724537</v>
+        <v>46191.6152905787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>67</v>
@@ -2257,13 +2257,13 @@
         <v>69</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.8321903125</v>
+        <v>46079.66552364583</v>
       </c>
       <c r="C19" s="8">
-        <v>46191.78194402778</v>
+        <v>46191.61527736111</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.781959687505</v>
+        <v>46191.61529302083</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -2322,13 +2322,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.83218699074</v>
+        <v>46079.66552032407</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.54480537037</v>
+        <v>46097.3781387037</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.77751619213</v>
+        <v>46100.61084952546</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -2387,13 +2387,13 @@
         <v>78</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.83218734954</v>
+        <v>46079.66552068287</v>
       </c>
       <c r="C21" s="8">
-        <v>46192.68083542824</v>
+        <v>46192.51416876157</v>
       </c>
       <c r="D21" s="8">
-        <v>46192.680850335644</v>
+        <v>46192.51418366898</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>79</v>
@@ -2440,13 +2440,13 @@
         <v>81</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.832187673615</v>
+        <v>46079.665521006944</v>
       </c>
       <c r="C22" s="5">
-        <v>46191.782201967595</v>
+        <v>46191.61553530092</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.78221601852</v>
+        <v>46191.61554935185</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>82</v>
@@ -2505,13 +2505,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.83218790509</v>
+        <v>46079.66552123842</v>
       </c>
       <c r="C23" s="8">
-        <v>46191.78214869213</v>
+        <v>46191.61548202546</v>
       </c>
       <c r="D23" s="8">
-        <v>46191.78215086806</v>
+        <v>46191.61548420139</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -2566,13 +2566,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.83218817129</v>
+        <v>46079.665521504634</v>
       </c>
       <c r="C24" s="5">
-        <v>46191.78218685185</v>
+        <v>46191.61552018518</v>
       </c>
       <c r="D24" s="5">
-        <v>46191.78218898148</v>
+        <v>46191.615522314816</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -2625,13 +2625,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.83218914352</v>
+        <v>46079.66552247685</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.78212915509</v>
+        <v>46191.61546248842</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.78214355324</v>
+        <v>46191.615476886574</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -2690,13 +2690,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.832189374996</v>
+        <v>46079.66552270833</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.782070057874</v>
+        <v>46191.6154033912</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.78207137731</v>
+        <v>46191.61540471065</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -2751,13 +2751,13 @@
         <v>100</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.83218710648</v>
+        <v>46079.66552043981</v>
       </c>
       <c r="C27" s="8">
-        <v>46191.78211299768</v>
+        <v>46191.61544633102</v>
       </c>
       <c r="D27" s="8">
-        <v>46191.7821143287</v>
+        <v>46191.615447662036</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -2812,13 +2812,13 @@
         <v>103</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.83218745371</v>
+        <v>46079.665520787035</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.54557929398</v>
+        <v>46097.37891262732</v>
       </c>
       <c r="D28" s="5">
-        <v>46127.17852545139</v>
+        <v>46127.011858784725</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>104</v>
@@ -2877,13 +2877,13 @@
         <v>106</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.83218777778</v>
+        <v>46079.66552111111</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.545485752315</v>
+        <v>46097.37881908564</v>
       </c>
       <c r="D29" s="8">
-        <v>46097.54548765047</v>
+        <v>46097.378820983795</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>107</v>
@@ -2938,13 +2938,13 @@
         <v>109</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.83218803241</v>
+        <v>46079.665521365736</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.54553935185</v>
+        <v>46097.378872685185</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.54554061343</v>
+        <v>46097.378873946756</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>110</v>
@@ -2999,13 +2999,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.83218831019</v>
+        <v>46079.66552164352</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.54556453704</v>
+        <v>46097.37889787037</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.54556621528</v>
+        <v>46097.37889954861</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>113</v>
@@ -3060,13 +3060,13 @@
         <v>115</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.83218859954</v>
+        <v>46079.66552193287</v>
       </c>
       <c r="C32" s="5">
-        <v>46112.505944282406</v>
+        <v>46112.33927761574</v>
       </c>
       <c r="D32" s="5">
-        <v>46120.17308952546</v>
+        <v>46120.0064228588</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>116</v>
@@ -3125,13 +3125,13 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.83218886574</v>
+        <v>46079.66552219907</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.54567796296</v>
+        <v>46097.379011296296</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.54567954861</v>
+        <v>46097.379012881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3186,13 +3186,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.83218913194</v>
+        <v>46079.66552246528</v>
       </c>
       <c r="C34" s="5">
-        <v>46112.50776791667</v>
+        <v>46112.34110125</v>
       </c>
       <c r="D34" s="5">
-        <v>46112.50776931713</v>
+        <v>46112.34110265046</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3247,13 +3247,13 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C35" s="8">
-        <v>46204.70985539352</v>
+        <v>46204.54318872685</v>
       </c>
       <c r="D35" s="8">
-        <v>46204.709868715276</v>
+        <v>46204.54320204861</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3300,13 +3300,13 @@
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.83218966435</v>
+        <v>46079.66552299769</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.51671186343</v>
+        <v>46114.350045196756</v>
       </c>
       <c r="D36" s="5">
-        <v>46127.68903959491</v>
+        <v>46127.522372928244</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3365,13 +3365,13 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C37" s="8">
-        <v>46127.68911905093</v>
+        <v>46127.52245238426</v>
       </c>
       <c r="D37" s="8">
-        <v>46127.689135925924</v>
+        <v>46127.52246925926</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -3430,13 +3430,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46087.77438462963</v>
+        <v>46087.607717962965</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.689870625</v>
+        <v>46127.523203958335</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.68990261574</v>
+        <v>46127.52323594908</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3495,13 +3495,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.77498508102</v>
+        <v>46087.60831841435</v>
       </c>
       <c r="C39" s="8">
-        <v>46204.709836469905</v>
+        <v>46204.54316980324</v>
       </c>
       <c r="D39" s="8">
-        <v>46204.710801249996</v>
+        <v>46204.54413458334</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3558,13 +3558,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.83218837963</v>
+        <v>46079.66552171296</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.78224238426</v>
+        <v>46191.61557571759</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.78225478009</v>
+        <v>46191.615588113425</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3611,13 +3611,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.83218865741</v>
+        <v>46079.66552199074</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.78222800926</v>
+        <v>46191.615561342594</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.78224288195</v>
+        <v>46191.61557621528</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3676,13 +3676,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.83218892361</v>
+        <v>46079.665522256946</v>
       </c>
       <c r="C42" s="5">
-        <v>46191.781853368055</v>
+        <v>46191.61518670139</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.78224165509</v>
+        <v>46191.61557498843</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3741,13 +3741,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.83218921296</v>
+        <v>46079.6655225463</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.78230420139</v>
+        <v>46191.61563753472</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.782318287034</v>
+        <v>46191.61565162037</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>162</v>
@@ -3794,13 +3794,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.83218950231</v>
+        <v>46079.66552283565</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.782240671295</v>
+        <v>46191.61557400463</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.78225513889</v>
+        <v>46191.615588472225</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3859,13 +3859,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.832189768524</v>
+        <v>46079.66552310185</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.78228831018</v>
+        <v>46191.61562164352</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.78230329861</v>
+        <v>46191.61563663195</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -3924,13 +3924,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.8321887037</v>
+        <v>46079.66552203704</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.78193627315</v>
+        <v>46191.61526960648</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.7823071875</v>
+        <v>46191.61564052083</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -3987,13 +3987,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.83218896991</v>
+        <v>46079.66552230324</v>
       </c>
       <c r="C47" s="8">
-        <v>46191.78245119213</v>
+        <v>46191.615784525464</v>
       </c>
       <c r="D47" s="8">
-        <v>46191.782462372685</v>
+        <v>46191.61579570602</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4040,13 +4040,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.83218923611</v>
+        <v>46079.66552256944</v>
       </c>
       <c r="C48" s="5">
-        <v>46191.78241675926</v>
+        <v>46191.61575009259</v>
       </c>
       <c r="D48" s="5">
-        <v>46191.78243247685</v>
+        <v>46191.61576581019</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4105,13 +4105,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.832189513894</v>
+        <v>46079.66552284722</v>
       </c>
       <c r="C49" s="8">
-        <v>46191.78242726852</v>
+        <v>46191.61576060185</v>
       </c>
       <c r="D49" s="8">
-        <v>46191.78244430556</v>
+        <v>46191.615777638886</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4170,13 +4170,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.83218978009</v>
+        <v>46079.66552311342</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.782435497684</v>
+        <v>46191.61576883102</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.78245195602</v>
+        <v>46191.61578528935</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4235,13 +4235,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.8321903125</v>
+        <v>46079.66552364583</v>
       </c>
       <c r="C51" s="8">
-        <v>46205.487603692134</v>
+        <v>46205.32093702546</v>
       </c>
       <c r="D51" s="8">
-        <v>46205.487614178244</v>
+        <v>46205.32094751157</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4288,13 +4288,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.83219059028</v>
+        <v>46079.66552392361</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.78238421296</v>
+        <v>46191.6157175463</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.7824008912</v>
+        <v>46191.61573422454</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4353,13 +4353,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.832187673615</v>
+        <v>46079.665521006944</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.7824912037</v>
+        <v>46191.61582453703</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.78250809028</v>
+        <v>46191.61584142361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4418,13 +4418,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.78258708333</v>
+        <v>46191.61592041666</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.78260511574</v>
+        <v>46191.615938449075</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4483,13 +4483,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.83218829861</v>
+        <v>46079.66552163195</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.7825933912</v>
+        <v>46191.61592672454</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.782608622685</v>
+        <v>46191.61594195601</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4548,13 +4548,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.83218858796</v>
+        <v>46079.6655219213</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.605380381945</v>
+        <v>46193.43871371528</v>
       </c>
       <c r="D56" s="5">
-        <v>46198.54290325231</v>
+        <v>46198.37623658565</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>
@@ -4613,13 +4613,13 @@
         <v>207</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.83218885417</v>
+        <v>46079.6655221875</v>
       </c>
       <c r="C57" s="8">
-        <v>46205.48758394676</v>
+        <v>46205.32091728009</v>
       </c>
       <c r="D57" s="8">
-        <v>46205.487604317124</v>
+        <v>46205.32093765047</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>208</v>
@@ -4676,11 +4676,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.83218913194</v>
+        <v>46079.66552246528</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46205.915604953705</v>
+        <v>46205.74893828704</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4723,11 +4723,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.83218939815</v>
+        <v>46079.66552273148</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46205.48760165509</v>
+        <v>46205.32093498843</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -4784,11 +4784,11 @@
         <v>217</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.83218965278</v>
+        <v>46079.665522986106</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.25042148148</v>
+        <v>46155.08375481481</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -4847,13 +4847,13 @@
         <v>220</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.83218994213</v>
+        <v>46079.665523275464</v>
       </c>
       <c r="C61" s="8">
-        <v>46205.91559434027</v>
+        <v>46205.748927673616</v>
       </c>
       <c r="D61" s="8">
-        <v>46205.91561125</v>
+        <v>46205.748944583334</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>221</v>
@@ -4910,11 +4910,11 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.83219021991</v>
+        <v>46079.66552355324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46205.91561136574</v>
+        <v>46205.74894469907</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -4973,11 +4973,11 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.83218761574</v>
+        <v>46079.66552094907</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.78121486111</v>
+        <v>46087.61454819444</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5020,11 +5020,11 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.832188368055</v>
+        <v>46079.66552170139</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46192.680783738426</v>
+        <v>46192.514117071754</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5083,11 +5083,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.832188009255</v>
+        <v>46079.66552134259</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.188807025464</v>
+        <v>46169.02214035879</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1342,13 +1342,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46079.66552056713</v>
+        <v>46079.8321872338</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.54914192129</v>
+        <v>46092.715808587964</v>
       </c>
       <c r="D4" s="5">
-        <v>46158.83449060185</v>
+        <v>46159.00115726852</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1391,13 +1391,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46079.66552091435</v>
+        <v>46079.83218758102</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54910645833</v>
+        <v>46092.715773125004</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.54914292824</v>
+        <v>46092.71580959491</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1456,13 +1456,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46079.66552115741</v>
+        <v>46079.832187824075</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.54910701389</v>
+        <v>46092.71577368055</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.5491424537</v>
+        <v>46092.715809120375</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1521,13 +1521,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46079.66552142361</v>
+        <v>46079.83218809028</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54910741898</v>
+        <v>46092.71577408565</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.54914295139</v>
+        <v>46092.71580961805</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1586,13 +1586,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46079.66552167824</v>
+        <v>46079.83218834491</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.54910778935</v>
+        <v>46092.71577445602</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.61045414352</v>
+        <v>46100.777120810184</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1651,13 +1651,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54910842593</v>
+        <v>46092.71577509259</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.549143275464</v>
+        <v>46092.71580994213</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1716,13 +1716,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46079.66552293982</v>
+        <v>46079.83218960648</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.39270920139</v>
+        <v>46193.559375868055</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.39274570602</v>
+        <v>46193.559412372684</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1769,13 +1769,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46079.66552079861</v>
+        <v>46079.832187465276</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.377863726855</v>
+        <v>46097.54453039352</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.51411703703</v>
+        <v>46192.680783703705</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1834,13 +1834,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46079.66552108796</v>
+        <v>46079.832187754626</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.61512047454</v>
+        <v>46191.781787141204</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.51411708334</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1899,13 +1899,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46114.348928506945</v>
+        <v>46114.51559517361</v>
       </c>
       <c r="C13" s="8">
-        <v>46191.61518097222</v>
+        <v>46191.78184763889</v>
       </c>
       <c r="D13" s="8">
-        <v>46191.615182407404</v>
+        <v>46191.781849074076</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -1954,13 +1954,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46114.349081990746</v>
+        <v>46114.5157486574</v>
       </c>
       <c r="C14" s="5">
-        <v>46191.615199583335</v>
+        <v>46191.78186625</v>
       </c>
       <c r="D14" s="5">
-        <v>46191.61520078704</v>
+        <v>46191.781867453705</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2009,13 +2009,13 @@
         <v>57</v>
       </c>
       <c r="B15" s="8">
-        <v>46079.665521435185</v>
+        <v>46079.83218810185</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.37807184028</v>
+        <v>46097.54473850694</v>
       </c>
       <c r="D15" s="8">
-        <v>46192.51411708334</v>
+        <v>46192.680783749995</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>58</v>
@@ -2074,13 +2074,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="5">
-        <v>46079.665522152776</v>
+        <v>46079.83218881945</v>
       </c>
       <c r="C16" s="5">
-        <v>46191.61528920139</v>
+        <v>46191.78195586806</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.61530193287</v>
+        <v>46191.781968599535</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>61</v>
@@ -2127,13 +2127,13 @@
         <v>63</v>
       </c>
       <c r="B17" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.37811188657</v>
+        <v>46097.544778553245</v>
       </c>
       <c r="D17" s="8">
-        <v>46097.37877938658</v>
+        <v>46097.54544605324</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>64</v>
@@ -2192,13 +2192,13 @@
         <v>66</v>
       </c>
       <c r="B18" s="5">
-        <v>46079.66552304398</v>
+        <v>46079.83218971065</v>
       </c>
       <c r="C18" s="5">
-        <v>46191.6152715625</v>
+        <v>46191.781938229164</v>
       </c>
       <c r="D18" s="5">
-        <v>46191.6152905787</v>
+        <v>46191.78195724537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>67</v>
@@ -2257,13 +2257,13 @@
         <v>69</v>
       </c>
       <c r="B19" s="8">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C19" s="8">
-        <v>46191.61527736111</v>
+        <v>46191.78194402778</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.61529302083</v>
+        <v>46191.781959687505</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -2322,13 +2322,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46079.66552032407</v>
+        <v>46079.83218699074</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3781387037</v>
+        <v>46097.54480537037</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.61084952546</v>
+        <v>46100.77751619213</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -2387,13 +2387,13 @@
         <v>78</v>
       </c>
       <c r="B21" s="8">
-        <v>46079.66552068287</v>
+        <v>46079.83218734954</v>
       </c>
       <c r="C21" s="8">
-        <v>46192.51416876157</v>
+        <v>46192.68083542824</v>
       </c>
       <c r="D21" s="8">
-        <v>46192.51418366898</v>
+        <v>46192.680850335644</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>79</v>
@@ -2440,13 +2440,13 @@
         <v>81</v>
       </c>
       <c r="B22" s="5">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C22" s="5">
-        <v>46191.61553530092</v>
+        <v>46191.782201967595</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.61554935185</v>
+        <v>46191.78221601852</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>82</v>
@@ -2505,13 +2505,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46079.66552123842</v>
+        <v>46079.83218790509</v>
       </c>
       <c r="C23" s="8">
-        <v>46191.61548202546</v>
+        <v>46191.78214869213</v>
       </c>
       <c r="D23" s="8">
-        <v>46191.61548420139</v>
+        <v>46191.78215086806</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -2566,13 +2566,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46079.665521504634</v>
+        <v>46079.83218817129</v>
       </c>
       <c r="C24" s="5">
-        <v>46191.61552018518</v>
+        <v>46191.78218685185</v>
       </c>
       <c r="D24" s="5">
-        <v>46191.615522314816</v>
+        <v>46191.78218898148</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -2625,13 +2625,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46079.66552247685</v>
+        <v>46079.83218914352</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.61546248842</v>
+        <v>46191.78212915509</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.615476886574</v>
+        <v>46191.78214355324</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -2690,13 +2690,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46079.66552270833</v>
+        <v>46079.832189374996</v>
       </c>
       <c r="C26" s="5">
-        <v>46191.6154033912</v>
+        <v>46191.782070057874</v>
       </c>
       <c r="D26" s="5">
-        <v>46191.61540471065</v>
+        <v>46191.78207137731</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -2751,13 +2751,13 @@
         <v>100</v>
       </c>
       <c r="B27" s="8">
-        <v>46079.66552043981</v>
+        <v>46079.83218710648</v>
       </c>
       <c r="C27" s="8">
-        <v>46191.61544633102</v>
+        <v>46191.78211299768</v>
       </c>
       <c r="D27" s="8">
-        <v>46191.615447662036</v>
+        <v>46191.7821143287</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -2812,13 +2812,13 @@
         <v>103</v>
       </c>
       <c r="B28" s="5">
-        <v>46079.665520787035</v>
+        <v>46079.83218745371</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.37891262732</v>
+        <v>46097.54557929398</v>
       </c>
       <c r="D28" s="5">
-        <v>46127.011858784725</v>
+        <v>46127.17852545139</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>104</v>
@@ -2877,13 +2877,13 @@
         <v>106</v>
       </c>
       <c r="B29" s="8">
-        <v>46079.66552111111</v>
+        <v>46079.83218777778</v>
       </c>
       <c r="C29" s="8">
-        <v>46097.37881908564</v>
+        <v>46097.545485752315</v>
       </c>
       <c r="D29" s="8">
-        <v>46097.378820983795</v>
+        <v>46097.54548765047</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>107</v>
@@ -2938,13 +2938,13 @@
         <v>109</v>
       </c>
       <c r="B30" s="5">
-        <v>46079.665521365736</v>
+        <v>46079.83218803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.378872685185</v>
+        <v>46097.54553935185</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.378873946756</v>
+        <v>46097.54554061343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>110</v>
@@ -2999,13 +2999,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="8">
-        <v>46079.66552164352</v>
+        <v>46079.83218831019</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.37889787037</v>
+        <v>46097.54556453704</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.37889954861</v>
+        <v>46097.54556621528</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>113</v>
@@ -3060,13 +3060,13 @@
         <v>115</v>
       </c>
       <c r="B32" s="5">
-        <v>46079.66552193287</v>
+        <v>46079.83218859954</v>
       </c>
       <c r="C32" s="5">
-        <v>46112.33927761574</v>
+        <v>46112.505944282406</v>
       </c>
       <c r="D32" s="5">
-        <v>46120.0064228588</v>
+        <v>46120.17308952546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>116</v>
@@ -3125,13 +3125,13 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46079.66552219907</v>
+        <v>46079.83218886574</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.379011296296</v>
+        <v>46097.54567796296</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.379012881946</v>
+        <v>46097.54567954861</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -3186,13 +3186,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="5">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C34" s="5">
-        <v>46112.34110125</v>
+        <v>46112.50776791667</v>
       </c>
       <c r="D34" s="5">
-        <v>46112.34110265046</v>
+        <v>46112.50776931713</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>125</v>
@@ -3247,13 +3247,13 @@
         <v>127</v>
       </c>
       <c r="B35" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C35" s="8">
-        <v>46204.54318872685</v>
+        <v>46204.70985539352</v>
       </c>
       <c r="D35" s="8">
-        <v>46204.54320204861</v>
+        <v>46204.709868715276</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>128</v>
@@ -3300,13 +3300,13 @@
         <v>130</v>
       </c>
       <c r="B36" s="5">
-        <v>46079.66552299769</v>
+        <v>46079.83218966435</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.350045196756</v>
+        <v>46114.51671186343</v>
       </c>
       <c r="D36" s="5">
-        <v>46127.522372928244</v>
+        <v>46127.68903959491</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3365,13 +3365,13 @@
         <v>135</v>
       </c>
       <c r="B37" s="8">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C37" s="8">
-        <v>46127.52245238426</v>
+        <v>46127.68911905093</v>
       </c>
       <c r="D37" s="8">
-        <v>46127.52246925926</v>
+        <v>46127.689135925924</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>136</v>
@@ -3430,13 +3430,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46087.607717962965</v>
+        <v>46087.77438462963</v>
       </c>
       <c r="C38" s="5">
-        <v>46127.523203958335</v>
+        <v>46127.689870625</v>
       </c>
       <c r="D38" s="5">
-        <v>46127.52323594908</v>
+        <v>46127.68990261574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3495,13 +3495,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46087.60831841435</v>
+        <v>46087.77498508102</v>
       </c>
       <c r="C39" s="8">
-        <v>46204.54316980324</v>
+        <v>46204.709836469905</v>
       </c>
       <c r="D39" s="8">
-        <v>46204.54413458334</v>
+        <v>46204.710801249996</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3558,13 +3558,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46079.66552171296</v>
+        <v>46079.83218837963</v>
       </c>
       <c r="C40" s="5">
-        <v>46191.61557571759</v>
+        <v>46191.78224238426</v>
       </c>
       <c r="D40" s="5">
-        <v>46191.615588113425</v>
+        <v>46191.78225478009</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3611,13 +3611,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46079.66552199074</v>
+        <v>46079.83218865741</v>
       </c>
       <c r="C41" s="8">
-        <v>46191.615561342594</v>
+        <v>46191.78222800926</v>
       </c>
       <c r="D41" s="8">
-        <v>46191.61557621528</v>
+        <v>46191.78224288195</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3676,13 +3676,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46079.665522256946</v>
+        <v>46079.83218892361</v>
       </c>
       <c r="C42" s="5">
-        <v>46191.61518670139</v>
+        <v>46191.781853368055</v>
       </c>
       <c r="D42" s="5">
-        <v>46191.61557498843</v>
+        <v>46191.78224165509</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3741,13 +3741,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46079.6655225463</v>
+        <v>46079.83218921296</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.61563753472</v>
+        <v>46191.78230420139</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.61565162037</v>
+        <v>46191.782318287034</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>162</v>
@@ -3794,13 +3794,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46079.66552283565</v>
+        <v>46079.83218950231</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.61557400463</v>
+        <v>46191.782240671295</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.615588472225</v>
+        <v>46191.78225513889</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3859,13 +3859,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46079.66552310185</v>
+        <v>46079.832189768524</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.61562164352</v>
+        <v>46191.78228831018</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.61563663195</v>
+        <v>46191.78230329861</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -3924,13 +3924,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46079.66552203704</v>
+        <v>46079.8321887037</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.61526960648</v>
+        <v>46191.78193627315</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.61564052083</v>
+        <v>46191.7823071875</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -3987,13 +3987,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46079.66552230324</v>
+        <v>46079.83218896991</v>
       </c>
       <c r="C47" s="8">
-        <v>46191.615784525464</v>
+        <v>46191.78245119213</v>
       </c>
       <c r="D47" s="8">
-        <v>46191.61579570602</v>
+        <v>46191.782462372685</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4040,13 +4040,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46079.66552256944</v>
+        <v>46079.83218923611</v>
       </c>
       <c r="C48" s="5">
-        <v>46191.61575009259</v>
+        <v>46191.78241675926</v>
       </c>
       <c r="D48" s="5">
-        <v>46191.61576581019</v>
+        <v>46191.78243247685</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4105,13 +4105,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="8">
-        <v>46079.66552284722</v>
+        <v>46079.832189513894</v>
       </c>
       <c r="C49" s="8">
-        <v>46191.61576060185</v>
+        <v>46191.78242726852</v>
       </c>
       <c r="D49" s="8">
-        <v>46191.615777638886</v>
+        <v>46191.78244430556</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>183</v>
@@ -4170,13 +4170,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46079.66552311342</v>
+        <v>46079.83218978009</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.61576883102</v>
+        <v>46191.782435497684</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.61578528935</v>
+        <v>46191.78245195602</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4235,13 +4235,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46079.66552364583</v>
+        <v>46079.8321903125</v>
       </c>
       <c r="C51" s="8">
-        <v>46205.32093702546</v>
+        <v>46205.487603692134</v>
       </c>
       <c r="D51" s="8">
-        <v>46205.32094751157</v>
+        <v>46205.487614178244</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>189</v>
@@ -4288,13 +4288,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46079.66552392361</v>
+        <v>46079.83219059028</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.6157175463</v>
+        <v>46191.78238421296</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.61573422454</v>
+        <v>46191.7824008912</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4353,13 +4353,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46079.665521006944</v>
+        <v>46079.832187673615</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.61582453703</v>
+        <v>46191.7824912037</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.61584142361</v>
+        <v>46191.78250809028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4418,13 +4418,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.61592041666</v>
+        <v>46191.78258708333</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.615938449075</v>
+        <v>46191.78260511574</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4483,13 +4483,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46079.66552163195</v>
+        <v>46079.83218829861</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.61592672454</v>
+        <v>46191.7825933912</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.61594195601</v>
+        <v>46191.782608622685</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4548,13 +4548,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46079.6655219213</v>
+        <v>46079.83218858796</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.43871371528</v>
+        <v>46193.605380381945</v>
       </c>
       <c r="D56" s="5">
-        <v>46198.37623658565</v>
+        <v>46198.54290325231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>146</v>
@@ -4613,13 +4613,13 @@
         <v>207</v>
       </c>
       <c r="B57" s="8">
-        <v>46079.6655221875</v>
+        <v>46079.83218885417</v>
       </c>
       <c r="C57" s="8">
-        <v>46205.32091728009</v>
+        <v>46205.48758394676</v>
       </c>
       <c r="D57" s="8">
-        <v>46205.32093765047</v>
+        <v>46205.487604317124</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>208</v>
@@ -4676,11 +4676,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46079.66552246528</v>
+        <v>46079.83218913194</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46205.74893828704</v>
+        <v>46211.69077050926</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4723,11 +4723,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="8">
-        <v>46079.66552273148</v>
+        <v>46079.83218939815</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46205.32093498843</v>
+        <v>46211.699635578705</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -4784,11 +4784,13 @@
         <v>217</v>
       </c>
       <c r="B60" s="5">
-        <v>46079.665522986106</v>
-      </c>
-      <c r="C60" s="6"/>
+        <v>46079.83218965278</v>
+      </c>
+      <c r="C60" s="5">
+        <v>46211.69076003472</v>
+      </c>
       <c r="D60" s="5">
-        <v>46155.08375481481</v>
+        <v>46211.69077887731</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -4833,13 +4835,13 @@
         <v>46155</v>
       </c>
       <c r="S60" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="U60" s="10" t="s">
-        <v>90</v>
+      <c r="U60" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4847,13 +4849,13 @@
         <v>220</v>
       </c>
       <c r="B61" s="8">
-        <v>46079.665523275464</v>
+        <v>46079.83218994213</v>
       </c>
       <c r="C61" s="8">
-        <v>46205.748927673616</v>
+        <v>46205.91559434027</v>
       </c>
       <c r="D61" s="8">
-        <v>46205.748944583334</v>
+        <v>46211.69077946759</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>221</v>
@@ -4901,8 +4903,8 @@
       <c r="T61" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="U61" s="11" t="s">
-        <v>32</v>
+      <c r="U61" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -4910,11 +4912,11 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46079.66552355324</v>
+        <v>46079.83219021991</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46205.74894469907</v>
+        <v>46205.91561136574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -4973,11 +4975,11 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46079.66552094907</v>
+        <v>46079.83218761574</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.61454819444</v>
+        <v>46087.78121486111</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5020,11 +5022,11 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46079.66552170139</v>
+        <v>46079.832188368055</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46192.514117071754</v>
+        <v>46192.680783738426</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5083,11 +5085,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46079.66552134259</v>
+        <v>46079.832188009255</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.02214035879</v>
+        <v>46169.188807025464</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="232">
   <si>
     <t>50001520 -  XEMORTIZ DDG</t>
   </si>
@@ -226,9 +226,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete ot 4268 // ot 4269</t>
   </si>
   <si>
@@ -236,12 +233,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -2272,11 +2263,9 @@
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="9"/>
       <c r="I19" s="8">
         <v>46086</v>
       </c>
@@ -2299,7 +2288,7 @@
         <v>51</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q19" s="8">
         <v>46086</v>
@@ -2319,7 +2308,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" s="5">
         <v>46079.83218699074</v>
@@ -2331,17 +2320,15 @@
         <v>46100.77751619213</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46087</v>
       </c>
@@ -2364,7 +2351,7 @@
         <v>58</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q20" s="5">
         <v>46087</v>
@@ -2384,7 +2371,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B21" s="8">
         <v>46079.83218734954</v>
@@ -2396,7 +2383,7 @@
         <v>46192.680850335644</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2420,7 +2407,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2437,7 +2424,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B22" s="5">
         <v>46079.832187673615</v>
@@ -2449,16 +2436,16 @@
         <v>46191.78221601852</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I22" s="5">
         <v>46090</v>
@@ -2476,13 +2463,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q22" s="5">
         <v>46090</v>
@@ -2502,7 +2489,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B23" s="8">
         <v>46079.83218790509</v>
@@ -2514,16 +2501,16 @@
         <v>46191.78215086806</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I23" s="8">
         <v>46090</v>
@@ -2541,13 +2528,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
@@ -2555,15 +2542,15 @@
         <v>0</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83218817129</v>
@@ -2575,16 +2562,16 @@
         <v>46191.78218898148</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I24" s="5">
         <v>46092</v>
@@ -2602,19 +2589,19 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U24" s="11" t="s">
         <v>32</v>
@@ -2622,7 +2609,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B25" s="8">
         <v>46079.83218914352</v>
@@ -2634,16 +2621,16 @@
         <v>46191.78214355324</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I25" s="8">
         <v>46090</v>
@@ -2661,13 +2648,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q25" s="8">
         <v>46090</v>
@@ -2687,7 +2674,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B26" s="5">
         <v>46079.832189374996</v>
@@ -2699,16 +2686,16 @@
         <v>46191.78207137731</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I26" s="5">
         <v>46090</v>
@@ -2726,13 +2713,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2740,15 +2727,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B27" s="8">
         <v>46079.83218710648</v>
@@ -2760,16 +2747,16 @@
         <v>46191.7821143287</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I27" s="8">
         <v>46092</v>
@@ -2787,13 +2774,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="O27" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="O27" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="P27" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2801,15 +2788,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B28" s="5">
         <v>46079.83218745371</v>
@@ -2821,16 +2808,16 @@
         <v>46127.17852545139</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I28" s="5">
         <v>46090</v>
@@ -2848,13 +2835,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q28" s="5">
         <v>46090</v>
@@ -2874,7 +2861,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83218777778</v>
@@ -2886,16 +2873,16 @@
         <v>46097.54548765047</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I29" s="8">
         <v>46090</v>
@@ -2913,13 +2900,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -2927,15 +2914,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83218803241</v>
@@ -2947,16 +2934,16 @@
         <v>46097.54554061343</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I30" s="5">
         <v>46099</v>
@@ -2974,13 +2961,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="O30" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="P30" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -2988,15 +2975,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83218831019</v>
@@ -3008,16 +2995,16 @@
         <v>46097.54556621528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I31" s="8">
         <v>46099</v>
@@ -3035,13 +3022,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="P31" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3049,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83218859954</v>
@@ -3069,16 +3056,16 @@
         <v>46120.17308952546</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I32" s="5">
         <v>46091</v>
@@ -3096,13 +3083,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q32" s="5">
         <v>46091</v>
@@ -3117,12 +3104,12 @@
         <v>31</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83218886574</v>
@@ -3134,16 +3121,16 @@
         <v>46097.54567954861</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I33" s="8">
         <v>46091</v>
@@ -3161,13 +3148,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3175,15 +3162,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B34" s="5">
         <v>46079.83218913194</v>
@@ -3195,16 +3182,16 @@
         <v>46112.50776931713</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I34" s="5">
         <v>46100</v>
@@ -3222,13 +3209,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3236,15 +3223,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B35" s="8">
         <v>46079.83218939815</v>
@@ -3256,7 +3243,7 @@
         <v>46204.709868715276</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>25</v>
@@ -3280,7 +3267,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3297,7 +3284,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83218966435</v>
@@ -3309,16 +3296,16 @@
         <v>46127.68903959491</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46087</v>
@@ -3336,13 +3323,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q36" s="5">
         <v>46087</v>
@@ -3362,7 +3349,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B37" s="8">
         <v>46079.832188009255</v>
@@ -3374,16 +3361,16 @@
         <v>46127.689135925924</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I37" s="8">
         <v>46108</v>
@@ -3401,13 +3388,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="8">
         <v>46108</v>
@@ -3427,7 +3414,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46087.77438462963</v>
@@ -3439,16 +3426,16 @@
         <v>46127.68990261574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46115</v>
@@ -3466,13 +3453,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q38" s="5">
         <v>46115</v>
@@ -3492,7 +3479,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>46087.77498508102</v>
@@ -3504,16 +3491,16 @@
         <v>46204.710801249996</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="8">
@@ -3529,13 +3516,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Q39" s="8">
         <v>46150</v>
@@ -3547,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U39" s="11" t="s">
         <v>32</v>
@@ -3555,7 +3542,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83218837963</v>
@@ -3567,7 +3554,7 @@
         <v>46191.78225478009</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3591,7 +3578,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3608,7 +3595,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46079.83218865741</v>
@@ -3620,16 +3607,16 @@
         <v>46191.78224288195</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3647,13 +3634,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="8">
         <v>46120</v>
@@ -3673,7 +3660,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83218892361</v>
@@ -3685,16 +3672,16 @@
         <v>46191.78224165509</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I42" s="5">
         <v>46122</v>
@@ -3712,13 +3699,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="O42" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="O42" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="P42" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="5">
         <v>46122</v>
@@ -3733,12 +3720,12 @@
         <v>31</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46079.83218921296</v>
@@ -3750,7 +3737,7 @@
         <v>46191.782318287034</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>25</v>
@@ -3774,7 +3761,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3791,7 +3778,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46079.83218950231</v>
@@ -3803,16 +3790,16 @@
         <v>46191.78225513889</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I44" s="5">
         <v>46126</v>
@@ -3830,13 +3817,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="5">
         <v>46126</v>
@@ -3856,7 +3843,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46079.832189768524</v>
@@ -3868,16 +3855,16 @@
         <v>46191.78230329861</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I45" s="8">
         <v>46128</v>
@@ -3895,13 +3882,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="8">
         <v>46128</v>
@@ -3921,7 +3908,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46079.8321887037</v>
@@ -3933,16 +3920,16 @@
         <v>46191.7823071875</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="5">
@@ -3958,13 +3945,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="5">
         <v>46135</v>
@@ -3979,12 +3966,12 @@
         <v>31</v>
       </c>
       <c r="U46" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B47" s="8">
         <v>46079.83218896991</v>
@@ -3996,7 +3983,7 @@
         <v>46191.782462372685</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>25</v>
@@ -4020,7 +4007,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4037,7 +4024,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46079.83218923611</v>
@@ -4049,16 +4036,16 @@
         <v>46191.78243247685</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I48" s="5">
         <v>46094</v>
@@ -4076,13 +4063,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="5">
         <v>46094</v>
@@ -4102,7 +4089,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46079.832189513894</v>
@@ -4114,16 +4101,16 @@
         <v>46191.78244430556</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I49" s="8">
         <v>46112</v>
@@ -4141,13 +4128,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46112</v>
@@ -4167,7 +4154,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46079.83218978009</v>
@@ -4179,16 +4166,16 @@
         <v>46191.78245195602</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I50" s="5">
         <v>46127</v>
@@ -4206,13 +4193,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="5">
         <v>46127</v>
@@ -4232,7 +4219,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46079.8321903125</v>
@@ -4244,7 +4231,7 @@
         <v>46205.487614178244</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>25</v>
@@ -4268,7 +4255,7 @@
         <v>26</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>26</v>
@@ -4285,7 +4272,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46079.83219059028</v>
@@ -4297,17 +4284,15 @@
         <v>46191.7824008912</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H52" s="6"/>
       <c r="I52" s="5">
         <v>46136</v>
       </c>
@@ -4324,13 +4309,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q52" s="5">
         <v>46136</v>
@@ -4342,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="T52" s="12" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="U52" s="11" t="s">
         <v>32</v>
@@ -4350,7 +4335,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B53" s="8">
         <v>46079.832187673615</v>
@@ -4362,17 +4347,15 @@
         <v>46191.78250809028</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H53" s="9"/>
       <c r="I53" s="8">
         <v>46146</v>
       </c>
@@ -4389,13 +4372,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="8">
         <v>46146</v>
@@ -4407,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="T53" s="12" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="U53" s="11" t="s">
         <v>32</v>
@@ -4415,7 +4398,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46079.832188009255</v>
@@ -4427,17 +4410,15 @@
         <v>46191.78260511574</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H54" s="6"/>
       <c r="I54" s="5">
         <v>46147</v>
       </c>
@@ -4454,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q54" s="5">
         <v>46147</v>
@@ -4472,7 +4453,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>32</v>
@@ -4480,7 +4461,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B55" s="8">
         <v>46079.83218829861</v>
@@ -4492,17 +4473,15 @@
         <v>46191.782608622685</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H55" s="9"/>
       <c r="I55" s="8">
         <v>46148</v>
       </c>
@@ -4519,13 +4498,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q55" s="8">
         <v>46148</v>
@@ -4537,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="T55" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U55" s="11" t="s">
         <v>32</v>
@@ -4545,7 +4524,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46079.83218858796</v>
@@ -4557,17 +4536,15 @@
         <v>46198.54290325231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H56" s="6"/>
       <c r="I56" s="5">
         <v>46149</v>
       </c>
@@ -4584,13 +4561,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="Q56" s="5">
         <v>46149</v>
@@ -4602,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U56" s="11" t="s">
         <v>32</v>
@@ -4610,7 +4587,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B57" s="8">
         <v>46079.83218885417</v>
@@ -4622,17 +4599,15 @@
         <v>46205.487604317124</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H57" s="9"/>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
         <v>46153</v>
@@ -4647,13 +4622,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q57" s="8">
         <v>46153</v>
@@ -4665,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="T57" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>32</v>
@@ -4673,7 +4648,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46079.83218913194</v>
@@ -4683,7 +4658,7 @@
         <v>46211.69077050926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4707,7 +4682,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4720,7 +4695,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83218939815</v>
@@ -4730,16 +4705,16 @@
         <v>46211.699635578705</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -4755,13 +4730,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="8">
         <v>46154</v>
@@ -4773,15 +4748,15 @@
         <v>0</v>
       </c>
       <c r="T59" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83218965278</v>
@@ -4793,17 +4768,15 @@
         <v>46211.69077887731</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H60" s="6"/>
       <c r="I60" s="5">
         <v>46155</v>
       </c>
@@ -4820,13 +4793,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="5">
         <v>46155</v>
@@ -4838,7 +4811,7 @@
         <v>1</v>
       </c>
       <c r="T60" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>32</v>
@@ -4846,7 +4819,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B61" s="8">
         <v>46079.83218994213</v>
@@ -4858,16 +4831,16 @@
         <v>46211.69077946759</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -4883,13 +4856,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="8">
         <v>46155</v>
@@ -4901,15 +4874,15 @@
         <v>1</v>
       </c>
       <c r="T61" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46079.83219021991</v>
@@ -4919,16 +4892,16 @@
         <v>46205.91561136574</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I62" s="5">
         <v>46157</v>
@@ -4946,13 +4919,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Q62" s="5">
         <v>46157</v>
@@ -4964,15 +4937,15 @@
         <v>0</v>
       </c>
       <c r="T62" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83218761574</v>
@@ -4982,7 +4955,7 @@
         <v>46087.78121486111</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5006,7 +4979,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5019,7 +4992,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46079.832188368055</v>
@@ -5029,16 +5002,16 @@
         <v>46192.680783738426</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I64" s="5">
         <v>46160</v>
@@ -5056,13 +5029,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q64" s="5">
         <v>46160</v>
@@ -5077,12 +5050,12 @@
         <v>31</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B65" s="8">
         <v>46079.832188009255</v>
@@ -5092,16 +5065,16 @@
         <v>46169.188807025464</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I65" s="8">
         <v>46160</v>
@@ -5119,13 +5092,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="Q65" s="8">
         <v>46160</v>
@@ -5140,7 +5113,7 @@
         <v>31</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="233">
   <si>
     <t>50001520 -  XEMORTIZ DDG</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete ot 4268 // ot 4269</t>
@@ -2254,7 +2257,7 @@
         <v>46191.78194402778</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.781959687505</v>
+        <v>46223.8079497338</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -2263,9 +2266,11 @@
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="I19" s="8">
         <v>46086</v>
       </c>
@@ -2288,7 +2293,7 @@
         <v>51</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q19" s="8">
         <v>46086</v>
@@ -2308,7 +2313,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B20" s="5">
         <v>46079.83218699074</v>
@@ -2317,18 +2322,20 @@
         <v>46097.54480537037</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.77751619213</v>
+        <v>46223.80794568287</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I20" s="5">
         <v>46087</v>
       </c>
@@ -2351,7 +2358,7 @@
         <v>58</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q20" s="5">
         <v>46087</v>
@@ -2371,7 +2378,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B21" s="8">
         <v>46079.83218734954</v>
@@ -2383,7 +2390,7 @@
         <v>46192.680850335644</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2407,7 +2414,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2424,7 +2431,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" s="5">
         <v>46079.832187673615</v>
@@ -2436,16 +2443,16 @@
         <v>46191.78221601852</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I22" s="5">
         <v>46090</v>
@@ -2463,13 +2470,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q22" s="5">
         <v>46090</v>
@@ -2489,7 +2496,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B23" s="8">
         <v>46079.83218790509</v>
@@ -2501,16 +2508,16 @@
         <v>46191.78215086806</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I23" s="8">
         <v>46090</v>
@@ -2528,13 +2535,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
@@ -2542,15 +2549,15 @@
         <v>0</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83218817129</v>
@@ -2562,16 +2569,16 @@
         <v>46191.78218898148</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I24" s="5">
         <v>46092</v>
@@ -2589,19 +2596,19 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U24" s="11" t="s">
         <v>32</v>
@@ -2609,7 +2616,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B25" s="8">
         <v>46079.83218914352</v>
@@ -2621,16 +2628,16 @@
         <v>46191.78214355324</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I25" s="8">
         <v>46090</v>
@@ -2648,13 +2655,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q25" s="8">
         <v>46090</v>
@@ -2674,7 +2681,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B26" s="5">
         <v>46079.832189374996</v>
@@ -2686,16 +2693,16 @@
         <v>46191.78207137731</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I26" s="5">
         <v>46090</v>
@@ -2713,13 +2720,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2727,15 +2734,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B27" s="8">
         <v>46079.83218710648</v>
@@ -2747,16 +2754,16 @@
         <v>46191.7821143287</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I27" s="8">
         <v>46092</v>
@@ -2774,13 +2781,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2788,15 +2795,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" s="5">
         <v>46079.83218745371</v>
@@ -2808,16 +2815,16 @@
         <v>46127.17852545139</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I28" s="5">
         <v>46090</v>
@@ -2835,13 +2842,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q28" s="5">
         <v>46090</v>
@@ -2861,7 +2868,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83218777778</v>
@@ -2873,16 +2880,16 @@
         <v>46097.54548765047</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I29" s="8">
         <v>46090</v>
@@ -2900,13 +2907,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -2914,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83218803241</v>
@@ -2934,16 +2941,16 @@
         <v>46097.54554061343</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I30" s="5">
         <v>46099</v>
@@ -2961,13 +2968,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -2975,15 +2982,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83218831019</v>
@@ -2995,16 +3002,16 @@
         <v>46097.54556621528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I31" s="8">
         <v>46099</v>
@@ -3022,13 +3029,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3036,15 +3043,15 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83218859954</v>
@@ -3056,16 +3063,16 @@
         <v>46120.17308952546</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>46091</v>
@@ -3083,13 +3090,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q32" s="5">
         <v>46091</v>
@@ -3104,12 +3111,12 @@
         <v>31</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83218886574</v>
@@ -3121,16 +3128,16 @@
         <v>46097.54567954861</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I33" s="8">
         <v>46091</v>
@@ -3148,13 +3155,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3162,15 +3169,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B34" s="5">
         <v>46079.83218913194</v>
@@ -3182,16 +3189,16 @@
         <v>46112.50776931713</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I34" s="5">
         <v>46100</v>
@@ -3209,13 +3216,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3223,15 +3230,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B35" s="8">
         <v>46079.83218939815</v>
@@ -3243,7 +3250,7 @@
         <v>46204.709868715276</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>25</v>
@@ -3267,7 +3274,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3284,7 +3291,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83218966435</v>
@@ -3296,16 +3303,16 @@
         <v>46127.68903959491</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I36" s="5">
         <v>46087</v>
@@ -3323,13 +3330,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q36" s="5">
         <v>46087</v>
@@ -3349,7 +3356,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="8">
         <v>46079.832188009255</v>
@@ -3361,16 +3368,16 @@
         <v>46127.689135925924</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I37" s="8">
         <v>46108</v>
@@ -3388,13 +3395,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="8">
         <v>46108</v>
@@ -3414,7 +3421,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46087.77438462963</v>
@@ -3426,16 +3433,16 @@
         <v>46127.68990261574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I38" s="5">
         <v>46115</v>
@@ -3453,13 +3460,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q38" s="5">
         <v>46115</v>
@@ -3479,7 +3486,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B39" s="8">
         <v>46087.77498508102</v>
@@ -3491,16 +3498,16 @@
         <v>46204.710801249996</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="8">
@@ -3516,13 +3523,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="8">
         <v>46150</v>
@@ -3534,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U39" s="11" t="s">
         <v>32</v>
@@ -3542,7 +3549,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83218837963</v>
@@ -3554,7 +3561,7 @@
         <v>46191.78225478009</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3578,7 +3585,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3595,7 +3602,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46079.83218865741</v>
@@ -3607,16 +3614,16 @@
         <v>46191.78224288195</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3634,13 +3641,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="8">
         <v>46120</v>
@@ -3660,7 +3667,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83218892361</v>
@@ -3672,16 +3679,16 @@
         <v>46191.78224165509</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46122</v>
@@ -3699,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="5">
         <v>46122</v>
@@ -3720,12 +3727,12 @@
         <v>31</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46079.83218921296</v>
@@ -3737,7 +3744,7 @@
         <v>46191.782318287034</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>25</v>
@@ -3761,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3778,7 +3785,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46079.83218950231</v>
@@ -3790,16 +3797,16 @@
         <v>46191.78225513889</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I44" s="5">
         <v>46126</v>
@@ -3817,13 +3824,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46126</v>
@@ -3843,7 +3850,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46079.832189768524</v>
@@ -3855,16 +3862,16 @@
         <v>46191.78230329861</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I45" s="8">
         <v>46128</v>
@@ -3882,13 +3889,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="8">
         <v>46128</v>
@@ -3908,7 +3915,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46079.8321887037</v>
@@ -3920,16 +3927,16 @@
         <v>46191.7823071875</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="5">
@@ -3945,13 +3952,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="5">
         <v>46135</v>
@@ -3966,12 +3973,12 @@
         <v>31</v>
       </c>
       <c r="U46" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="8">
         <v>46079.83218896991</v>
@@ -3983,7 +3990,7 @@
         <v>46191.782462372685</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>25</v>
@@ -4007,7 +4014,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4024,7 +4031,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46079.83218923611</v>
@@ -4036,16 +4043,16 @@
         <v>46191.78243247685</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I48" s="5">
         <v>46094</v>
@@ -4063,13 +4070,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46094</v>
@@ -4089,7 +4096,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46079.832189513894</v>
@@ -4101,16 +4108,16 @@
         <v>46191.78244430556</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I49" s="8">
         <v>46112</v>
@@ -4128,13 +4135,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="8">
         <v>46112</v>
@@ -4154,7 +4161,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46079.83218978009</v>
@@ -4166,16 +4173,16 @@
         <v>46191.78245195602</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I50" s="5">
         <v>46127</v>
@@ -4193,13 +4200,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="5">
         <v>46127</v>
@@ -4219,7 +4226,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46079.8321903125</v>
@@ -4231,7 +4238,7 @@
         <v>46205.487614178244</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>25</v>
@@ -4255,7 +4262,7 @@
         <v>26</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>26</v>
@@ -4272,7 +4279,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46079.83219059028</v>
@@ -4281,18 +4288,20 @@
         <v>46191.78238421296</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.7824008912</v>
+        <v>46223.80805787037</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I52" s="5">
         <v>46136</v>
       </c>
@@ -4309,13 +4318,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="5">
         <v>46136</v>
@@ -4327,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="T52" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U52" s="11" t="s">
         <v>32</v>
@@ -4335,7 +4344,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B53" s="8">
         <v>46079.832187673615</v>
@@ -4344,18 +4353,20 @@
         <v>46191.7824912037</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.78250809028</v>
+        <v>46223.808054270834</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="I53" s="8">
         <v>46146</v>
       </c>
@@ -4372,13 +4383,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="8">
         <v>46146</v>
@@ -4390,7 +4401,7 @@
         <v>1</v>
       </c>
       <c r="T53" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U53" s="11" t="s">
         <v>32</v>
@@ -4398,7 +4409,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46079.832188009255</v>
@@ -4407,18 +4418,20 @@
         <v>46191.78258708333</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.78260511574</v>
+        <v>46223.80804981482</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I54" s="5">
         <v>46147</v>
       </c>
@@ -4435,13 +4448,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q54" s="5">
         <v>46147</v>
@@ -4453,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>32</v>
@@ -4461,7 +4474,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B55" s="8">
         <v>46079.83218829861</v>
@@ -4470,18 +4483,20 @@
         <v>46191.7825933912</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.782608622685</v>
+        <v>46223.80804584491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="I55" s="8">
         <v>46148</v>
       </c>
@@ -4498,13 +4513,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="8">
         <v>46148</v>
@@ -4516,7 +4531,7 @@
         <v>1</v>
       </c>
       <c r="T55" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U55" s="11" t="s">
         <v>32</v>
@@ -4524,7 +4539,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
         <v>46079.83218858796</v>
@@ -4533,18 +4548,20 @@
         <v>46193.605380381945</v>
       </c>
       <c r="D56" s="5">
-        <v>46198.54290325231</v>
+        <v>46223.80804175926</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I56" s="5">
         <v>46149</v>
       </c>
@@ -4561,13 +4578,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q56" s="5">
         <v>46149</v>
@@ -4579,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U56" s="11" t="s">
         <v>32</v>
@@ -4587,7 +4604,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B57" s="8">
         <v>46079.83218885417</v>
@@ -4596,18 +4613,20 @@
         <v>46205.48758394676</v>
       </c>
       <c r="D57" s="8">
-        <v>46205.487604317124</v>
+        <v>46223.80803569444</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
         <v>46153</v>
@@ -4622,13 +4641,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="8">
         <v>46153</v>
@@ -4640,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="T57" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>32</v>
@@ -4648,7 +4667,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46079.83218913194</v>
@@ -4658,7 +4677,7 @@
         <v>46211.69077050926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4682,7 +4701,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4695,7 +4714,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83218939815</v>
@@ -4705,16 +4724,16 @@
         <v>46211.699635578705</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -4730,13 +4749,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="8">
         <v>46154</v>
@@ -4748,15 +4767,15 @@
         <v>0</v>
       </c>
       <c r="T59" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83218965278</v>
@@ -4765,18 +4784,20 @@
         <v>46211.69076003472</v>
       </c>
       <c r="D60" s="5">
-        <v>46211.69077887731</v>
+        <v>46223.808229965274</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I60" s="5">
         <v>46155</v>
       </c>
@@ -4793,13 +4814,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q60" s="5">
         <v>46155</v>
@@ -4811,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="T60" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>32</v>
@@ -4819,7 +4840,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B61" s="8">
         <v>46079.83218994213</v>
@@ -4831,16 +4852,16 @@
         <v>46211.69077946759</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -4856,13 +4877,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="8">
         <v>46155</v>
@@ -4874,15 +4895,15 @@
         <v>1</v>
       </c>
       <c r="T61" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46079.83219021991</v>
@@ -4892,16 +4913,16 @@
         <v>46205.91561136574</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I62" s="5">
         <v>46157</v>
@@ -4919,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q62" s="5">
         <v>46157</v>
@@ -4937,15 +4958,15 @@
         <v>0</v>
       </c>
       <c r="T62" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83218761574</v>
@@ -4955,7 +4976,7 @@
         <v>46087.78121486111</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -4979,7 +5000,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -4992,7 +5013,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B64" s="5">
         <v>46079.832188368055</v>
@@ -5002,16 +5023,16 @@
         <v>46192.680783738426</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I64" s="5">
         <v>46160</v>
@@ -5029,13 +5050,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="5">
         <v>46160</v>
@@ -5050,12 +5071,12 @@
         <v>31</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="8">
         <v>46079.832188009255</v>
@@ -5065,16 +5086,16 @@
         <v>46169.188807025464</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I65" s="8">
         <v>46160</v>
@@ -5092,13 +5113,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q65" s="8">
         <v>46160</v>
@@ -5113,7 +5134,7 @@
         <v>31</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -4849,7 +4849,7 @@
         <v>46205.91559434027</v>
       </c>
       <c r="D61" s="8">
-        <v>46211.69077946759</v>
+        <v>46224.67008298611</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>219</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -4721,7 +4721,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46211.699635578705</v>
+        <v>46225.552571493055</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>207</v>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="234">
   <si>
     <t>50001520 -  XEMORTIZ DDG</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2269,7 +2272,7 @@
         <v>71</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I19" s="8">
         <v>46086</v>
@@ -2293,7 +2296,7 @@
         <v>51</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q19" s="8">
         <v>46086</v>
@@ -2313,7 +2316,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" s="5">
         <v>46079.83218699074</v>
@@ -2325,7 +2328,7 @@
         <v>46223.80794568287</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2334,7 +2337,7 @@
         <v>71</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I20" s="5">
         <v>46087</v>
@@ -2358,7 +2361,7 @@
         <v>58</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q20" s="5">
         <v>46087</v>
@@ -2378,7 +2381,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" s="8">
         <v>46079.83218734954</v>
@@ -2390,7 +2393,7 @@
         <v>46192.680850335644</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2414,7 +2417,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2431,7 +2434,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" s="5">
         <v>46079.832187673615</v>
@@ -2443,16 +2446,16 @@
         <v>46191.78221601852</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I22" s="5">
         <v>46090</v>
@@ -2470,13 +2473,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q22" s="5">
         <v>46090</v>
@@ -2496,7 +2499,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" s="8">
         <v>46079.83218790509</v>
@@ -2508,16 +2511,16 @@
         <v>46191.78215086806</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I23" s="8">
         <v>46090</v>
@@ -2535,13 +2538,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
@@ -2549,15 +2552,15 @@
         <v>0</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B24" s="5">
         <v>46079.83218817129</v>
@@ -2569,16 +2572,16 @@
         <v>46191.78218898148</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I24" s="5">
         <v>46092</v>
@@ -2596,19 +2599,19 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U24" s="11" t="s">
         <v>32</v>
@@ -2616,7 +2619,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" s="8">
         <v>46079.83218914352</v>
@@ -2628,16 +2631,16 @@
         <v>46191.78214355324</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I25" s="8">
         <v>46090</v>
@@ -2655,13 +2658,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q25" s="8">
         <v>46090</v>
@@ -2681,7 +2684,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46079.832189374996</v>
@@ -2693,16 +2696,16 @@
         <v>46191.78207137731</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I26" s="5">
         <v>46090</v>
@@ -2720,13 +2723,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2734,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" s="8">
         <v>46079.83218710648</v>
@@ -2754,16 +2757,16 @@
         <v>46191.7821143287</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I27" s="8">
         <v>46092</v>
@@ -2781,13 +2784,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2795,15 +2798,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5">
         <v>46079.83218745371</v>
@@ -2815,16 +2818,16 @@
         <v>46127.17852545139</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I28" s="5">
         <v>46090</v>
@@ -2842,13 +2845,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q28" s="5">
         <v>46090</v>
@@ -2868,7 +2871,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="8">
         <v>46079.83218777778</v>
@@ -2880,16 +2883,16 @@
         <v>46097.54548765047</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I29" s="8">
         <v>46090</v>
@@ -2907,13 +2910,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -2921,15 +2924,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46079.83218803241</v>
@@ -2941,16 +2944,16 @@
         <v>46097.54554061343</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I30" s="5">
         <v>46099</v>
@@ -2968,13 +2971,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -2982,15 +2985,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" s="8">
         <v>46079.83218831019</v>
@@ -3002,16 +3005,16 @@
         <v>46097.54556621528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I31" s="8">
         <v>46099</v>
@@ -3029,13 +3032,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3043,15 +3046,15 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B32" s="5">
         <v>46079.83218859954</v>
@@ -3063,16 +3066,16 @@
         <v>46120.17308952546</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I32" s="5">
         <v>46091</v>
@@ -3090,13 +3093,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q32" s="5">
         <v>46091</v>
@@ -3111,12 +3114,12 @@
         <v>31</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="8">
         <v>46079.83218886574</v>
@@ -3128,16 +3131,16 @@
         <v>46097.54567954861</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I33" s="8">
         <v>46091</v>
@@ -3155,13 +3158,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3169,15 +3172,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46079.83218913194</v>
@@ -3189,16 +3192,16 @@
         <v>46112.50776931713</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I34" s="5">
         <v>46100</v>
@@ -3216,13 +3219,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3230,15 +3233,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B35" s="8">
         <v>46079.83218939815</v>
@@ -3250,7 +3253,7 @@
         <v>46204.709868715276</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>25</v>
@@ -3274,7 +3277,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3291,7 +3294,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B36" s="5">
         <v>46079.83218966435</v>
@@ -3303,16 +3306,16 @@
         <v>46127.68903959491</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I36" s="5">
         <v>46087</v>
@@ -3330,13 +3333,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="5">
         <v>46087</v>
@@ -3356,7 +3359,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46079.832188009255</v>
@@ -3368,16 +3371,16 @@
         <v>46127.689135925924</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I37" s="8">
         <v>46108</v>
@@ -3395,13 +3398,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="8">
         <v>46108</v>
@@ -3421,7 +3424,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46087.77438462963</v>
@@ -3433,16 +3436,16 @@
         <v>46127.68990261574</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I38" s="5">
         <v>46115</v>
@@ -3460,13 +3463,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="5">
         <v>46115</v>
@@ -3486,7 +3489,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46087.77498508102</v>
@@ -3498,16 +3501,16 @@
         <v>46204.710801249996</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="8">
@@ -3523,13 +3526,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="8">
         <v>46150</v>
@@ -3541,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U39" s="11" t="s">
         <v>32</v>
@@ -3549,7 +3552,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46079.83218837963</v>
@@ -3561,7 +3564,7 @@
         <v>46191.78225478009</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>25</v>
@@ -3585,7 +3588,7 @@
         <v>26</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3602,7 +3605,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46079.83218865741</v>
@@ -3614,16 +3617,16 @@
         <v>46191.78224288195</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3641,13 +3644,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="8">
         <v>46120</v>
@@ -3667,7 +3670,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46079.83218892361</v>
@@ -3679,16 +3682,16 @@
         <v>46191.78224165509</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46122</v>
@@ -3706,13 +3709,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q42" s="5">
         <v>46122</v>
@@ -3727,12 +3730,12 @@
         <v>31</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46079.83218921296</v>
@@ -3744,7 +3747,7 @@
         <v>46191.782318287034</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>25</v>
@@ -3768,7 +3771,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3785,7 +3788,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46079.83218950231</v>
@@ -3797,16 +3800,16 @@
         <v>46191.78225513889</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I44" s="5">
         <v>46126</v>
@@ -3824,13 +3827,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46126</v>
@@ -3850,7 +3853,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="8">
         <v>46079.832189768524</v>
@@ -3862,16 +3865,16 @@
         <v>46191.78230329861</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I45" s="8">
         <v>46128</v>
@@ -3889,13 +3892,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="8">
         <v>46128</v>
@@ -3915,7 +3918,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46079.8321887037</v>
@@ -3927,16 +3930,16 @@
         <v>46191.7823071875</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="5">
@@ -3952,13 +3955,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q46" s="5">
         <v>46135</v>
@@ -3973,12 +3976,12 @@
         <v>31</v>
       </c>
       <c r="U46" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B47" s="8">
         <v>46079.83218896991</v>
@@ -3990,7 +3993,7 @@
         <v>46191.782462372685</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>25</v>
@@ -4014,7 +4017,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4031,7 +4034,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46079.83218923611</v>
@@ -4043,16 +4046,16 @@
         <v>46191.78243247685</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I48" s="5">
         <v>46094</v>
@@ -4070,13 +4073,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46094</v>
@@ -4096,7 +4099,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46079.832189513894</v>
@@ -4108,16 +4111,16 @@
         <v>46191.78244430556</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I49" s="8">
         <v>46112</v>
@@ -4135,13 +4138,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46112</v>
@@ -4161,7 +4164,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46079.83218978009</v>
@@ -4173,16 +4176,16 @@
         <v>46191.78245195602</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I50" s="5">
         <v>46127</v>
@@ -4200,13 +4203,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q50" s="5">
         <v>46127</v>
@@ -4226,7 +4229,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46079.8321903125</v>
@@ -4238,7 +4241,7 @@
         <v>46205.487614178244</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>25</v>
@@ -4262,7 +4265,7 @@
         <v>26</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>26</v>
@@ -4279,7 +4282,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46079.83219059028</v>
@@ -4291,7 +4294,7 @@
         <v>46223.80805787037</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4300,7 +4303,7 @@
         <v>71</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I52" s="5">
         <v>46136</v>
@@ -4318,13 +4321,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="5">
         <v>46136</v>
@@ -4336,7 +4339,7 @@
         <v>1</v>
       </c>
       <c r="T52" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U52" s="11" t="s">
         <v>32</v>
@@ -4344,7 +4347,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46079.832187673615</v>
@@ -4356,7 +4359,7 @@
         <v>46223.808054270834</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
@@ -4365,7 +4368,7 @@
         <v>71</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I53" s="8">
         <v>46146</v>
@@ -4383,13 +4386,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="8">
         <v>46146</v>
@@ -4401,7 +4404,7 @@
         <v>1</v>
       </c>
       <c r="T53" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U53" s="11" t="s">
         <v>32</v>
@@ -4409,7 +4412,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46079.832188009255</v>
@@ -4421,7 +4424,7 @@
         <v>46223.80804981482</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4430,7 +4433,7 @@
         <v>71</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I54" s="5">
         <v>46147</v>
@@ -4448,13 +4451,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q54" s="5">
         <v>46147</v>
@@ -4466,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U54" s="11" t="s">
         <v>32</v>
@@ -4474,7 +4477,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B55" s="8">
         <v>46079.83218829861</v>
@@ -4486,7 +4489,7 @@
         <v>46223.80804584491</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -4495,7 +4498,7 @@
         <v>71</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I55" s="8">
         <v>46148</v>
@@ -4513,13 +4516,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q55" s="8">
         <v>46148</v>
@@ -4531,7 +4534,7 @@
         <v>1</v>
       </c>
       <c r="T55" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U55" s="11" t="s">
         <v>32</v>
@@ -4539,7 +4542,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46079.83218858796</v>
@@ -4551,7 +4554,7 @@
         <v>46223.80804175926</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4560,7 +4563,7 @@
         <v>71</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I56" s="5">
         <v>46149</v>
@@ -4578,13 +4581,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q56" s="5">
         <v>46149</v>
@@ -4596,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U56" s="11" t="s">
         <v>32</v>
@@ -4604,7 +4607,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B57" s="8">
         <v>46079.83218885417</v>
@@ -4616,7 +4619,7 @@
         <v>46223.80803569444</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -4625,7 +4628,7 @@
         <v>71</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4641,13 +4644,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q57" s="8">
         <v>46153</v>
@@ -4659,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="T57" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>32</v>
@@ -4667,7 +4670,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46079.83218913194</v>
@@ -4677,7 +4680,7 @@
         <v>46211.69077050926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4701,7 +4704,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4714,7 +4717,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B59" s="8">
         <v>46079.83218939815</v>
@@ -4724,16 +4727,16 @@
         <v>46225.552571493055</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -4749,13 +4752,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="8">
         <v>46154</v>
@@ -4767,15 +4770,15 @@
         <v>0</v>
       </c>
       <c r="T59" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46079.83218965278</v>
@@ -4787,7 +4790,7 @@
         <v>46223.808229965274</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4796,7 +4799,7 @@
         <v>71</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I60" s="5">
         <v>46155</v>
@@ -4814,13 +4817,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q60" s="5">
         <v>46155</v>
@@ -4832,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="T60" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>32</v>
@@ -4840,7 +4843,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B61" s="8">
         <v>46079.83218994213</v>
@@ -4852,16 +4855,16 @@
         <v>46224.67008298611</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -4877,13 +4880,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="8">
         <v>46155</v>
@@ -4895,15 +4898,15 @@
         <v>1</v>
       </c>
       <c r="T61" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5">
         <v>46079.83219021991</v>
@@ -4913,16 +4916,16 @@
         <v>46205.91561136574</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I62" s="5">
         <v>46157</v>
@@ -4940,13 +4943,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q62" s="5">
         <v>46157</v>
@@ -4958,15 +4961,15 @@
         <v>0</v>
       </c>
       <c r="T62" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="8">
         <v>46079.83218761574</v>
@@ -4976,7 +4979,7 @@
         <v>46087.78121486111</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5000,7 +5003,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5013,7 +5016,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46079.832188368055</v>
@@ -5023,16 +5026,16 @@
         <v>46192.680783738426</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I64" s="5">
         <v>46160</v>
@@ -5050,13 +5053,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="5">
         <v>46160</v>
@@ -5071,12 +5074,12 @@
         <v>31</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="8">
         <v>46079.832188009255</v>
@@ -5086,16 +5089,16 @@
         <v>46169.188807025464</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I65" s="8">
         <v>46160</v>
@@ -5113,13 +5116,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q65" s="8">
         <v>46160</v>
@@ -5134,7 +5137,7 @@
         <v>31</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="234">
   <si>
     <t>50001520 -  XEMORTIZ DDG</t>
   </si>
@@ -4675,9 +4675,11 @@
       <c r="B58" s="5">
         <v>46079.83218913194</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46240.600958055555</v>
+      </c>
       <c r="D58" s="5">
-        <v>46211.69077050926</v>
+        <v>46240.60097216435</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>210</v>
@@ -4711,9 +4713,13 @@
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
+      <c r="S58" s="6">
+        <v>1</v>
+      </c>
       <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
+      <c r="U58" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
@@ -4722,9 +4728,11 @@
       <c r="B59" s="8">
         <v>46079.83218939815</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46240.600907835644</v>
+      </c>
       <c r="D59" s="8">
-        <v>46225.552571493055</v>
+        <v>46240.600942777775</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>208</v>
@@ -4767,13 +4775,13 @@
         <v>46154</v>
       </c>
       <c r="S59" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="U59" s="12" t="s">
-        <v>119</v>
+      <c r="U59" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4787,7 +4795,7 @@
         <v>46211.69076003472</v>
       </c>
       <c r="D60" s="5">
-        <v>46223.808229965274</v>
+        <v>46240.60093152778</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -4837,8 +4845,8 @@
       <c r="T60" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="U60" s="11" t="s">
-        <v>32</v>
+      <c r="U60" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4911,9 +4919,11 @@
       <c r="B62" s="5">
         <v>46079.83219021991</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46240.60094069444</v>
+      </c>
       <c r="D62" s="5">
-        <v>46205.91561136574</v>
+        <v>46240.60095825231</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>223</v>
@@ -4958,13 +4968,13 @@
         <v>46157</v>
       </c>
       <c r="S62" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="U62" s="12" t="s">
-        <v>119</v>
+      <c r="U62" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5023,7 +5033,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46192.680783738426</v>
+        <v>46240.60096106482</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>229</v>
@@ -5073,8 +5083,8 @@
       <c r="T64" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U64" s="10" t="s">
-        <v>89</v>
+      <c r="U64" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5086,7 +5096,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.188807025464</v>
+        <v>46240.60096083333</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5136,8 +5146,8 @@
       <c r="T65" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U65" s="10" t="s">
-        <v>89</v>
+      <c r="U65" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="234">
   <si>
     <t>50001520 -  XEMORTIZ DDG</t>
   </si>
@@ -4984,9 +4984,11 @@
       <c r="B63" s="8">
         <v>46079.83218761574</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46251.952800127314</v>
+      </c>
       <c r="D63" s="8">
-        <v>46087.78121486111</v>
+        <v>46251.95281420139</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>226</v>
@@ -5020,9 +5022,13 @@
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
+      <c r="S63" s="9">
+        <v>1</v>
+      </c>
       <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="U63" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -5031,9 +5037,11 @@
       <c r="B64" s="5">
         <v>46079.832188368055</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46251.95276326389</v>
+      </c>
       <c r="D64" s="5">
-        <v>46240.60096106482</v>
+        <v>46251.95278392361</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>229</v>
@@ -5078,13 +5086,13 @@
         <v>46168</v>
       </c>
       <c r="S64" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>119</v>
+      <c r="U64" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5094,9 +5102,11 @@
       <c r="B65" s="8">
         <v>46079.832188009255</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46251.95278212963</v>
+      </c>
       <c r="D65" s="8">
-        <v>46240.60096083333</v>
+        <v>46251.95280108796</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5141,13 +5151,13 @@
         <v>46168</v>
       </c>
       <c r="S65" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U65" s="12" t="s">
-        <v>119</v>
+      <c r="U65" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001520 - XEMORTIZ DDG.xlsx
+++ b/data/50001520 - XEMORTIZ DDG.xlsx
@@ -1719,7 +1719,7 @@
         <v>46193.559375868055</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.559412372684</v>
+        <v>46263.508176863426</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
